--- a/excels/restaurantes_v1.xlsx
+++ b/excels/restaurantes_v1.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$G$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$H$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G227"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,6 +482,11 @@
           <t>Imagen URL</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Imagen archivo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -506,6 +512,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlfB3M8j_kNFP5gTGGYpBgcbBjkWOFxx0pZ3QUn6iS_GzNcJPURnxWkzOL3zIPXgHXQcJQ6GK5R5K8S0Ti3EjF6IPv4vVZygeWUn51YAuia-eUH_KdoqkpyjfglUEsTr-_sE0F2faY4ztQn=w80-h142-k-no</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -535,6 +542,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlX21tjDLll9is-08XKoxZPbpD8N5X1NMn2Dzpd0tfLhUsFpKDT0ChJ3avU1sERJZDoYzAhvsLdKwNH8uajhaJmfECPU8zl-O5U5DeQxxxwJURKzuPa4FbasWksi0XLrkkDdqa4=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -564,6 +572,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm8nHiEui8oHBOfsKkV4Jfn7xyLWOLVBI6keFZwlXTOCJ3ONddDSJ0n09zl7IejlQ9Rekgc5VydQpCbmHKS0dgu2o_kTqSe8efj1czT-Z9HAFHLb4m4vFRU6GrfJLQlvJHFhti1K1l5Hk7b=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -593,6 +602,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmo1LHa7IR3NsOVhITuvhLfMAmrEYA5dFYbRVABFI3eCCesuQRF40RY265H5rvfdSM4hcURfPW14BukwpDb7jv_cZ5xzMMDQOUI2hI3dNI6le_mccExPRf5JbyLdbtC4AIyqj7Z=w80-h114-k-no</t>
         </is>
       </c>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -622,6 +632,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkHZbLj0zXSBHRKm-kPXZ5thFE_Wgg1JOxR5nmwwNCBbv6NCz55VTx0Kq9qN_iChEBCyMcU4JSvO7OcWJlxfJz2i4BZvdX7j80bgmO2DtVGzo2lDl5ZjSnibO62w6M0HVRb9NU=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -651,6 +662,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlfes0XN9RA7B8HuxDZUED9aM5DCEh0Ou1qlfKZUx9HZmtc-AAto6Epss0iSSNZ2h5Ch01Aoq2v1-TW1TYeCCCpzEmq-RKTyeOg0da1qRyfqmNQloxxAhOM120yoC5UxwHbULndpAhsfQW9=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>kogumi.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -680,6 +696,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkOrrxc_SubrM6An5P6b54TmxEfo5XWtp7SRcUC_t3SSPtE4zlmCfVP90ctXrAiGvmpxYknTIQV0rvv80hJmdG3So2znAg7ez4pQJ-mAGN40vSE5RIFhV6J_xEpIlqYlTu4XJhZDfFbdfpM=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -709,6 +726,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWliQD6qcC66QiWNiLuVPsApQDMNDThZL9CEzd61CeqREYzP_XZZeJzYLHdEwY9GoibQxU4llFPeeXzxvrXBoGRxbQ33p57NlkFTA2eCO0dEpRCXwEw7Tu3WB6LGlDdA6JJB2t4bpY0I42Fo=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -738,6 +756,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkNbqQgA82izjyqQ7T3jh5JF62Ng2hg-dEKNqNHnVXivL_S8eIMIp1KXZqpG9PMEpchRCzvY1fIkRz0S8x41UbMB-Ei0MTzAcfYdkLjwWB5e5vcFvauUNt_aoswNqS8Sc72bT_-_01Qn7kr=w80-h142-k-no</t>
         </is>
       </c>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -767,6 +786,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlf4hIuCqeonBhL4_vnQQJo_Jgiq-7k7vzTWKaCzCDAjf7XnA3BsiWJR3MxLboWYuvAE11RU7lugXdr5VtMzM2VRCvlPxnEcOmsb0Og-UVMi5Vxcq41ofEXIsoZzEyLAVHnR2YG3Y_wfY6a=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -796,6 +816,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm-GAgKSx_6pGIvrY-fwQeAgTVD2p9sDx_GO2h6lSDi1jqdGQtsdY0purM6EXE4_2eb4hW9WI37Qna9UX_ID3yT_7aTmRnv6vopSL3duzGg69Za-eU6JXePvYdjcVF0Nt4n_oTofbs4neo=w80-h99-k-no</t>
         </is>
       </c>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -825,6 +846,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmj-Y0JkO1DAbEGhlGxwJGOwsRfc0FHBkYvNEJoldnZYUzJu6r9UaD6iV310ywwUO0bphYlR-hzGChNkI3ZZLE1sYtFfRkguMQ4aq6FXp5Dud7yPZNuQOtkKjCPBOWgLU6YilbUyxVUb7EK=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -854,6 +876,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnEr8EAJge9c1ZdTjKKMfPZRwValWIgMc7i4zYu_l8lT_3mVl_OORqlEA6Xqkp34yAThqRQ1uez_HNBqG2Qy-m6-pvskFQYJEbweya6RUaIQNIdTs_v3ZO2Bnc6IM8oYVNzyobwpg=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -879,6 +902,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl3oebDfIzvKtgFU0MAh3HaOxZM7yYC5GSdVGqIbbXN_5Coj8DDm86M7_btOMbxZIi9Z4FzPog7GKa1Wgi9PMWata04BPesFdhlo5if8MMj8patB2dn3mVZB_nTEPfUK3TKVwjU0CRkhkE=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -906,6 +930,11 @@
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl-3zeT25APhrnQP8E9uUtqf95Utk3aKQSUTxmqwAjN34VfiiXSUkzkT-OWzrSDMQY-eD_QEWx0cZC8w6MMA-UcHkHvZ3hyI0I5BIvXuqq-uYCpsMDymNhf2TI8aE7WFmBy4qap-GnuJFfI=w80-h106-k-no</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>mr-sando.jpg</t>
         </is>
       </c>
     </row>
@@ -933,6 +962,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl4FpKh7AICaKjIUFMj5tBqb1sfmMDZbMqkA1_0UkfTS-X4ooPPGzyPkJwz2dI7FXi4EWfm_5CMyK0Wnan7PZK8BplVMjkwR7VFWr1-cRkR26PNfNafHbE79CT2HBpWCf14_eJk1G3QULmu=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -962,6 +992,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkd_BuP-WkpM8ScXE57Z3RD5URopXudPGw_c0LmaRSWn3fX_QH65dPK9r2V5vmJsYuFGX1fYzdC59LEsbbl7wcPZtznjIGh62uewrXTIIL7Ac4uhQ0PlQiQbRieQsaLuN_V0h4Db-FKfEUn=w129-h92-k-no</t>
         </is>
       </c>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -991,6 +1022,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn5ah8Haqruhu7ysJOzmAwIvA45ZRrkc9qAEb9Oc9_q1S22CW8jngrohf_aCg0AN90gLWXYD-pxxYk8-NL78nzfPFis5RWvQg02-uMWmujU4eqoyyFkj2paFRkeT7uR0KcFP_miluF8uTH9=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1020,6 +1052,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkisWZP9CAgvBBI6lOTokvsuc8iWJDx63mHdwNrqUHTVN-9HBxas17haCkcO_LQ5ku_c2ExK8i4lDkKhNvo_JpnJeWdkHuAJzSRARXaOCSKhnuHy0paoxmMH1Qo4Yn-JklFehenVwNbC38=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1049,6 +1082,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkHhkXY3Oi7dQSd8mLL4_-qT1otCREc89WUbTgVuS612Uxc3oqqafEOtO-cuciXu_rfL3fIjPMdeh60f8tAmyRfZaGWrJ6w5lB4YJGlDohm_ntRPY9pHrAmrppu0iVxCpA6mNWoIdZmZVix=w92-h92-k-no</t>
         </is>
       </c>
+      <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1078,6 +1112,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmdi2Giy1td-Ot-2bvUB0oe_qplDSOO2i8LYumqRmc6MmsK4TbJic0HlqPnZMZndGkSZbPYTpYpUslfkSbh6MQDNlCCyMWwrza8JvfGe-COtQ_V-RqOixp60oidonc5iYy5g2o=w91-h92-k-no</t>
         </is>
       </c>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1107,6 +1142,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlBNQiEpQlt2pVKyUPnVJ0teuErK93bS6ZERJyyshiG6iP7pWEz8rdnQlv1lLVR2DbwfKE8QvM8ghYZVZjLtpGsXnjrcRG9GMkyaHEi6JfJmDGOvtutFVjUPMYw8ZeIH12ihTx_=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1136,6 +1172,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnRawVHcm_5aYV4jrJjVI3UiYbPscHl5pM18x1Rg4MQOaP5CN7rPGmhusGjgXyKd1OqAFt_KAtGpp9qnYyyV6lV_s-koe1beWeWDBMDi4fe05bz2dUblxYTKBfVKH6Es5z3rXrVcrAm_rsU=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1165,6 +1202,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkY6ExIlVNRxE0TDdrqrMOWLsToGzc5mhcRTmmo3QspzN3EPG-s_kJ0HWY2eyVSgs_87TrsAl8ac4OqVtSS0NiUn7TynDRdUKDhe_n4J_tIABDHXGSu0DQ7cGFFjmH09AfZIHl2=w85-h92-k-no</t>
         </is>
       </c>
+      <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1194,6 +1232,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnUvsYEH822UCNYMQvmkn905JyHWteB7RsSe_NGFSiP9NogTE9o-GviLIW7_6heq2To9F9u923j5BPMr--Mq3zj46kMndu7_m3J4an3ycnhHds176amLPytTfiWTVUd4SSwmqU=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1223,6 +1262,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlnkCCLSMJX1A6ZkXqsxnaVZw6n914CEjlV38BG1sr7bMRyCfV_MzQUTOeLStH_2bRAzYROhV3SXDTBJnQrAJoYIr8ygyoB1jwyFJdvVMDRE2qvRntdxxtYdpZ8GM2EZPZFevo6=w80-h142-k-no</t>
         </is>
       </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>gaston-wine-bar-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1252,6 +1296,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmk0Q8gbhK4XLGSZN_Yp84gjq2DZ_NFkPyri-F5bEnm_6AwkY-H-9MYuPVsqKINK699KdeZ4ZzBi3QNxqtoXsOjqh55bAmx5jlFlVm7LKaCOS89r36sjRZiBkfjA8Nz_lAvbAx2sOicOg7h=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1281,6 +1326,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlm4XzuGcMPUq9gLRi1gxetjbKPopFw60973p-9d0H6M0Dj-ngEARyHVZOEvIVuVIZpMmxbCI900J77QEQjKsDhqULVbHlU0KcwqJJuTivoPuAajzkUNoqcp3AkoqFn6OAtmbU_Lc0SSuA=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1310,6 +1356,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnCw7pu_OO8x8TLqZDrsACWkPzAdUAFedVcNt8ubt5tL-iXDhPLNlj-W76mC03rqVFIE52FrxqvKbV1vgABapITRjF-iAXcp42fl1Aqh8NzzgKVyjGvrQTFhV3IA4eD2kaS-QZW=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1339,6 +1386,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmQ8ikwImCTt1cBgtRyQhENG6-2QykxRrxACFA0wivqYGhoy4Zm8u6AySmUU9ZZQLd7Dhn6mDWBAKyq49cyDLyE93rDFs_D4kBeRbDsCsLBbGVlZxLhI93RoNQdNhzcD52cO_t95A=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-el-nautico.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1368,6 +1420,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkhYfQYp_VGbC4cI_8i1cVUZ6QduuNLujWYfiokTaou7wFSEUErtuZB4I77uzUmEG0FtPNdWonbC2zsrbxqCjKDR4MYZVz9f0zFoqvIZNAo9jdTJFKrExA3yyHF-HYAdTN4cvV4ozx_3wE=w80-h100-k-no</t>
         </is>
       </c>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1397,6 +1450,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkfyC4CzI9Zu0URaLokK8L9MI_8TACewdQl_LIs6G10K5g5S3N9_RIJGOE4Fo2XatA03mkRPWqyBHgzIdi_t45g7sn_ndSYh0RYh-sSz_2WPru3PVsHmH2e86yDuWYa8KrFjgiI=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>yothai-bar-restaurante-thai.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1422,6 +1480,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmCPLJADlJX_M1DyFdcpBfzhnu-ug8dXSJR0etbZJ0Ot4XarBBU0z7fKBkfZH6lpx9GAHHUpVqhVWzb97hpyTc-XGvlbBHOiYSlq5cqDha-SlY3vdRHp0VY-VH7RcAx2v2l1MuW0y-bgHLZ=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1451,6 +1510,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmUOp8ST-KCzvMCboPkZnPCdLtK-7N2bpGzwfYo37W2ZIXV-f2fazSnJoyAauBpvkz7ucY8s3P_R8Ui0E5N9iUPiHr5IC-1n7V6KObIqb3bTcCgHMWfUe5Z_eIEJaDSViLCJCP5=w145-h92-k-no</t>
         </is>
       </c>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1480,6 +1540,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk27Y7Vpu3S54ik9krMdvdkA8oF3ovWDKoU1n7p80_2-qSK2Id-WKyQGvSLvUYOnTMJm9wB3EM862oVmHcfnKJHg2tC71d-9mLEol3LgO3OoErTEWenSOp92PR8FySfFRfFrK-A9xMHI3lw=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1509,6 +1570,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmxglAiKV-9DR4uYKUWuu4_9TJ3-rRImBmIfV8fI0abPnv03EpeevrZldJH3h-GA2wBCK3DWBFNQtXbNH-jykwLf48hFud7AOStLGhRCr1PceXvVXIXAObwys34eSQJRUL3TNUavx9oKqQu=w80-h99-k-no</t>
         </is>
       </c>
+      <c r="H37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1538,6 +1600,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmjNTtqWfeSvvaHQF_tTYm1zaxYNl5r6lrcRKPwMuB6S_Be4IpA_gWJ1htpyrmXdHHuyhzYY0UbiBK1wCUtVuKOXOlqrNtviJwCMFGWIcWWqtLBDRVL7G2Wxhj5llqyZHbSakas=w164-h92-k-no</t>
         </is>
       </c>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1567,6 +1630,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk1ZKvqvv2h_sEVE_CWGc_wD-mbLAJRYB7Yq30_1YVt1NwR2vrwtrhfvmycjDh3f_XZulW6cgYUrBa3rlpMjeVIiZerTOzQMinTB1Ora2UACeNngJ6RWgeQFvHS-phRuAxHgInC1XS9kPMo=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1596,6 +1660,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk9QvvPBvPsUGBJQ3HBa7zqrfzJX7s7Gz-A2DSO-9wRJiMqbPqkWGXc3YQLRm9-o_se2OdxUeobAV6OfbLoI-cJoLAbLX4I1WuZmBjRfRLbFb2ZaI8nRqQfseeM62tJSMwACMXywlmn38VS=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1625,6 +1690,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlLr7nE9Jsc3FHBP9-Ntg5JbHH_6NPBy6DMHMblF8m0R0CkI2G311Q84FKPFvsGcA0GMv2FmRUg6hDBm8G-n5VdnFIi9oNcW6ljr1q_9zy9586n1m0u-s40X_14IBQPo7zeKP4CnpX06v8=w98-h92-k-no</t>
         </is>
       </c>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1654,6 +1720,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlWcnKG-qIpU01KKny__xDUXCmG077WP525QDx4XLOygo7mtDgbKyVw-fLUZ0_yig4CDiObc1WLYg5E0xaIAeypfO5xlNIQMQxsljwyJBsKM_bnaWbKxfD1UiED5HUeUYj4jE4tew=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1683,6 +1750,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlV3j5B8mFPlxcDsVlHDyFEb0vjKso2C2MGbpP3eIxOprzfS99gh6QqDZaMHpO61wGcGmDoWMVpJrGORje5Uj4oAcWq9gC6dsiWhSrWVcjesYvPCxCxVpcSh5DM779y9c8TffMDa3mkUZVc=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1712,6 +1780,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlTNvdXadSkJ_d4XyV-qQGCLO5DgnvIeLIWaH3S-Ha4jrLJzGg1N_qn_yoImBqEU2LL1LULv-kasUo9vqrYpNEhg5e_Jrv_9KK6GgR7AzH97s01-X_9BvjBf54lN04nemKlLGqYGgy3cksL=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1741,6 +1810,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlOVj-9SFQH7dd0UMPSeEkH9TvOzYYKg_5uFm8MEACAQikToPp4xVJsHZ46LCWymiwNcV2yJ3eTvFUEXYxzIBBg8KPbrdh3heSAbSNk1oOhavq2PpnkSznLTFl8_Xs5k-dVk1GEr6H7cVc_=w80-h119-k-no</t>
         </is>
       </c>
+      <c r="H45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1770,6 +1840,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlKHTaJRabiMzSQEPClvsuS5-Hlvd2MrqL7wb5lx_ovoXFXYsD7Cpp3OkLbDNEg0qvHn2oAReAfli_ZvG7xKczkFxmUV4Vflblcrl3t346oVz4NtcVdxuH6VCAHAqDRD-KO2_xNnY4BZ7oM=w92-h92-k-no</t>
         </is>
       </c>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1799,6 +1870,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlE7osT86fCOxIqk_sa3L8_4T4hI1fVgJmvCzrnV-5ZhfP7s2au62CxgDXkUOAWqn2iTjXvFc0ybOJ3S2VbOuexJyUEr_AOI-RD40RToFYOgyoTdaukY_wReBiVnVTMzaKKxI8Bkg=w80-h111-k-no</t>
         </is>
       </c>
+      <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1828,6 +1900,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWme_a8-dIKs_E823qJQlmIusGwdnOSktBCRyAaXPNk7l0eXaT5rFJHafDJ44nVyZxGwIBtQYhjFo4izvBlG57nQR9mvm_5qtabM0gJJklkKXk18Iv7_3AmOL2HJnQZMKoz6JpTniJnuuRnE=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1857,6 +1930,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmp0Dq5wwAAqP047Sa9lbRQGMhMlFF6PoKOX-MthEAp2ElqzNzcDJ8BGTWU8yyCPCGgkyhc7zOpUaGXj62aHET7RevUBJsdgGN5WPazJvIIUANcQ7UP7w7MNDc4TknZD5lIcBI=w80-h166-k-no</t>
         </is>
       </c>
+      <c r="H49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1886,6 +1960,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlqvuWyMY1fNty2AxogW9ubwCTp2R-Bl5Yt4d_JDDbZ37uERgnXING_F7off_8Wchse5FF6-_j51sEGpQuPsVtX4ZXkvj12RBgTqAsnTDCqD3TqZz4QVHy-zM_F07dkJBF3mI480yLV3rMq=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1915,6 +1990,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm2Aef8Ar-B0N9kVoZfRtMeKdkfSU1Rv2E0pXEIaRAQVcJT_y5paz6OHZWCn3idoxB3S-H3r6i7DS74CmL3OkR46yj_EAdNxo98UWq1XQfqd2y6VHk2D2TpwG7FJcg0A8JkrNlS=w80-h105-k-no</t>
         </is>
       </c>
+      <c r="H51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1944,6 +2020,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnNFE3zupO5sonInSOkuDnY4rJcTU-kLvcYWWKwHjAdtDXAK-Be4FTIM4XPOXKpYxcCK5TnUp-09E3vvVanTUWBayeQKC4rgyGLV5x2K6hkQy6TOh2MIr4Pkfp9auhGSMD0x55902YnzwgF=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1973,6 +2050,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnsSbvWsmT9SrN832ThhsbKmJ8jCssBoRr01x1UZt8hfkQ4J2zkvwxm4LMhlntvoYZyZe4gAz9dfI42rfQCcGnQR6_w6tYW5oKpmbxF5V_mumF3nP3JmlUPxOuep7w4uNcULmMf3vEZQk8D=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>panorama-restaurante-bar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2002,6 +2084,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkAocObmo0dPpYGdkGASwS0WpZpXDCvhcih7kmsPugAUzK_GeHebA6cqMPIfhtzu2Yz-ddL8ON2A3gUKpf7Q4Otkx90BLWamVflVXBUbnqyWjMYkJFKXnQ0hKpK6x-TCeZnmwJB=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2031,6 +2114,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmSdvYFozmJneo7atba5yrADFNNeMOzSE-0hCt0l6zwPMuKF0JebI8nyX_kgLrvXwMRMB5hYe5bvI7LL3UP5Q7KBJvKGehgG0Rd7d2ULieoTw4XJOX-1vKSxJLmSsaWqqKzAk8e5A=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2060,6 +2144,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkRged6vZfwV8acmz5sANZsjQdrWwTfOUC9tptiypFYrkKekmFuTjnlyZRN7AzQ51sUCrxPiqeob5_aNjSu4ikxKVd6E1tIJ-mT5b-o3-KQdOstxRKlnFo-mm835Okp-JrdhKF8rhFvFak=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2089,6 +2174,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnLU5fDW4gCa7K3ogMe5_YUS68pQxnKLDfdZ1X7KjlTaDJN4jf1Aum4bvpDO2mE7i-qRCLRPdvOS9CXdULy1_zp-8RiP1RS0WCdu23dCtmQbSQaHjpBuVCsV2pjg08b-NXA7B-k5iD9Ehm-=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2118,6 +2204,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlP49Dp3D7ZPPtDQRyL1xpQayqhOLcQXpvfckXy-o8PTKi6XEbqpafQm5pLU68ClytxsiyDDyjNzzi_40C03pygKqEaDyVUXEuRM-XO7rdfQwgP4dOCZWww64mXlI6a5CDVi50cKROQHLcP=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2147,6 +2234,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlwVBMO-Yg4m23n5QU27_ywwLv6MjbnwpdAavuS2alv_NbMlC_LWP-GOQkvSsXN4i6ac88fhm_SrF41n1zCDcew8ppzVjf3gRuDB7CBm8yDBF2qfmFziMES5hA4udUWxos5z-QxMbWHQ8k=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2172,6 +2260,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnRrCwFHzIvMehS2tzHDOyc_Vk1Lh_BVlxUKTinG8qViomg8HoiHRCrz0J9lJ4n-MTOCjeYnzLby4_rETR99WtIOzhG01Tc39fRfS5Lgl4E1sce6-vQfKFQBFYqIr1BTpD7dnuwag=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2201,6 +2290,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnFRqNqk-V0i1f_YJ631kNUUilPJliAiqPNV5YCo2fKdpb6o-hEHiq1u55pY5f_6zz7gi0c3SQmkrlhKh3ZgreMGXWtvY_jkRhJjhz6oghv_4E-pooUYGauMCkrfWFFa7k-hfSw=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2230,6 +2320,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnlsMGELEWE9aKdFfKyu7TBeCCW8L482KqEyQVWeMb14jy_vNqEiIsi_8aaqP16NvIbqnim-Fod2BEZYQWhxjcYt067vNUR6UM6BJW_E202vG_USQ8fBP-QwDIQswU5_dpwEKJPaSeaJ9Ek=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2259,6 +2350,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm7z2Nyg2ftwfln3bBZdLnbdS9X-pdxvp9_vMWjzBk6D5csgDaRjSKiXMUsYsT74KmBE6T54VVUE0GCmcuQQwtrr3JZbk8IzSQ8-8Ez6yO08qZXGAHxpls7lnVWKzWa9hk9usYrDj-J0Emx=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2288,6 +2380,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkRg_1Y8J9uHKodHJfBShMqAP3GgTDFrbXYPUv_608i--0asMtC8sPFuA12q6uDOVK1c4c_i1NKMHQNYDqS7gvVS4w-dD9LuMw4jnMozUPPeK1AwbOiJfWQxdRt7cJIKvzAPb2Qlbkcouv2=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2317,6 +2410,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlTZGf4ze9lFibD27PYW_a1mC20CfzFkCs3J_tV2NJ2Y-6ivi5Uugj7-avuI463g_cZWe_h_IVHYjkl-QercEs-uojCHJisNBQpv2OHYPmMbR6gUt-FaiVh6w7KzYxAQ3ut7oKXcWgiZv4=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2346,6 +2440,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkByzZcBkqqx3Az2VQwQVP1nCeAjkNHtBMZs54G9kPnIENtQHq2OjJDRD4Intr3NK-8UfbMGMJaw03Qvy44HuyM930ByTgtSc-JCu6SNQpN3Mx8ShXfSvuG4mdIWAyCuUqOmphR=w80-h99-k-no</t>
         </is>
       </c>
+      <c r="H66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2375,6 +2470,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkZx2O3GuBREi0Jzfprb6lFJ8h1iZq3Fmgbf0npBv3jp7tq6u1H3IgiSHCAfwDMz23XCb_lA0ueYGWfm4lVN6a5FjeIsEPzH1WHXt9ZnEmrCryYqZkBSlvJrxm8ot5nmcJHjreTgyQXheqn=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2400,6 +2496,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnwbJiPMNL5ptMl6iCjm1WJY_B3ZXGEMD5HHvhWjkoctcIIo6OLWdHhvRXmpvLRpSEKhdHgz3d-1p54X9gW2VuLv0teF1-68DZAwGQaqgqu5PkooPWx3x_PxajLT28vrO0t1zO-EIKE2VzP=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2429,6 +2526,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk1MCs04BjRmBatN7S3P1K2KH1vV6TJkWrQx_H1Oy0egqYJfVsiu4SB8nbRQYt3oz3CRHbCLX-fIAWe_Gz_kkFBXbl1xeaOfhiB9RDGn8GS_OZBNF9xpQDHl3bCMfren1xiADI=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2458,6 +2556,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXX9WVrg23tR2HOaoYtdoT4KhmAhUln4Wirmkid4JvAhgU4edss4bjhmZZYGRkGLsz8KuyeA6u21QoHXtwjQ6Tp76LdbL0NJF-pOwSmqKm36c8DS70vs7QGL-y6FLZwtA9VJvoCp-qjhfZ=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2487,6 +2586,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWluryhDJy3uag9kVnydbCSP6OLuMlyI8B3fgT6hbGL-sHwuxRnjV9kYhVm84PHr4xP03vpzWBc3MMZAQWBVrlesdRAg8UmycjDiXpujYkXxXPEMpMbQtWmyMC5sOWtdSC6wA99_oydsg9Q=w80-h94-k-no</t>
         </is>
       </c>
+      <c r="H71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2516,6 +2616,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkeUkUNQ8GOKA_4astHDIGV_76be9F_o8YHuwPruINSk8GKRAG33w3VBm8myrEdtmMfu87fnR3sow1_BABNThxGEB6md-fPRTrCrjxJ7fH6Eo_wtdMKSU755LfVG_0Vr94eOY8fqst_Ccpf=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2541,6 +2642,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWne6x56TKstVCstw_ByiI2TQWAwIVVqO4Rr0OjpEdYLNcJpGNINdvgVkBszRVQGnvSPeQnHj6qqN5M0-le7DbHtGH4LcOeR97axShRzyJP-g6XzxS2Q1qUc5rFPrGtC1s6RTQkGCg=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2570,6 +2672,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk7X5chstch91wBI--xlpKSXSzlxlWnkqSCo2tZVVtEmdvPn7W8PRszSBVT_b19QBwudDAf5-HSMHkTRS33E6XQfRBZNmGX9bVJsu6X3D_darGFQ2K_UkzLjianE7IRf9yEpt_xt5ZAjTCa=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2599,6 +2702,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkQ7yja7pMzZdaXzfR5TLNrD_TXh0_YaBksjJIv2na_7OIyO7TdbEf_d4gAEUkGi7USLAv5Rua2OArYWAkC_7TFpVGEDYjOGkH6G8wcK4de--rn7Q3W8dBm4opd0Z4UrErSD5mPlQ=w147-h92-k-no</t>
         </is>
       </c>
+      <c r="H75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2624,6 +2728,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl6gGRZ4Q_HqxG7DzPCN2iwClmZWaEf982DoUNPNHE0NZufcYioYmLTPmWzeIo6_rEV6jv2buotUQV-KGRJ2PHmAxlgcntcOjb7u8uQ7CUHrYmcIb8_CMeYKoj8YUblGGfpyZXTpwTiGywb=w80-h119-k-no</t>
         </is>
       </c>
+      <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2653,6 +2758,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlYkceBYRmvLkpw-OQEfiHKNL4DZOFf5jaKHCSlKN4lAb7c-ns2ZU5jhzrWYr69Z23FVLv1QTW_vTPqscDiuT7CK7IFb-EfSLJYLMUXkOL9Yl5WIkYOnXT9oWKmpKZwDwAJ4hoq0Ozi8BWK=w80-h142-k-no</t>
         </is>
       </c>
+      <c r="H77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2682,6 +2788,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnpVIWuWwKIHYtTB3Fxrel9kqEFmlHKuA2z6zzi0vOINyGt4nfz_4wxZsianr4t1Y3-Gw0s_AAE4dz-sVLOrh0CFlOi-3dHiLDzx3TGo0eaXtHgojHBTu7ZU3mHKrvS__YrXLaUULqaKKnO=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2711,6 +2818,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnBpmfD0obqQbX1d95kC_ftkMkw2i0UMG1lC8VCxNoSC7ASU02aAjYqrRhB3R1dtaxRmRu35U0NnR1K4bjhHGxoUAiXC1alQ3MJ7f77zuNAKfzW_QNsbcMYROTxEjGOg7Ccs3BZvg=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2740,6 +2848,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnd4QsAyRx_uygDe09jD26j9tw1zp8R3JFGuaCAcik8JH33mvf63s7kEuMi5jznAul0qY4D-krSMFeD_5222kAo2Lus5zz4lTq-gYYc5Hznj9pShlV0dSHP4Q0xFE2XX3BR8O31ceTFPLbP=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2769,6 +2878,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkT1zb_x5NbP_-6zUcq90hTsv_iMT7gneNCycCDWdq6CgHrjqm7kdchoEZXBCoq239QRLtiYqoYDEL7D2dGYUytVSMrLvpcCldv92tfbPDsRortPPW9HkZ36saAC2IhkcG7pYpslSyzoGq5=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>kera-restaurante-georgiano-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2798,6 +2912,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkYHgPD62RgZ3-FHB1TfmgsPnoLNNkVY6JjeW5l95jwnjt9oWetMzWP5ySLoNJfVIuyDJScZq2xj8QTb7VtO4STVyNFBFcy83nNkswyaK7QveYlbJY7TbS-tkf41o-vGHteP5HJ4dJMVav-=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2823,6 +2938,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkGiHY8YHizzi_7SOJaerANYeRcl6zXaUnVrAq-lxXixWqWPp8CWhotu8jTzkE_AiJHdsT9ssDwieJ2T5UTbk6-JfJ8aJ6AbyKjspvjX_bJpDMtsla7tQVavkOi4HuthsrTaNqkpJC4dRpN=w80-h99-k-no</t>
         </is>
       </c>
+      <c r="H83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2852,6 +2968,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn3tJ0QUoXcaVXonUfD8FlMLadBgREUo000OTS9Gs9ffsWd_yFSn7eAcjkKsTeRlQVC556JKMRq0tlJdN0o0VDetJ_1fhPkjKv4-nGQm9CRgUeQj7TYIryo__jPcgYnpVGahUupd1EqKZ0=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2881,6 +2998,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnZXGBaxdSBAh0JMtnNxnsnJJ4ixV9X1Tcse_pO-et5dLvEEATYMuoCVd9yVDP3Tm0uTg11K218Na31GWacmxep3a0bYM-d3Ee_bzQxsBFB7MWby338s4R8S9Gt044rcJhl015wNaq5MViv=w80-h95-k-no</t>
         </is>
       </c>
+      <c r="H85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2910,6 +3028,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmkIB-mUbVbRzOS9e1dZOnqcyfBHyXA-dEodnkZoUW2gNaFbNDFk3b9CrvvzK73GXh0jXuGmin0dcUqivmjoxrnocxslJ9PDUMJzR_hwHuMHoLR_SLo5cTHMPHRFqzs8avZdmaLHSbodzbD=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>velarde-13.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2939,6 +3062,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmc5q5XyXScMicTiG65jBmAd7w9-PNhZSMTUKz85XUSqQow0gmOHytpD0jIYMPBbUOXk5A_75jZ85s0TnAa26wHBqNe0ECGP_WPS6KMmJx91nBHs6IsGA6DibiMPjJVU0QUXJ5ZQg=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2968,6 +3092,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk6HqgyKQNNmkJE81N-7eqJKeNQAsoXpHTG9iogadUTtXPmTOSt_oQPmuDyk89eNFTaQEVIWJ2i_0_yYvJElbgtACa_-JQXTaxDO3XtqmLrIRFqdSz6ThJkLN1NXmywaqQPt_zqdk173SI=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2997,6 +3122,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl1ZX8_sLzr4ujdF4aoCy6eKyVnBRrjyoHgXbLHlKDLWhwbJPIYZxSFMGPVGWEJqPS212ZyJjeSV_RzJimhsuC3Yeey6yZzup6qjhalBGRLiNvvXyRzP5o0d5wG6TwrKaqO-VwU=w92-h92-k-no</t>
         </is>
       </c>
+      <c r="H89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3026,6 +3152,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnMsCMniTc9nGfipGCfb21xx49nDQ7X1Pv_eoWAp-R4H-ZnptimbYw-Awr3mWG9qbcWH_Lo_EKQ6pYYu0qCegkm8B9NnTNofnnPUEQABuN2zeVpOuoT2YN3sDTjj4T0R58PY5wV9qj95QEY=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3055,6 +3182,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkf92i4dY2xt4t8yI42Cq5EAFEX106O9az7gaAyaqJawYYJjSEYaxkHVlZb-kbsBysfSDp65jC_LAmeO4NOueqPOR5YTpeZeWs_vMOvY8rSVMM7vinSgc2ZC2hcNAdzPBLmO53i=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3084,6 +3212,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn6OnnyMfyQgZOEHsXCM0xS3-w-emmUE1gIf-MOKe78JKyc6wae5uhQMdz67XCY4yXnDYAQlv6A_HSe2c83HpsmU-P5qy21tgp1yE7vEalNCqE2ePo_MaHDEUtPJbe8zh_yQhNHhPSbSpA=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3109,6 +3238,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlDQV4PW5fFUC5i_yG0RpD5eFE-BbqNKpIqoUOm6mbkiClICJVQSU1vzfyotfokwp7CJO8WQArVHKNUN6vsRDgxACoBg_09pb3zhejyduhDLN-_VTms8MxO0HEBZrCuCoeUShN1X-gYMms=w125-h92-k-no</t>
         </is>
       </c>
+      <c r="H93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3138,6 +3268,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXlXmfzPrlkZsM6OvWHVYL0waAlxSDP4S7IIswFaJ2ZJDRJoGilEqQ0NAtgLK5nZ8eWCCkUVlvPTERuGpbw1_HIWwY2ODs4rYEVdE-Tg_Nvkj5LEmRcyNoN-4u1I0eHJZtaEWssA=w103-h92-k-no</t>
         </is>
       </c>
+      <c r="H94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3167,6 +3298,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkesAiRT4uZ6y8dt-X7O5XVzVOk2afWDLOI3IcLsysTk2BxV4mzqrfdXihYrNSYwPQjlRHES_Kf5K76LGD8PYJDFscflH06sssj-YUyW0ddiNJX9oOYbwxUieLxMW1mFMiTcNYD=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3196,6 +3328,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkcWyBTAZ2AX-3ccqQKLCtcREvg676x9BCuyTWt-wkijEW5ubvE-rN554478fn3BHZ2n27pbUtgQh6_9vGfEqSMP1lbnsrhmVj_HQ1AJEBLXuYzOQShvYr-0GNr3ehsgEzTvsJhDJbjPBbg=w80-h92-k-no</t>
         </is>
       </c>
+      <c r="H96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3225,6 +3358,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlsl03Te7Sk-u0DkXNkL64ETogrnrMySf7Oh9pTaJr98AwswD_Hk6TNHpMjFgKK-iFgq2V7jUK_L0INUCRzCzq4zl0aaYK4rnBFGt3dy0mNb_I_bI9CxLZisbNSrZTUajRufRUd=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3254,6 +3388,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmbj7R3-1Sm5SKjTnqCNnaupOylxcah3OjTuXCI8eBU907aAYJaD48GVu3IPcuzGicbwTGgH7o5pgWUOwx3VK8f27gAl5EO5mhY5-RtP8haFzlMza51lqOlABOehSS7ElxQldRdOzbfhlU=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3283,6 +3418,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkju1XMUINev2-NRf6_cw-Z4BjilNtDpFSuHKagxWZsUO0G8eX_IHM4ZtJeFaE6lZIaZng8rcRPBN_r-WZmAfKOnv7HnT2rdBGPHsMFrxQbLU-FblS3qBqQTfE540W70rScuymuXg=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3308,6 +3444,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkBhhYq9wR2g8tuWuHdk4doZ63_BCSMeBjQBQhEB1fV-e-ttgoz4MX9IEpGfq6Xn8s5OkbCf9yPxC6kBMQh-VA1ZTU4HmYBoqvYrj2gDIWjFeBptH4mSLsqAtr3xXyUPYgyEfZIrjiF1v2k=w92-h92-k-no</t>
         </is>
       </c>
+      <c r="H100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3337,6 +3474,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkw8djyYh-crq1sl1tVKbEFZ3GjkqHZcfaW397KQFiF7A-4PI4phmLrz5Hbf3NkqsnSJwdeUel4b9NpBsCGqmbdNNC9JnUMoJgMMu0-MlXjZbFbubeK89Koqfi10Mhi421ciHet=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3366,6 +3504,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnzSUZWV3XogcaNmm3ZU40lbF8K9XYGxmLB7Ltn2gQ27AteDrYOdRNsXjDu5ClCdo0AIQTsqh9xVWVWgvRNySLZEP0mTHehDLJfwT5JmOIf_nXTi8m9wNcb7s8FQyLlYSrw2G5rtg=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3395,6 +3534,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmV3N_CIfc2NMm3zBQ-icE6L1D6hfUWk5Wxj3jg8_c1LE93EhJC_guPgtKlv9Dx-cEhy-27MHbA0ZPPuOi5RQvcXPvH7xM5Yuz6-2et_d0N6u5Y6ZXBApNMu2Vq9xTtFEaG1gBBE8Uy1Xg=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3424,6 +3564,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnlfFBhr8Z17rxHJBGLbRuxV7Zj0KR_ca5_PRoOTipnFsdjbBLJTsK_2edo0DgPkni-vLaonSkeMNfuL6G5CTGumkL9xd1F8st7yi_fNMjUYne6brKJPhf4yVAWfpkib-hzMV9msgRKaerB=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>alright-majadahonda.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3453,6 +3598,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnVIgjeG59XiLCzCIursWh9B8es4Eevrmt9I3SyC9Xmc9HFRTNyShuujzf8adYE84a4c7hAMAAOYoPbH9FQ8mszDiaAcj-x08a4oU65Ah9VfNcca8Udcg36pgawXFeFOBkoopopog=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3482,6 +3628,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmCuts-mY7GW4PXpSZCnq2sAiyEmttQYj7OkHtBIoBfj4J8-fPPPaHPqsBOlaG6zHsKuLtgOA15UrGDnuPEHUBliF5LffmwMXhQ26hkpoyxQqyVozB2J1ISU4GdB7UWkrBSezU=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3511,6 +3658,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkKIDMxwNyMceLlfwdR28lnxJciFQCFSMR9nT5948vMZDE4kT4VntIwoVNkZRCECL8YP8NwIhxt0_buRGwzjSJ5YLDzWvFp2zD5RELZvsS_koYJo9YPaPB6ibvSc5wjFDuOvCLFR2ljLylY=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3540,6 +3688,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm7PHKOJ8ET49cQoaRaLfSfy19h_re-JgQgYQ1H6gPz8TGW6_ZjQzAylKNOLTwKoD_IQMQSLKpbKYA5dgAJS7oLcKLIC8epE5gn2HH03AXa_6tV9KGRG0Vpy7K1e-Yw10YIOqlXqRGcpTE=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3569,6 +3718,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmJCv52Jl1nqlux1v8j60mhYOZYCLcbQYthJzTuynBlfJ-DPQd2aPSmOwFQPLbmZFt381iAXUQkAg-AR1bbO6ELb32XYDmI760vH_UM1DTmo5sNBzEc2_i0gPOJUkvyXWgr9dD0=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3598,6 +3748,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn_Vl4ZXUbzin-34d8XsLKs7JnF_Ircd7G1nBHiTy8UlM6T8mdzJxO-NapEhSezBemErnBr4-hqxqS8QAf1WoD45Rfj81ZmHcK_ckrZVqAuXakIceAkyVpaT8R7a5nyRKR7IaqJ=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3627,6 +3778,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmwC_QLO_9-yKQ5lMs1dE8pLKzfdNYyThA20TDutXt7IzEEtnyUhaR0Sw4fSnFbi9ckpuWZxoogreCxsZnc0by3HpAtYvQQLjLlFu-kWN4EdeGZc6WqsfKviDsx7gEpOPaKN1SA-IDPYkTO=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3656,6 +3808,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkn-AA1-qyKZymJ8-PwpVIcXmdwY-QsTOh1GIVR8ThcBUk_C6U6dkqb7ZB4SPQanTV2p-13pxhWbdw8Izm6MKb80QjlkL0NcwJpOdIJRvJa1ZUDj0mPszIGQ0Nj2lmdqcBKTChp=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3685,6 +3838,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm5-HxKlYBH5WWx519MxffbXOsR1dk9GDkEWrpy9jELY5Ei2yoNeVoRfrWWrTQkBmDhzb77YPIL8nwNRLawfURm06ibpwQwo54PW9dvoEwkoxW7-kw8h1JfVoCKBfHJleaZuR-5=w177-h92-k-no</t>
         </is>
       </c>
+      <c r="H113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -3714,6 +3868,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWllUbOZlQ3-LXHQ-taWuwe2WMDKkWHkUi5rQeENxTA94etX_FFmVgxrSaEcqqhT7mrIxvOAxGptGk_Oosgb2o4axW4bq4BU_hFMNh8YIR1kEFSlNZSFO8YOkZ_9ub8_WW26PJkHrPKpMdJi=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3743,6 +3898,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnHKwPwIitDnGUQlNpIcTCkTY0D4I4BYZewFwB0Y6iSv6d4zGwxIqr6uaS9uONO6mDEBAwjWb78KsSLPIj0uVuw0i_Bbqk1eq9B3abWg8CuvTf6KmX5ybu8aLHkKkP2tZcJZyIDXjh9biCb=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3772,6 +3928,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkocwHOSO9HEQh1qlSnz8CWIZxc-MFdYpD9IMV5RuLWiALc3v65Nq5tsKoE5Xh66KSuSnwnIVLiVrzJ_BdLlrz_Ub9GZQs_Om7GYzElkHm8PG3S4LFcoyzpeD2gLIADUPVNuEdZ=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3801,6 +3958,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm5Be-9pDkYGabcYNIJFA35FA8RxhFkLp1jIzsrThGPv27rpL_R1V0d2-QwGuW3_ZPsTqQBK4NagwByqpIHb1pcInRV-l17f58AsqQZQvDny4GGZFyCP4uCre5iQ9tjOhBnyoNo=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3830,6 +3988,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkgz03R-axzlIuHzOYwCFWCrr07ksXNxCclsb6YEKm6dasmVDHHj4g_lrRwKW11p3-ShxQWpsq6Ior3st9h_wv3dL4HKFE-FG-RfZ19X4eHfD6D19HZ_WQqAf1wGv1v8wP0VRaq=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3859,6 +4018,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlEHeojkbMgtWSL_o5RKGMdBmgWYWGzhOKy5c0PGBgf5Fr7O-E8EHn_V42U1ohTONmR9BcnOHnfwHYfXvhlCQOJQCn22l7iwfIXqBVoNUIJKMURX60UU3LOQJISDaMrpcdgctEj=w80-h137-k-no</t>
         </is>
       </c>
+      <c r="H119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3888,6 +4048,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnPfVvPjgJ_jUC_uJVKmShjf3GCOvLMEdrYg_V0gpTYD-G3PSIHSKHuPDATWzP9jIrbgqUUrXLQRO0nKeReu7CMceSkRTrm71V3wM4l3wzTOOVEcOqo-i5j_tgNNWoRhnNk_ahMuQSee4SE=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3917,6 +4078,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnKC1T9csp_qyZuXnuQl2Uj78Yi4oPqPtyINvIYls8__qHH45Y15JOQctEbM1AvRtXoehddM5oKsLBlSKfiKUQZMezViwDTF59uR-rQlX24jlyOqqZ2G4pYmAzack22p8ulWNV4t3AxUcU=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3946,6 +4108,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnQcPEdV7d95TmFF9-uWuiin0JSKFuLm-pvcGM02VBx_7z4FMCzrBgqoh5bsxZiaelDv0p-H-BWB1VbKIhvu3goFQ50Zp8KFRmJT7ux7w5YvTI3Y2BjlqgblNxK2sO1h3JnLm24ZTJHBJjX=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3975,6 +4138,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkbWZoZ9OjPAS80GP5Q6qi-cE8r_fjKAsSva4gR4QdSPJtHhr-xM2aPU6Cy8B1L5RHN2g_ksohcBkT5MOCgWbZdHXJwvj0QQ5AswuVWXF16vc0RCOc1HBYj9YES9Rje-wEBX0RA=w80-h119-k-no</t>
         </is>
       </c>
+      <c r="H123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4004,6 +4168,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnMAEvD3S0QBSBRq8QtB0OI1KIcCVcpGb0RHyGh5oYVS_QEy4aXNWCOjoPFcGD__XLsnIfNiDFbzH_hlTi-zU8b0kXgZ_DPsYZ_-GC2-PqzQeb3mN6lm0e2M749k3uTjvZvAN4W7DUBE5nN=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -4033,6 +4198,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmHXd-NYHTOm-L0Gpenn_w9j8vUuz7cm8i4256hF4TkY0AN-qogCi-h1WTBIHfgipBiH0iaVf9ET0260KXi2AwDyeOktehJw6XZXcig1-sxrjp7JsKwJPzodli_8R8N6mZl8jFmNA=w116-h92-k-no</t>
         </is>
       </c>
+      <c r="H125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4062,6 +4228,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnBGlI-x1cYnqirGFsfvlxJRzG7Y7Ay5H6M5rs_sS-Oylt4IQ5Yt8XT1TBpaC3TAIlmDDe6HULfBmDDKcvId_CU2-D7VsD5UOV4mldUzS37trPl4Br_TXlmszBGa3ZI9G8nqoiIfUMWKIwG=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -4091,6 +4258,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl7lQ_SsSMCWQKtvTRRTcGS98f2h_hHuPh8YV62t92evyLhmuY920ADdGidPZkZborinOQLo5L0BbAJ7VykhVMFLkTw6tX54gYHcq7DRrJCHASmLYPIvUxdtgfVxq_2CsdSNDrqf1BMhDDP=w101-h92-k-no</t>
         </is>
       </c>
+      <c r="H127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -4116,6 +4284,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmPlAg62VWjLDijXEInLzAdRRniaQPUURvDjEuxvgFy6aM-S8be7I1cgAh5WWxvcMF6eylFHSyGPUkiGOSFi07Tjt220KD7qHN76eEMOSlzEGxKUgZv168EwcYfRzKKnwMbLm6JE8bfHuOF=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -4145,6 +4314,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn2f3c-hNlVutkzKjyNC13W53g_70aLZQ4CKLedVLFNure8Pf_emTsEHX7Z-1YYhG0Vn-WTVvXjPeNq1hx84MF7J_zvq_cfpktYokv8C4xjLMeKgy52FrvH8u_urD7cvlQYFAJYlOulRTU=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4174,6 +4344,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmgMipgpDm6J8TJPWpSsg1oT1PLuxp5JO60sJeGqfSF8ZPXwQq9BPsFVqU6hfBKk1LteI1clzufs85e1J1hQCbm8XRkYC6XRmKO2l5T0sraWMFOi5jGMSWKLfEUwt6Hk8MzatVp3w=w92-h92-k-no</t>
         </is>
       </c>
+      <c r="H130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -4203,6 +4374,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkZs1A6whXp7NZDHhJ2Im-KO-UPn0Nf6wWLHfJ_Ety0cbvMNHZKZqJnW3JJ7U8qvk3Dz6tMPFF7cle50CnDPO_IczILRTkXpwrfqQPMmgy3CX8JWvO9oKZZ-mUWGhY58A0rct8-=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -4232,6 +4404,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl8FPE0oXPOvolN2G7Vfk4ZSKlkUJobZZc-_nOTt4oahrsw-MxJBNdfc8qlmvq25Z0YMo4QfQG3yzA9hBJ3dBXNunR6KZrLVO40JlsjgJSJ71v6CI-Qls65U-UOKB4oUpU4mEiL=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -4261,6 +4434,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlrAxDG33xbn56W4_fehxv9kQtrQPlg6wxciPtmK-uwKjCa2CA8F4B43GY44yP6QB2R26bqFrMjcnTQzhC3OlQtj2CURz8GcnWV_DTxKTag1LbiIVvkPu1pC0UyQBpJgr8_v-7jrcZbq3L_=w92-h92-k-no</t>
         </is>
       </c>
+      <c r="H133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -4290,6 +4464,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkZrxIzooG5v2TlhYjHS48ABmycOTEjWKgHb3iUOrlrzYrAPPwSMiSI7loKfMEX6lU-_xOG0cExt0wrIuMffHz8V6W9nn0q_rWuOPN71wFfKwTJeCDiGZBO2sSvXbEfDbUGQTLN=w139-h92-k-no</t>
         </is>
       </c>
+      <c r="H134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -4319,6 +4494,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmg8OScFHyEfI9teI8tMgDX1bMHFKzJRa_BZ7CCbSREJlwM7ITo87rfRaZKiuBCm08sE9B_EpiX_FxbftiKnKukPxNTE68uQZ2G11-uBu2xCbAp-l4wUo8oLBiY-FaHs6653mYPLw=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4348,6 +4524,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkMmSTUtFJCMAMGW3K77eUgjSJIofpF79DC4KgTGuAyUF5XpFTliDApM1xuaAS-EzO-W73XiSKacJ0ogOCmYFLtUB8GYfDKcGNVuGzQLUvnTYj5RAy-9SjvN2G2atGNWo9MRZyrCg=w80-h119-k-no</t>
         </is>
       </c>
+      <c r="H136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4377,6 +4554,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnW46ixyY3-5RRAZWpa0clnsSTwxkYpzqAiXZHzG_hW82HjxQkgnJncps6LiPlk3cfjjwSxjkXAIYtihdfee8u-Ecy4O6E7RTTta8Qcrcuk1sxe9srfq55-uiwKhGcndB5kQ94oEdvikRiH=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -4406,6 +4584,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk9H6wPuaBE0FcapS_nYyU0kr1HN3LrncbAJkr9lU4lVlVpkQmqsxZHNDv-znnfT41eKlIHF6Hxx7dbqjKQsQbOAi0vrf-eKn6GI7GfU7vcHDitmv76IP-mR9zFQAklcIXMflEkIP-TByM=w92-h92-k-no</t>
         </is>
       </c>
+      <c r="H138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -4435,6 +4614,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkyyjl2Kfm1886XTk7OPOIe56-upq7u9zGDy6ai24VnZa4melfBeG99o0maCcTgE_RG8esUNSCLJFoqHmDlcmCm35vkPGH4dkYuh9gZTDaOJCAJZUtFShicHUXv5_pOMzLeX6fYMjIWSLF4=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -4464,6 +4644,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnAarH_QCN_94bWRcAXHIg6gkcMzdUEaUjTYwgg9tgVDDRTdQ7SBnyKCq5PltK-HX2bXGyqKC2aZwdVJ3IoMG5wZeaEDBhxzxKLgVtbpJkXqzFG6FqDsYvpQpoKW_D2Y8mhKJliFg=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>tasca-barea.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -4493,6 +4678,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnb8RzYfX852xk4Y31chcaA9RkIREQGhGFmoFFUDcv79wMlilQB-zgaCCcxH4PqpQTF7mQ20gjT87H8HzDh-pW0FgVq0IKQQv7bVGwrvh-4x4l5fQt7gxw8uKgpKYAJr18mHKsuoowkLBY=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -4522,6 +4708,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm3evZ_9EGmBRW2p0oFZZxwTaZtu9MdDeoaev3Ihk1le1ynPPBeW_00PrgCtZGKSx_lWX-ZBU2C4mMe_H0UQHu9wzofxgNsnog1eGSoKgiUfGO34X5-k57eKiZnSfwGNdjHHrMJVPRYKR3Z=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -4551,6 +4738,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnJ0_dHa6n3cQR8iZyK-RCfxlAB8hAXn3xlGGarSg2s7xi44aYBfTCD6T2xVC4z0wmTF-lfky4npCjMEI0K-cIGfsOJjXc7zG8HOQJfltC9ubBuZE4HxhML22ihyzHmZL0onHAEjMQtSgA=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -4580,6 +4768,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn7JGAwKEDOJOmTP1NEUdBOAn1PZpAi-cK1D8OTS1U24fbOHPWQ3lpSl3FMh6THzMXUsQ0PQ3O3YUzlfayq8se6Em2atU5u8jFYIwwp1lML5JjnoB7KM4tdYKeSoH0cScXzvZUb00Et6BK8=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -4609,6 +4798,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm5pzw3J35qdCSLGxlO0jDBRf2mNnB_ADTDrBK13GfJKcHdJAbfmpz90CH88VxMfRJZ6arPuKx_1VMkK7a-8cVZ3Bxxy1PTiakRogoxYW2i_SDPlC5pzVIDRDls-ks6hcFxLBEm5KJeIce-=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -4638,6 +4828,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkFakgzAKJOM2lLqrnql-Lr0h-cxu7wiAn4zLF56L2_RjCd3WSoGIg0nO6EOnX7razK3ERnbX2EWUTduogHhQZyb9c0yyNR66ESGMlK9NXfYO5Jcsf6kwqZyTFK8Ay-5LkKRkjF7EaB-do=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -4667,6 +4858,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkbClm0S7_I_GAqgb-ZMxHN3IKRzDUB0OZVquQY8ffMUhm2ggPZm_Mp44_t_ClMAiEM0ezLL2L1MAm0pzI8MYFq2azcSg12J97kULRABOR3X94Paf_4TU-V8G_WfFLc4ZbbBPpuHA=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4696,6 +4888,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk47MaevpmhZbeBq1dOJhbesUqWUxUAwxYSdBNqknAufhJKLSlgiytOh1YtvvelojBPstaqjzKfUuMaxLIvOV2B4eohnWQ3WNEQJj4KrlvPUWjSIhw6fuWJUmx4yuJHmbEYoUbz=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -4725,6 +4918,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWncge-M6-K7-6By88NWjHdcyAixskpW85BFTfbi7asBGnUeMLKkPuR2TV3T31BcfN0Q9lccUGomC8LijjzSA3kVUUxpsXaSsmQOptrjIYRlKhjvb0kLUgHyGWTV7cCtKSXMF13YFQmJyo1b=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>alto-bardero.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -4754,6 +4952,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn5phprnXu109fjXyyxpJdNYWkIYJ9gWqWU8Ljhn0lpPmB2bA0vaCMpNZ2kwEO6MFIUcExJQ7yVtR1E0Yv_0AgBeabXj-c4poMH0MCK_qvR5ew6PZ7r1JR6V8AtaZR0BeIzb2XqNX7FdQF9=w80-h100-k-no</t>
         </is>
       </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>taberna-la-corta-la-latina.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -4783,6 +4986,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnfpzlbFvNbpViJULMacs8snaVoEMuHZHerKcffJQ8ALdi_BGZtLknc-m1i-XSCZ0mV1MQIMyJ-6KvemBGVJ71vqo-tS4iq1Am470oGd0OAjtQPX3cUNN0Yqsr4mQUIQwkWHxPte66mv4Sh=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -4812,6 +5016,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnbZv1QV9XfHQikQWxCuIDShQzm4s6Es4KwNPooJ_uRZODp_Kbah4BYiMTZsb2fDre0j_N53FhQbMKHs0tZGwOZUWIvND0IyXI8ED4JZfxW0bJ5QEFO4sZodGqQLJ7LE7ZfbI1v=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -4837,6 +5042,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnXO3c8vtm9JKn9BtndHHYrR9uCOW0NHdrnvt0AzcWpyKPl5uPpXdvGR8SLfcQBoxhwS0hSGzVz48sEuXXs3s4K5k38kKWdtfH-uSxDiJ9jZWNpo-DE7aehvUmf6D2P0FWVeQRf=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -4866,6 +5072,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmSwI0jGilx4_UgYWqHzMRkIKCM-ZckIUCYGWXIRAWfwuhdohMWRM2BUjDWhJkIgc-CfRsQCMZOdKSJtXkDPVfJWwClvSxStE4xuTi5ZeCG4WSPDrRIVn72rgOMBCYk3kMMn88ORYYpGy8=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>vrro-serrano.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -4893,6 +5104,11 @@
       <c r="G155" s="2" t="inlineStr">
         <is>
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlStWxnhGdyC12lYEQE_0tTF5C6GjX-RC2e_vZTMlnpESPzDUut114TUCEJFESn8Q3ZAUyPr3HxBOiRDEDQU90EZmhxlN0X2RxLkSJCtOuWEdsCuW4t-3zdaaBki3ynrVM2JFg6=w122-h92-k-no</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>amasa.jpg</t>
         </is>
       </c>
     </row>
@@ -4920,6 +5136,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlr2KKoy4NHWDEVVDe_RDTL2y7AfJkg-z_Mj116RT80dQX6ThS4uue_KH4lrj8RaSFtLJ-SknxP5NmpjtIR4OA1G96guJWXqkQJ-d1sy0LCWctSHiQiYh1TyyUk8dUno1m8B7o9=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -4949,6 +5166,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWno_Fx9ORouoNDgSdb1qfhcfZmK57JzwSb2TYEUGN4HQbRtHgxJG-9LNzg86PNjCSI4QeEo2YGHvEmw42HvY6H7YzkPwl1_bW96GHTHfT-ZlLrpxaHdlZWm1pulDqse1sUmXKrC=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -4978,6 +5196,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmB8uXSZceBnxmGCurFGAVWRp47YbAxbmzZc3sPisF6ELPltUvEnuDT1kCSyar3RI1SMNbRUQlGxCedbXasgjS5IsW2d0emOe3WvBVa8PDq--R2gOizsUDsONGh9hezO4n-XsUErLoqGd0=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -5007,6 +5226,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkvn5AYHbfrXvI2zqfSjQpMs4s9OmkEk8io0aEnahr82vVFEhXG7YOUB07Hw4emoLWcTnGAcrwA0j-xDff_px_ATCMpGcC_ZFtExlZOnx4Q__Mu0YhYFc_JaUJwaV3gVQYScAm-LU8Xdlw=w80-h98-k-no</t>
         </is>
       </c>
+      <c r="H159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -5036,6 +5256,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnenXRZZ_OBYerFhVBpwLXXRK-9P0JS0HOyn1PvBPR061vTJuZDmWcFCQeofA8ysflNHdYY5fVhqrpZ6gKjMe-inX5U8vDA1DU05v_Xh_iZOLHl1q_qH-OcxZmUS-VUyMUYORn3yzc4-O_q=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -5065,6 +5286,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnoM7GFX6wuXrrknBjx0V2m6tLyKDasI1Btv4bV4DACMLJ5CVVtiHH8uqmKCMEwiQyHLp2lJG2iqO-fHDgEw_fZ7xIoPcOO99CJhMotiz9CFYHmVyEZ6avLtDhegArjCOkg3bsJ4Q=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>casa-a-la-malicia-bar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -5090,6 +5316,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmLL_jekVVNTnpVGOYwjqifT51NXYF1C5GhVEpq5v9nUDdidpy8k8PjzdBwU1821k1TWbenEvhxRRCAc2CNtK12j8vKputAt9Ez1lZKTGtE7Z3-OPJMGtwL3VKh9HR3skkjZ8KCXbXI0rLv=w89-h92-k-no</t>
         </is>
       </c>
+      <c r="H162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -5119,6 +5346,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXcCd_cE5kNWE00PvW553rK7EyIogcLLTClCqlwLVFsA2AbSU9i2yIUTB8idfePMtoEHlTcigiYd9J24dy8u-EpcFha45kKkbVOH8BxpJZ53pJ6bbeaiajfribowFbk2TDE6w=w115-h92-k-no</t>
         </is>
       </c>
+      <c r="H163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -5148,6 +5376,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkHi3Lgp_3Yj9wt4vgA1oSIa_JtCtj7RjGhbND5hT3yq3AY2CY9254AYshpiIazZ42rP6BeRMSm88asoQ3aNqgnJC-CFz7D2ycPcfyBVm03G4OkITFocSIG4weBMRm1FQwM--e0=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -5177,6 +5406,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmfK3ecwp1KBCUDxN6dCJqA70pgrH2NfKG7lsDomBMq7fInbPd3or2ybPemLytTq26yVayvp7CmSlXk-9Pj-gr8UOqF-WgSU6MZynG6s4R0t2iSq6XBBJGi9BxeCNDM-j1M8heSbsiWKP_N=w193-h92-k-no</t>
         </is>
       </c>
+      <c r="H165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -5206,6 +5436,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkbp8VEU4GVRT19DVy7rphHluzcXyM7blQAEsobdcdpggvupAmD5UOHyLSNV3x8RNxQ3EbJZz82tWu8lqULGRZKJfYTYtwv9asVOVp0u_llO_T3wojvqXBE3NXx6UANeR4hzXAwuXcbfJam=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -5235,6 +5466,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmV59HL7K3xWwnxQnRu1yMRwgw1Pp7guppkyZ0vM6uhCXMg1DK4v-QUf1Sqw74nHoki79qLZdPvAMnFY5cf1_i_jgpt8gq8bfLzS7lVZ7dRq9FTgo24B6CE7i6wj9HfvYi33dmUo_iVK07l=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -5264,6 +5496,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmjJipUmK6ZvnZg1l9WfKEpLp3iXi08B0RKTsMHTp43wY3cuT_JKc9RXPBHprfJ1Maug-lLxeYB4k38KDPZTZ5c6gRRQfD9xuaKST11cJsmrO5HbChDEKlo4HVpZXCCu9EDo9yniJ4zd7nx=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -5293,6 +5526,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlFKvu-TpV97nj0N4cmKZMQk0EmTPJ1ZvHUGOXnxK3-11VPXjJeexT_7rD4HmS9lv-rIXX94_xrO48LMlvTm2N1mulasQNy7OE8s6X7q_IHQFt-2eQYO67IstFdivepy8nVwf7PQhbrwFEI=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -5322,6 +5556,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWntgGk1DOhDxFjJQ7vnsTiDfbkmROiCpDMKnOx-dd5d3QOQBgg1klZTTJhPYsQhl40HLPfWEPZAuyPh9RzOZZEnpyVjSRdxdqTXlRUlolBgojEy5YcX2vVNkqZCY7MjRvbSieQNBuHavFg1=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -5351,6 +5586,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmtJGLhoXbA6lnL9LruHQySC55yVSGDQCeqXD-l8zCJTrrtf3aERoaNoutAm7i1qUP_Rw9LT1gIiraeu-wgvG0cGk3W7k7SmuakGwiZ8nD8PIGstpflpsf5kn-qCvhAknnt5C3X=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5380,6 +5616,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlVsNj5QDkjzHNbsPXWe_seVczmAf1g527WAgQKj4ZL_4k069T_4sj207bPH6MFeS0JYsNB_8hhwo4IG7zGiVIGF-pBNjY7ApB5OgOl67caOGQZ1uUY_OQqCf7PFzqzAApJkjSAh-S1LRc=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -5409,6 +5646,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk8g9XPieZ0rpJ2AF3CSBhvvpNea6AAADzjKNxkPykMQHg0BRTJdMIrzW54LxLzcCPJc1jbuLOBbnTH2a77cfjPiTVo_wE4cA8G6D-MgG5dwbcGkmhft8vaaV6B7nwmrGnfAYj7ZpEJqdw=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -5438,6 +5676,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnrA-AHwWR1yB1KcXKcQbJbENPEVkEI1jDS3YcXa1Jk4Q8KQl0YeeFEojK57RPkK6KHBLZdYMNm9InHBxbzQ1N-FtYbPkgC-B82DQyf_AXZT7SKPHEUBlVwkbx3O7SX7S_vfkr07g=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -5467,6 +5706,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnrwfhPJiwQ71bHgktbGYa2D1xugjx-0vtQEgX1YByNiByvY5HRkI6XjWsBtstPmWKWS2NHBIE3hlwani4Vgz3lmNdd6pJZBeBis7MZI7zPe0rmzVshWGwuaKD0-A29ThQwZnUJ=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -5496,6 +5736,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnz4wJoU_mmglk-ONZZhO7duc24Y09ZP9J7j-p4FWA9zQmmBtZZjdC2U-SrZchv61C6IB3dII_-s1Oezw6KH_wq6Gt4KejtZAXF2r69N0osmdAC3gKly0mquQivpc5Hz--pAWcjanKkPmU=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -5525,6 +5766,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkjxoZPrOdjXH3UAEEh4cgxpFP4qhsI6XgD9iAZJjI-WrOBNWm7RcSfDJ6cG4zyDFICdq3SkgVtXhr7cvqjUS4XTJbJYjBfrSvjurCRuUDo9IVcvxTqNYdQldgJlfbRYHR-mbPB=w150-h92-k-no</t>
         </is>
       </c>
+      <c r="H177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -5554,6 +5796,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkW8R9vY9vjKJa5XWqO7If7wmEZ6MJYpy9_2cU8cMag72hx5QyTRUsmZP-FK_P9WZPqIZzPbKjn8VItPLPRwFH8atId6Ocm8vrM_INK3EUbjeSBFE6Yg-vm1aEFFwPsgkymCto=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -5583,6 +5826,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnq-37-KgDL85yQ2uLvCejm80_jEvI2XwB0I7GIfuARfqVh_yLsD_qwtqtf9Ass9HuvXQFv_mbCP9ixfgXhqCMrXePaOC0Es3gozANSNSdo60vUzupLMxyMfaJMh0QSONVJcsKJ3WIXbNZ5=w92-h92-k-no</t>
         </is>
       </c>
+      <c r="H179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -5612,6 +5856,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk5ENBFxDLsWLMKESI_HIoUTaKkSc05BTNvHEpB_3VkI6KVlIMrGmJWg_7fWRz_arxH14frJhnFCd-_O7_XMbcDtN58smUuPVq5607cmy6Xb4blUPBld7qWWcj4jGGiMPErZxM=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>sushita-cafe.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -5641,6 +5890,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnwNvfM2DR0qgyLOetV_93L18yPO5xIgCk6jubKoAIculjWYvsjdPtEBRm5EKJsN6LqPHIzXGe2QN42o1mY0BOiCeWKGHM9U_GTsMgfFIP5M8mh5p3l-S8qbLYe5twK6NVtJ16G=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -5670,6 +5920,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn0qRcRlsyL7G5xhHwmVyC_Ad1UqTqO3tBN1DIOFRyQY4mEjaTAPURpQ7QQtKjm_vUDrs-lPx1eAZupEgxS5v565s9OjOZydnyc2Tu6CORsYi8cKum-9AClpx4mgcae9sHwPhp7fxnCTWs=w164-h92-k-no</t>
         </is>
       </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>dolce-positano-restaurante-italiano-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -5699,6 +5954,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmbSDqwcVZxzbKM-LMFn37HHrZeREVLAh9uM4D-koFz4oV5wT0963iBTsZNufEQ6s51CWbOPu8xDUzr2f7YMkxxkjkQPHBdk7e4ZFFieQ8OosaEvznzniG2oB5BFdI0E2Rl8OWjRg=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -5728,6 +5984,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlFcfuashghttHiMhwyh_U3NAdfCGjooYGrhcW2c1HgyurCXV4hFEMgL58I5ZFxeuk0KQt0jDYx-BP8mpHnX4Hvnq0wo9ypdrOAjiJ6pO_gJUHbAqV7negns120Zvk74148WWFD=w80-h142-k-no</t>
         </is>
       </c>
+      <c r="H184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -5757,6 +6014,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn4O9177RvgABSCVIwLj2g1V8XzwE-ijeSAuoMTBfDo2-i0HBhJOlS9yQOmSfrV9oXsPSYBn6qtlL6i5EdscaWaT4it_hsbmQLH_AK3yl7MvgmqaqQJrNLpZwO-xZNzHujsGlfs=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -5786,6 +6044,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnddzT4JoveyUvfvdol8QFAKYHfGyE1m_hwFgdsSWt_B8jYiSDsRCUt8INx1qcMrg6sVHCg87EA-zf_CyKXU9xoebMJ0KUhmEaQRDGzLc7Xx9hPtWgIFNvyLADm1bL2dcwFd3dDjIGZ_YQw=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -5815,6 +6074,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmq0f8OT2dUDgN0xbZ9GLda36tm4VGtygucuHxqAADAQwq1V2EqR02n9yrgfqyZQuGhRYTXAwmqmgzjmU_jqYPHmfzHNKdQgw-MCyAuctKIncFmotQOfjTVzth2WlW35_HKBZ4lcouiooX4=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>biri-biri.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -5844,6 +6108,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnPjDc5bh4LFSIEKpuv05Oh4WOJJZSkppR_6SbOMQyk4v75geNMLW01jXLGK2NkaHK9HCszashkO_E80ECXTQC1FnhQLxCmWc-YtkOFhmiu3B50RUUCyg81D1fmoiA-YSIzqPJU=w80-h142-k-no</t>
         </is>
       </c>
+      <c r="H188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -5873,6 +6138,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm6HgvQrzMvPYUdgdIV9YjCoKUPu7FHvOYLGvj3_sxhJplv2Y_jJcNurlf5nDpZT_qwuOY_yUp8H6MLZUOQZlyZyVVzqFOv3TgRoJinx-08h9g3vziZp4Ztqi-ZzZYatQ0HejzOxdNXoTY=w80-h94-k-no</t>
         </is>
       </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>tacos-real.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -5902,6 +6172,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlGaY0aM7AgZeYu0xagcYF8GesroW3sxZGXz1JXqTmXndps7FH0vSAXvBktPYtWzoFWOVeartR0DECK9dIC-TXLRQ_6yV0pVBoxLjMrWq8jROaJniiWVJ02_GZOJtuhbwLSFuL4pnOBQwqy=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -5931,6 +6202,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmqyiJa348exTrE5CDlfaOT1DN5dt2NKQFmnRs_grLR3Qrn5C5tKY2tnw8HQKJkQx3OSH_ICxUdbroSZSgxDHuBpmZ-MDhigorF9dtIy10A7TOv-CszWKfYcd18YhzeHoWJsIobewoJH5Ha=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>dum-dum-chamberi.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -5960,6 +6236,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk5ufatZmRUeksQFfy8hfSZSAJclBPfVZll6DCmHt8scoOrmnpc-oOfpcKkb1E6S3nwukJWE6IdY-GhrI2rezkOwOqA01K2j6dUv9bhiOYocICkA1H8isXl3vu66Q2kmBWsvTLP=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -5989,6 +6266,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkUwVPBYFVB6T-qaqtm9ewH1mqU4jc_ORURELD3-zdJWsyICMpYpArlhFk8kpWnMD1MSceo5fDPQzfxzafI9Cz-OCKKnzq80jQe7edOCeFGNVWehTXdRX3ZAmuZuuAtlYCpH3b9IDW4da4=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -6018,6 +6296,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk-uaQDG9sGGGLqhOTjREIou27tPtIePPXFmYia08XmgYhjSvDIitx5exq4q_oHtwvKv_7Q3bnR4y37tChFm2MsaJ1y4B7O6uSrgnq1qp3XdJ0CSZ0je98C1VsMWqjqzlyQ1SAg=w149-h92-k-no</t>
         </is>
       </c>
+      <c r="H194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -6043,6 +6322,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmX0luTULxC6m_L6d0I6vDuCNdPMpikMLmNtGb5TX0OCzSRycAkXyz5QPdeCVTkSFO96LgG6nDUnDSaKC1hs43V40zPLsQxC3e9OEXH-sNmnaNScZYT5BLzoqB3p8kqi51K2-HAnG-acMas=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -6072,6 +6352,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn1LvjVRJL4DMByI785R81wQTwxO8Jy6FTRYRtQRccJfS1dJg-Xp__SBoYAc5f23Q2Bj67SoNCsh7v-zJK8-9PItwccMz4DbzseTQoG3ly1_lKl636dJnO_NKFIcAb-cEBcn7qtQw=w105-h92-k-no</t>
         </is>
       </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>neotaberna-miguelin.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -6101,6 +6386,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkCNTPAsIFYNaoUbXO4qVdTUIJl6inFsN8kx3WddoQgAMQLnT0rXLuDH0SYsufUx4RTC-XUNdzxsHkGqSMaCyXl02Z_iblM_asrpFcYMqaei2fhWS6xbgUkR7k_ijfVL0xmdHUgNcXhsWc=w163-h92-k-no</t>
         </is>
       </c>
+      <c r="H197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -6130,6 +6416,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm-EVEk5BuAIf6AXhm3QeIyOeHvxnebpBg-1ruB5ejv13gTneDJ0mHUm3JIlUbN7aJNVKzyrl4bN_XYmF8M7MfBON5lUpOYru3LVUdVjDp3DiEznnpKuKOAWHKZYolFgMpBWN5nwD9tnwA=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -6159,6 +6446,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnzzwMFMDKcKtJoKJW1Ab-fyIVb2uUg2TWHIUmMBEeeaCXQ6EmUsU5afClFpCZGrFdX1onr9TJs2cP8HTjE69Zjw46WvDv1i2jfE9YCMks7xYRrq2JdoUXbnePBoJ9iqFQz90QrDA=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -6188,6 +6476,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm_l8AosF2tDF6Rd8f2rIGT5txcveozBmoIg_WBcJP3U99vAdS-F8gVO3La4ZJq4TbQr-lWOM4x4UKIPoMmcef5zRkP4TlTk2Af3_d6lrobAn2hZTGV-gPgPjotsDjdUTXCv0m7=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -6217,6 +6506,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkURIoTEUuVbhHpnGkhJ4EsTSFF_C6VpoiBwU4XeqwpkIz6wz-FQXUBu82mlj5dqfCd_Ui6jvKR4wM7M6tJmrfFkuO_xjpwEsle9slyvTlI6Jqk3izsze-bide09i3pClHarXVBqXl6Qpdq=w165-h92-k-no</t>
         </is>
       </c>
+      <c r="H201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -6246,6 +6536,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl9guvz3LePoJ4MX3MZbHlFP55To2KvStk8vIisEXH8a5SbdmkHKkH1mVsmNfTGtO2DjPhnNw3LYxFzmG7XpWW3Ioc2k1aEEfcxd4OOG129BK2fZpSegf1nPKMbtZnAMGYHNFU=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>ristorante-reginella.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -6275,6 +6570,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnQVFs7la_iFfYM96wyzWG-p6vqUkskS2voT2pSZR2yEvjZ9vgtlpyGdZMfSpmr9C4av1-sOMJcalAtB3KGXw7iBOgxQHMxLmj811W2bbvHqhCCsWx9Z99dYGBuVENhnbMN2gn5sQ=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -6304,6 +6600,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm7qtPRk8xp7Lx-x9yohOl3kRquZWunfshm8SAyAQO9pLvaxQSr_oU97nmH2Oyvo1rU7q3RX_G1FzuPMiEHvORInSXK4iKtTdskA39j-yZuvpCmKy8xocZNeR4cenr2TJoUZvH3HMiYHbkO=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>macas-goya.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -6333,6 +6634,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWma_sS1qvWDv80ytQwp5uf_fWl8iQwoBGJvNC4Hrx4XYAkA1bYb3I5-g6hLIiY5etQQnihXdAajiSkiWC4k8XJJLkHIgGr2EpkPmUyNj-NT3sGnPnDDMF2cKLlGPXkmjpumnG5OKzYt52Pg=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -6362,6 +6664,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWku-kWAWPypnALdXRyOOOkAaInj4aqB_6cIEi81JZKeXltPTalWsC0GsQDy8XpYOyDUyJzXFxODnj6OREKV7ZaxUF-062gt7xhPU5jyoApacFuE5Q0oCxw0_26bfroI0efwcJKDSuqwOdOS=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -6391,6 +6694,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmOFTKFMr8iyqEsQ3Lmptld7UFNi4jV64ev4cfA4Ugb_dtd51Ux_0kTy0YZe7LGp8d9mii2BYgAn7zl-3FWqjH1fP9tn0nangXmMd-mLUUHeADKIDXXtjJZdX8ZnuLQHUssQm2x1w=w80-h107-k-no</t>
         </is>
       </c>
+      <c r="H207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -6420,6 +6724,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnQ1NANrSZJxcFWL-uPUHiWchCc8cPoGlYTAB8VirVuldpkAqpO6I7z63xXX0HSgH6k1xJJFlKgk_1HJTt7nfFJd-2iHc5KdSMjBWrVDBrsHrAltUCjHLQWDT4eupUbJmNny_Kbgw=w80-h106-k-no</t>
         </is>
       </c>
+      <c r="H208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -6449,6 +6754,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWncEEJiMkwPNe176qLfrBwzoxQAai0gm7anSEVKOKjk0L8XgzCdFa17gTRswuu_T-lEXLzLuWO_4exJ5soNTG666KCQ_ivydO6-KWpuRe8P-tLFNBFhSZEm1OD7P7frJQCeq4jQ0A=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -6478,6 +6784,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmhKVCQ96vsGRXz4ZTca0kqEJUUM4e5O-XlAoa08fvobVqiMARLGkNGq2v2CxRYmiOHHZwEYwYZpLmZJuVlS4Mdr6YFn1fklLd0mP064w9tmisxbEfEidkxNtcOnjRogA-4RLOs=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -6507,6 +6814,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmje8PF2hqtOUeGQ580JpB_rrkTcx14yLuPtBnPg7QUJccwt7AFuodw-KnPovuUlkrTOpekt4nKw0Me1xF3XJpe6YpLzNIfz6a31Fmp336Zvly2zboNX-hc3doCWYv-Rrppz5tbag=w80-h142-k-no</t>
         </is>
       </c>
+      <c r="H211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -6536,6 +6844,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm6jdemr111CVr9aIMgVR0oMRY9EY75JvO9AP7O8R5PnE8E1FOlWM471fJeoIzQjAJPdwCXZgrvYLkMwrLbNC9awuKTyfbFLAc8iDkTOuE6hcb2kQUhpPoqBiFqmB7oSqiSLOIZ7j3GOqQ0=w122-h92-k-no</t>
         </is>
       </c>
+      <c r="H212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -6565,6 +6874,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlcAmVkL6_A26sL9OklMJkfyrQgZRJmNXXgN2OYe8vtfQfAlgUKrpxi6uHbwZE9TxMgR1YK1JdZ73Q-LJcRI44d0mBnXjWTOoU12_xOYa5rOUg3Oh7vkpSGqiorv7eXqEc26l8ajA=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -6594,6 +6904,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlvHpMEz1IRConmp0VxcyaH0t2C163h63peWWWETTZF2zIESdQ_oUqznKyttqKHJFJ28s_hMIK_LLDOXGnx9nL8gxPZbbqDpye7PsYJNQHoKMeVF8ISLcirGHRMo_d27k3OeF0QN-BWZQE=w80-h120-k-no</t>
         </is>
       </c>
+      <c r="H214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -6623,6 +6934,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnmwEdQKcsT54Kf2c7IQu6tWN-Tdbm9VR4O84crwlPCJBTEYchkQfoBVPzKnCBrr_ccz8YxfJBfPwZ7xyd9zzXOS-Lq-JpnbyAqIwFwaAYF2wBUAshJ1eVRURdM8saYisdQGkmh5qaoVI_s=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -6652,6 +6964,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm_mZL0uZd1Lp7JTY9K2gui-k_e7BMkA6Wf-zxYqLJsX81OHbkxneGASFCaoy6G0kpl-vOpxENdhM4yPCA77F3tcsdkCN99F7ZlMIdba-6uCAu_D2Pu6ZhjuJt2XS_ddEAMUM7_Rt7bS3EM=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -6681,6 +6994,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnWEgZ6yjzASlMSzIbZP633oC-zJYZzlB8f3bbz6qNY4jDB5YGqYtUPt1XzpvV7OLx-QS7me6-ZtTV_YirCvKEnztMWBwhGOPhruT012nYueKE-W3CDsOFgPQkoqkehD92_17MThw8axdNg=w80-h100-k-no</t>
         </is>
       </c>
+      <c r="H217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -6710,6 +7024,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm0z6_e2ir2rY95KB6aXmXZ2t80FUv0xophiD_jMduKeTtUu4cANv7PiPAuqiDssEm3QaITqj1oPiwvU-PBQTV5v1UswbCIgbsupecCEEoxUsttU45kbgnROPghW2TIt74XYDl0=w130-h92-k-no</t>
         </is>
       </c>
+      <c r="H218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -6739,6 +7054,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlIlCtKmXRf7qTlDHlT8-hc1qD7qVF9RB-hiJq4yyqzsnVm_MG63J4hxe3UPLSEWJ5PGrt2ZmujrTCGzT6hDAl7kmp3SzGhowvYn4dzY8v04gHIruVvlnoVeySGzpCpZop06BoqveDrftTP=w80-h100-k-no</t>
         </is>
       </c>
+      <c r="H219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -6768,6 +7084,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkCxiUFxRw3nm4JGLZXN5Ss6qdlBDdpNX-H85Bb-cFNh27AUGEjv-Q_TnmnHFCNQNpRZ2b3JuI4hToXvCv_ajNivlqcfqFxB05NpQBcZnKL0QYQnjSfZVXSe7goHjmcgwW54q4mjAmEJVk=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -6797,6 +7114,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlP3rIVHQnWMRBK0I5bZEcTEa4FrsgQcAThLNOrhF2LxcEoVKfU6i3uImhSvHCWPnGSFoQK5pM1RwaAepgIwfXLxOalmmpeUZM87sIPk-kvGrM9mI_isSs3NTlyCLGau9ODKb4jWNIH-lud=w80-h142-k-no</t>
         </is>
       </c>
+      <c r="H221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -6826,6 +7144,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnitVyBt9hS3r9P1DxseAE0E9xyXBET8xnviTXG1hDByPW94Bexf1MMKfBvADoDWTK8RyzXveOackQj3XoQbtFjyYYI0bGLwZiOKt8MfW3hsTpmEXw9IH0PdiBse7OCl8OCeCSgU0OFtfA=w123-h92-k-no</t>
         </is>
       </c>
+      <c r="H222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -6855,6 +7174,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlj65SS3CeymI9IK1WoDv0ldmp35xkmC1xT2dkCcUvupdqqW7metr3vCw0nsMQq4mCAO954XYsIAPHSM_L6muNDex9HJ6SRHtOZje7Q89T88E-mZM7HfWNGx7TsP5f9lCZyYBAucyCFp1S8=w80-h142-k-no</t>
         </is>
       </c>
+      <c r="H223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -6884,6 +7204,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkb0scJIp9D9tjVRCRzEkr1qN1aOD_hmk3g0SZhgbmk1gWtdO9wLPn100PcejbK8xZmB_YTvSAM9QNvGYpIkc8aQYdKdKxpEzKWtpK5gZl_ndWD_okp9m8Wn-_LxCQt4lBt91iY=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -6913,6 +7234,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWliggOLQTHpQ9w4rvdF6jCVdWVo6FvdxIjdEHyBKvrqyERLMeIWT_QiZefZH3Q1qQwJhqIIHl5hGVS3QFoxKriWNhV3pHYO_s4nUHnxq1ujPushtKRYpXsRdvf5_UVWAtt-FZ_X-A=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -6942,6 +7264,7 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlbyYjn7hBQBddUxxyin0rERnLvrGYuC6glmE37DKbq81vCYRSdKdu4Xp6990Gru6xpw7Ge5a55kVyC79XYpl3crKB-Tf4LVfU5mWyAVRq_1d4fQN46Fhs6oux41bU0jrxASQlpD_m7AT0Z=w137-h92-k-no</t>
         </is>
       </c>
+      <c r="H226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -6971,9 +7294,10 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkihOJUBSty1FjBbYUhyplG2HMKWQ3GHet4XDHPduR-aBQWS-q8eo5kmBVEPLpm4V9ZHZ3EG7ySeJnhCo5U7i3nFji0XaWwNpY7UHzE6UDAlChwRVeeH5CbreOyAbxAeY2XDiSb8g=w138-h92-k-no</t>
         </is>
       </c>
+      <c r="H227" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G227"/>
+  <autoFilter ref="A1:H227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/excels/restaurantes_v1.xlsx
+++ b/excels/restaurantes_v1.xlsx
@@ -512,7 +512,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlfB3M8j_kNFP5gTGGYpBgcbBjkWOFxx0pZ3QUn6iS_GzNcJPURnxWkzOL3zIPXgHXQcJQ6GK5R5K8S0Ti3EjF6IPv4vVZygeWUn51YAuia-eUH_KdoqkpyjfglUEsTr-_sE0F2faY4ztQn=w80-h142-k-no</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>gazteka-bernabeu.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -542,7 +546,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlX21tjDLll9is-08XKoxZPbpD8N5X1NMn2Dzpd0tfLhUsFpKDT0ChJ3avU1sERJZDoYzAhvsLdKwNH8uajhaJmfECPU8zl-O5U5DeQxxxwJURKzuPa4FbasWksi0XLrkkDdqa4=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>pez-japanese-grill-s-l.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -572,7 +580,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm8nHiEui8oHBOfsKkV4Jfn7xyLWOLVBI6keFZwlXTOCJ3ONddDSJ0n09zl7IejlQ9Rekgc5VydQpCbmHKS0dgu2o_kTqSe8efj1czT-Z9HAFHLb4m4vFRU6GrfJLQlvJHFhti1K1l5Hk7b=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>in-ristolab-chamberi-restaurante-italiano-y-carnes-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -602,7 +614,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmo1LHa7IR3NsOVhITuvhLfMAmrEYA5dFYbRVABFI3eCCesuQRF40RY265H5rvfdSM4hcURfPW14BukwpDb7jv_cZ5xzMMDQOUI2hI3dNI6le_mccExPRf5JbyLdbtC4AIyqj7Z=w80-h114-k-no</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>chiton.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -632,7 +648,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkHZbLj0zXSBHRKm-kPXZ5thFE_Wgg1JOxR5nmwwNCBbv6NCz55VTx0Kq9qN_iChEBCyMcU4JSvO7OcWJlxfJz2i4BZvdX7j80bgmO2DtVGzo2lDl5ZjSnibO62w6M0HVRb9NU=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>gladiatore-ristorante.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -696,7 +716,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkOrrxc_SubrM6An5P6b54TmxEfo5XWtp7SRcUC_t3SSPtE4zlmCfVP90ctXrAiGvmpxYknTIQV0rvv80hJmdG3So2znAg7ez4pQJ-mAGN40vSE5RIFhV6J_xEpIlqYlTu4XJhZDfFbdfpM=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>toro-burger-bistro-malasana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -726,7 +750,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWliQD6qcC66QiWNiLuVPsApQDMNDThZL9CEzd61CeqREYzP_XZZeJzYLHdEwY9GoibQxU4llFPeeXzxvrXBoGRxbQ33p57NlkFTA2eCO0dEpRCXwEw7Tu3WB6LGlDdA6JJB2t4bpY0I42Fo=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>san-fries.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -756,7 +784,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkNbqQgA82izjyqQ7T3jh5JF62Ng2hg-dEKNqNHnVXivL_S8eIMIp1KXZqpG9PMEpchRCzvY1fIkRz0S8x41UbMB-Ei0MTzAcfYdkLjwWB5e5vcFvauUNt_aoswNqS8Sc72bT_-_01Qn7kr=w80-h142-k-no</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>tender-club.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -786,7 +818,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlf4hIuCqeonBhL4_vnQQJo_Jgiq-7k7vzTWKaCzCDAjf7XnA3BsiWJR3MxLboWYuvAE11RU7lugXdr5VtMzM2VRCvlPxnEcOmsb0Og-UVMi5Vxcq41ofEXIsoZzEyLAVHnR2YG3Y_wfY6a=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>corchito-bar-de-vinos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -816,7 +852,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm-GAgKSx_6pGIvrY-fwQeAgTVD2p9sDx_GO2h6lSDi1jqdGQtsdY0purM6EXE4_2eb4hW9WI37Qna9UX_ID3yT_7aTmRnv6vopSL3duzGg69Za-eU6JXePvYdjcVF0Nt4n_oTofbs4neo=w80-h99-k-no</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>la-firma-tacos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -846,7 +886,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmj-Y0JkO1DAbEGhlGxwJGOwsRfc0FHBkYvNEJoldnZYUzJu6r9UaD6iV310ywwUO0bphYlR-hzGChNkI3ZZLE1sYtFfRkguMQ4aq6FXp5Dud7yPZNuQOtkKjCPBOWgLU6YilbUyxVUb7EK=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>qiqihary-sushi-chueca-korean-bbq.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -876,7 +920,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnEr8EAJge9c1ZdTjKKMfPZRwValWIgMc7i4zYu_l8lT_3mVl_OORqlEA6Xqkp34yAThqRQ1uez_HNBqG2Qy-m6-pvskFQYJEbweya6RUaIQNIdTs_v3ZO2Bnc6IM8oYVNzyobwpg=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>la-notaria-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -902,7 +950,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl3oebDfIzvKtgFU0MAh3HaOxZM7yYC5GSdVGqIbbXN_5Coj8DDm86M7_btOMbxZIi9Z4FzPog7GKa1Wgi9PMWata04BPesFdhlo5if8MMj8patB2dn3mVZB_nTEPfUK3TKVwjU0CRkhkE=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>carupanadas-espana-chueca.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -962,7 +1014,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl4FpKh7AICaKjIUFMj5tBqb1sfmMDZbMqkA1_0UkfTS-X4ooPPGzyPkJwz2dI7FXi4EWfm_5CMyK0Wnan7PZK8BplVMjkwR7VFWr1-cRkR26PNfNafHbE79CT2HBpWCf14_eJk1G3QULmu=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>dabaobao.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -992,7 +1048,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkd_BuP-WkpM8ScXE57Z3RD5URopXudPGw_c0LmaRSWn3fX_QH65dPK9r2V5vmJsYuFGX1fYzdC59LEsbbl7wcPZtznjIGh62uewrXTIIL7Ac4uhQ0PlQiQbRieQsaLuN_V0h4Db-FKfEUn=w129-h92-k-no</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>my-pasta-my-art.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1022,7 +1082,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn5ah8Haqruhu7ysJOzmAwIvA45ZRrkc9qAEb9Oc9_q1S22CW8jngrohf_aCg0AN90gLWXYD-pxxYk8-NL78nzfPFis5RWvQg02-uMWmujU4eqoyyFkj2paFRkeT7uR0KcFP_miluF8uTH9=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>roost-chicken-barrio-de-salamanca.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1052,7 +1116,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkisWZP9CAgvBBI6lOTokvsuc8iWJDx63mHdwNrqUHTVN-9HBxas17haCkcO_LQ5ku_c2ExK8i4lDkKhNvo_JpnJeWdkHuAJzSRARXaOCSKhnuHy0paoxmMH1Qo4Yn-JklFehenVwNbC38=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>nube-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1082,7 +1150,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkHhkXY3Oi7dQSd8mLL4_-qT1otCREc89WUbTgVuS612Uxc3oqqafEOtO-cuciXu_rfL3fIjPMdeh60f8tAmyRfZaGWrJ6w5lB4YJGlDohm_ntRPY9pHrAmrppu0iVxCpA6mNWoIdZmZVix=w92-h92-k-no</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>little-dragon-plaza-de-espana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1112,7 +1184,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmdi2Giy1td-Ot-2bvUB0oe_qplDSOO2i8LYumqRmc6MmsK4TbJic0HlqPnZMZndGkSZbPYTpYpUslfkSbh6MQDNlCCyMWwrza8JvfGe-COtQ_V-RqOixp60oidonc5iYy5g2o=w91-h92-k-no</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-varra.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1142,7 +1218,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlBNQiEpQlt2pVKyUPnVJ0teuErK93bS6ZERJyyshiG6iP7pWEz8rdnQlv1lLVR2DbwfKE8QvM8ghYZVZjLtpGsXnjrcRG9GMkyaHEi6JfJmDGOvtutFVjUPMYw8ZeIH12ihTx_=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>taberna-nonnetta-general-castanos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1172,7 +1252,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnRawVHcm_5aYV4jrJjVI3UiYbPscHl5pM18x1Rg4MQOaP5CN7rPGmhusGjgXyKd1OqAFt_KAtGpp9qnYyyV6lV_s-koe1beWeWDBMDi4fe05bz2dUblxYTKBfVKH6Es5z3rXrVcrAm_rsU=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>toom-deli-libanes.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1202,7 +1286,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkY6ExIlVNRxE0TDdrqrMOWLsToGzc5mhcRTmmo3QspzN3EPG-s_kJ0HWY2eyVSgs_87TrsAl8ac4OqVtSS0NiUn7TynDRdUKDhe_n4J_tIABDHXGSu0DQ7cGFFjmH09AfZIHl2=w85-h92-k-no</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>ni-fu-ni-fa.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1232,7 +1320,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnUvsYEH822UCNYMQvmkn905JyHWteB7RsSe_NGFSiP9NogTE9o-GviLIW7_6heq2To9F9u923j5BPMr--Mq3zj46kMndu7_m3J4an3ycnhHds176amLPytTfiWTVUd4SSwmqU=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>cocteleria-salmon-guru.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1296,7 +1388,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmk0Q8gbhK4XLGSZN_Yp84gjq2DZ_NFkPyri-F5bEnm_6AwkY-H-9MYuPVsqKINK699KdeZ4ZzBi3QNxqtoXsOjqh55bAmx5jlFlVm7LKaCOS89r36sjRZiBkfjA8Nz_lAvbAx2sOicOg7h=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>marciano.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1326,7 +1422,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlm4XzuGcMPUq9gLRi1gxetjbKPopFw60973p-9d0H6M0Dj-ngEARyHVZOEvIVuVIZpMmxbCI900J77QEQjKsDhqULVbHlU0KcwqJJuTivoPuAajzkUNoqcp3AkoqFn6OAtmbU_Lc0SSuA=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>rambutan-thai-canteen.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1356,7 +1456,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnCw7pu_OO8x8TLqZDrsACWkPzAdUAFedVcNt8ubt5tL-iXDhPLNlj-W76mC03rqVFIE52FrxqvKbV1vgABapITRjF-iAXcp42fl1Aqh8NzzgKVyjGvrQTFhV3IA4eD2kaS-QZW=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>donzoko.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1420,7 +1524,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkhYfQYp_VGbC4cI_8i1cVUZ6QduuNLujWYfiokTaou7wFSEUErtuZB4I77uzUmEG0FtPNdWonbC2zsrbxqCjKDR4MYZVz9f0zFoqvIZNAo9jdTJFKrExA3yyHF-HYAdTN4cvV4ozx_3wE=w80-h100-k-no</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>em-sherif-restaurante-libanes-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1480,7 +1588,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmCPLJADlJX_M1DyFdcpBfzhnu-ug8dXSJR0etbZJ0Ot4XarBBU0z7fKBkfZH6lpx9GAHHUpVqhVWzb97hpyTc-XGvlbBHOiYSlq5cqDha-SlY3vdRHp0VY-VH7RcAx2v2l1MuW0y-bgHLZ=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>santo-dippeo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1510,7 +1622,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmUOp8ST-KCzvMCboPkZnPCdLtK-7N2bpGzwfYo37W2ZIXV-f2fazSnJoyAauBpvkz7ucY8s3P_R8Ui0E5N9iUPiHr5IC-1n7V6KObIqb3bTcCgHMWfUe5Z_eIEJaDSViLCJCP5=w145-h92-k-no</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>concabeza-taberna.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1540,7 +1656,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk27Y7Vpu3S54ik9krMdvdkA8oF3ovWDKoU1n7p80_2-qSK2Id-WKyQGvSLvUYOnTMJm9wB3EM862oVmHcfnKJHg2tC71d-9mLEol3LgO3OoErTEWenSOp92PR8FySfFRfFrK-A9xMHI3lw=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>taberna-griega.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1570,7 +1690,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmxglAiKV-9DR4uYKUWuu4_9TJ3-rRImBmIfV8fI0abPnv03EpeevrZldJH3h-GA2wBCK3DWBFNQtXbNH-jykwLf48hFud7AOStLGhRCr1PceXvVXIXAObwys34eSQJRUL3TNUavx9oKqQu=w80-h99-k-no</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>fu-canteen.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1600,7 +1724,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmjNTtqWfeSvvaHQF_tTYm1zaxYNl5r6lrcRKPwMuB6S_Be4IpA_gWJ1htpyrmXdHHuyhzYY0UbiBK1wCUtVuKOXOlqrNtviJwCMFGWIcWWqtLBDRVL7G2Wxhj5llqyZHbSakas=w164-h92-k-no</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>treze-restaurante-bar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1630,7 +1758,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk1ZKvqvv2h_sEVE_CWGc_wD-mbLAJRYB7Yq30_1YVt1NwR2vrwtrhfvmycjDh3f_XZulW6cgYUrBa3rlpMjeVIiZerTOzQMinTB1Ora2UACeNngJ6RWgeQFvHS-phRuAxHgInC1XS9kPMo=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>taberna-tempranillo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1660,7 +1792,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk9QvvPBvPsUGBJQ3HBa7zqrfzJX7s7Gz-A2DSO-9wRJiMqbPqkWGXc3YQLRm9-o_se2OdxUeobAV6OfbLoI-cJoLAbLX4I1WuZmBjRfRLbFb2ZaI8nRqQfseeM62tJSMwACMXywlmn38VS=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>origine-by-salvatore-romano-restaurante-italiano-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1690,7 +1826,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlLr7nE9Jsc3FHBP9-Ntg5JbHH_6NPBy6DMHMblF8m0R0CkI2G311Q84FKPFvsGcA0GMv2FmRUg6hDBm8G-n5VdnFIi9oNcW6ljr1q_9zy9586n1m0u-s40X_14IBQPo7zeKP4CnpX06v8=w98-h92-k-no</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>focacciamo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1720,7 +1860,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlWcnKG-qIpU01KKny__xDUXCmG077WP525QDx4XLOygo7mtDgbKyVw-fLUZ0_yig4CDiObc1WLYg5E0xaIAeypfO5xlNIQMQxsljwyJBsKM_bnaWbKxfD1UiED5HUeUYj4jE4tew=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>pizzeria-napolitana-rifugio.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1750,7 +1894,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlV3j5B8mFPlxcDsVlHDyFEb0vjKso2C2MGbpP3eIxOprzfS99gh6QqDZaMHpO61wGcGmDoWMVpJrGORje5Uj4oAcWq9gC6dsiWhSrWVcjesYvPCxCxVpcSh5DM779y9c8TffMDa3mkUZVc=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>king-sushi.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1780,7 +1928,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlTNvdXadSkJ_d4XyV-qQGCLO5DgnvIeLIWaH3S-Ha4jrLJzGg1N_qn_yoImBqEU2LL1LULv-kasUo9vqrYpNEhg5e_Jrv_9KK6GgR7AzH97s01-X_9BvjBf54lN04nemKlLGqYGgy3cksL=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>paipai.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1810,7 +1962,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlOVj-9SFQH7dd0UMPSeEkH9TvOzYYKg_5uFm8MEACAQikToPp4xVJsHZ46LCWymiwNcV2yJ3eTvFUEXYxzIBBg8KPbrdh3heSAbSNk1oOhavq2PpnkSznLTFl8_Xs5k-dVk1GEr6H7cVc_=w80-h119-k-no</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>bar-serranito.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1840,7 +1996,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlKHTaJRabiMzSQEPClvsuS5-Hlvd2MrqL7wb5lx_ovoXFXYsD7Cpp3OkLbDNEg0qvHn2oAReAfli_ZvG7xKczkFxmUV4Vflblcrl3t346oVz4NtcVdxuH6VCAHAqDRD-KO2_xNnY4BZ7oM=w92-h92-k-no</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>terrys-bar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1870,7 +2030,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlE7osT86fCOxIqk_sa3L8_4T4hI1fVgJmvCzrnV-5ZhfP7s2au62CxgDXkUOAWqn2iTjXvFc0ybOJ3S2VbOuexJyUEr_AOI-RD40RToFYOgyoTdaukY_wReBiVnVTMzaKKxI8Bkg=w80-h111-k-no</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>askuabarra.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1900,7 +2064,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWme_a8-dIKs_E823qJQlmIusGwdnOSktBCRyAaXPNk7l0eXaT5rFJHafDJ44nVyZxGwIBtQYhjFo4izvBlG57nQR9mvm_5qtabM0gJJklkKXk18Iv7_3AmOL2HJnQZMKoz6JpTniJnuuRnE=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>sushi-tairyo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1930,7 +2098,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmp0Dq5wwAAqP047Sa9lbRQGMhMlFF6PoKOX-MthEAp2ElqzNzcDJ8BGTWU8yyCPCGgkyhc7zOpUaGXj62aHET7RevUBJsdgGN5WPazJvIIUANcQ7UP7w7MNDc4TknZD5lIcBI=w80-h166-k-no</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>claxon-majadahonda.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1960,7 +2132,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlqvuWyMY1fNty2AxogW9ubwCTp2R-Bl5Yt4d_JDDbZ37uERgnXING_F7off_8Wchse5FF6-_j51sEGpQuPsVtX4ZXkvj12RBgTqAsnTDCqD3TqZz4QVHy-zM_F07dkJBF3mI480yLV3rMq=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>hundred.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1990,7 +2166,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm2Aef8Ar-B0N9kVoZfRtMeKdkfSU1Rv2E0pXEIaRAQVcJT_y5paz6OHZWCn3idoxB3S-H3r6i7DS74CmL3OkR46yj_EAdNxo98UWq1XQfqd2y6VHk2D2TpwG7FJcg0A8JkrNlS=w80-h105-k-no</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-el-ochenta.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2020,7 +2200,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnNFE3zupO5sonInSOkuDnY4rJcTU-kLvcYWWKwHjAdtDXAK-Be4FTIM4XPOXKpYxcCK5TnUp-09E3vvVanTUWBayeQKC4rgyGLV5x2K6hkQy6TOh2MIr4Pkfp9auhGSMD0x55902YnzwgF=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>el-viejo-fogon.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2084,7 +2268,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkAocObmo0dPpYGdkGASwS0WpZpXDCvhcih7kmsPugAUzK_GeHebA6cqMPIfhtzu2Yz-ddL8ON2A3gUKpf7Q4Otkx90BLWamVflVXBUbnqyWjMYkJFKXnQ0hKpK6x-TCeZnmwJB=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>toque-restaurante.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2114,7 +2302,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmSdvYFozmJneo7atba5yrADFNNeMOzSE-0hCt0l6zwPMuKF0JebI8nyX_kgLrvXwMRMB5hYe5bvI7LL3UP5Q7KBJvKGehgG0Rd7d2ULieoTw4XJOX-1vKSxJLmSsaWqqKzAk8e5A=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>anonymo-restaurante.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2144,7 +2336,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkRged6vZfwV8acmz5sANZsjQdrWwTfOUC9tptiypFYrkKekmFuTjnlyZRN7AzQ51sUCrxPiqeob5_aNjSu4ikxKVd6E1tIJ-mT5b-o3-KQdOstxRKlnFo-mm835Okp-JrdhKF8rhFvFak=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>caino-wine-bar-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2174,7 +2370,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnLU5fDW4gCa7K3ogMe5_YUS68pQxnKLDfdZ1X7KjlTaDJN4jf1Aum4bvpDO2mE7i-qRCLRPdvOS9CXdULy1_zp-8RiP1RS0WCdu23dCtmQbSQaHjpBuVCsV2pjg08b-NXA7B-k5iD9Ehm-=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>manifesto-13.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2204,7 +2404,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlP49Dp3D7ZPPtDQRyL1xpQayqhOLcQXpvfckXy-o8PTKi6XEbqpafQm5pLU68ClytxsiyDDyjNzzi_40C03pygKqEaDyVUXEuRM-XO7rdfQwgP4dOCZWww64mXlI6a5CDVi50cKROQHLcP=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>boom-boom-ciao.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2234,7 +2438,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlwVBMO-Yg4m23n5QU27_ywwLv6MjbnwpdAavuS2alv_NbMlC_LWP-GOQkvSsXN4i6ac88fhm_SrF41n1zCDcew8ppzVjf3gRuDB7CBm8yDBF2qfmFziMES5hA4udUWxos5z-QxMbWHQ8k=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-her.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2260,7 +2468,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnRrCwFHzIvMehS2tzHDOyc_Vk1Lh_BVlxUKTinG8qViomg8HoiHRCrz0J9lJ4n-MTOCjeYnzLby4_rETR99WtIOzhG01Tc39fRfS5Lgl4E1sce6-vQfKFQBFYqIr1BTpD7dnuwag=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>camping-osuna.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2290,7 +2502,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnFRqNqk-V0i1f_YJ631kNUUilPJliAiqPNV5YCo2fKdpb6o-hEHiq1u55pY5f_6zz7gi0c3SQmkrlhKh3ZgreMGXWtvY_jkRhJjhz6oghv_4E-pooUYGauMCkrfWFFa7k-hfSw=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>bella-napoli.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2320,7 +2536,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnlsMGELEWE9aKdFfKyu7TBeCCW8L482KqEyQVWeMb14jy_vNqEiIsi_8aaqP16NvIbqnim-Fod2BEZYQWhxjcYt067vNUR6UM6BJW_E202vG_USQ8fBP-QwDIQswU5_dpwEKJPaSeaJ9Ek=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>baoyilong.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2350,7 +2570,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm7z2Nyg2ftwfln3bBZdLnbdS9X-pdxvp9_vMWjzBk6D5csgDaRjSKiXMUsYsT74KmBE6T54VVUE0GCmcuQQwtrr3JZbk8IzSQ8-8Ez6yO08qZXGAHxpls7lnVWKzWa9hk9usYrDj-J0Emx=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>street-food-burger-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2380,7 +2604,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkRg_1Y8J9uHKodHJfBShMqAP3GgTDFrbXYPUv_608i--0asMtC8sPFuA12q6uDOVK1c4c_i1NKMHQNYDqS7gvVS4w-dD9LuMw4jnMozUPPeK1AwbOiJfWQxdRt7cJIKvzAPb2Qlbkcouv2=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>bar-gyoza-go.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2410,7 +2638,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlTZGf4ze9lFibD27PYW_a1mC20CfzFkCs3J_tV2NJ2Y-6ivi5Uugj7-avuI463g_cZWe_h_IVHYjkl-QercEs-uojCHJisNBQpv2OHYPmMbR6gUt-FaiVh6w7KzYxAQ3ut7oKXcWgiZv4=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>grab-sandwiches.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2440,7 +2672,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkByzZcBkqqx3Az2VQwQVP1nCeAjkNHtBMZs54G9kPnIENtQHq2OjJDRD4Intr3NK-8UfbMGMJaw03Qvy44HuyM930ByTgtSc-JCu6SNQpN3Mx8ShXfSvuG4mdIWAyCuUqOmphR=w80-h99-k-no</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>mami-tacos-taqueria-malasana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2470,7 +2706,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkZx2O3GuBREi0Jzfprb6lFJ8h1iZq3Fmgbf0npBv3jp7tq6u1H3IgiSHCAfwDMz23XCb_lA0ueYGWfm4lVN6a5FjeIsEPzH1WHXt9ZnEmrCryYqZkBSlvJrxm8ot5nmcJHjreTgyQXheqn=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>baovan-house-of-specialty-baos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2496,7 +2736,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnwbJiPMNL5ptMl6iCjm1WJY_B3ZXGEMD5HHvhWjkoctcIIo6OLWdHhvRXmpvLRpSEKhdHgz3d-1p54X9gW2VuLv0teF1-68DZAwGQaqgqu5PkooPWx3x_PxajLT28vrO0t1zO-EIKE2VzP=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>diurno-restaurante-bar-chueca.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2526,7 +2770,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk1MCs04BjRmBatN7S3P1K2KH1vV6TJkWrQx_H1Oy0egqYJfVsiu4SB8nbRQYt3oz3CRHbCLX-fIAWe_Gz_kkFBXbl1xeaOfhiB9RDGn8GS_OZBNF9xpQDHl3bCMfren1xiADI=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>manekita-bar-y-restaurante.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2556,7 +2804,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXX9WVrg23tR2HOaoYtdoT4KhmAhUln4Wirmkid4JvAhgU4edss4bjhmZZYGRkGLsz8KuyeA6u21QoHXtwjQ6Tp76LdbL0NJF-pOwSmqKm36c8DS70vs7QGL-y6FLZwtA9VJvoCp-qjhfZ=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>mandrake-greek-street-food.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2586,7 +2838,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWluryhDJy3uag9kVnydbCSP6OLuMlyI8B3fgT6hbGL-sHwuxRnjV9kYhVm84PHr4xP03vpzWBc3MMZAQWBVrlesdRAg8UmycjDiXpujYkXxXPEMpMbQtWmyMC5sOWtdSC6wA99_oydsg9Q=w80-h94-k-no</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>ficus-bar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2616,7 +2872,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkeUkUNQ8GOKA_4astHDIGV_76be9F_o8YHuwPruINSk8GKRAG33w3VBm8myrEdtmMfu87fnR3sow1_BABNThxGEB6md-fPRTrCrjxJ7fH6Eo_wtdMKSU755LfVG_0Vr94eOY8fqst_Ccpf=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>snake-bar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2642,7 +2902,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWne6x56TKstVCstw_ByiI2TQWAwIVVqO4Rr0OjpEdYLNcJpGNINdvgVkBszRVQGnvSPeQnHj6qqN5M0-le7DbHtGH4LcOeR97axShRzyJP-g6XzxS2Q1qUc5rFPrGtC1s6RTQkGCg=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>dolores-y-lola.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2672,7 +2936,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk7X5chstch91wBI--xlpKSXSzlxlWnkqSCo2tZVVtEmdvPn7W8PRszSBVT_b19QBwudDAf5-HSMHkTRS33E6XQfRBZNmGX9bVJsu6X3D_darGFQ2K_UkzLjianE7IRf9yEpt_xt5ZAjTCa=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>tribeca-bistro.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2702,7 +2970,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkQ7yja7pMzZdaXzfR5TLNrD_TXh0_YaBksjJIv2na_7OIyO7TdbEf_d4gAEUkGi7USLAv5Rua2OArYWAkC_7TFpVGEDYjOGkH6G8wcK4de--rn7Q3W8dBm4opd0Z4UrErSD5mPlQ=w147-h92-k-no</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-la-monteria.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2728,7 +3000,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl6gGRZ4Q_HqxG7DzPCN2iwClmZWaEf982DoUNPNHE0NZufcYioYmLTPmWzeIo6_rEV6jv2buotUQV-KGRJ2PHmAxlgcntcOjb7u8uQ7CUHrYmcIb8_CMeYKoj8YUblGGfpyZXTpwTiGywb=w80-h119-k-no</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>pilla-tortilla-fuencarral-tortilla-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2758,7 +3034,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlYkceBYRmvLkpw-OQEfiHKNL4DZOFf5jaKHCSlKN4lAb7c-ns2ZU5jhzrWYr69Z23FVLv1QTW_vTPqscDiuT7CK7IFb-EfSLJYLMUXkOL9Yl5WIkYOnXT9oWKmpKZwDwAJ4hoq0Ozi8BWK=w80-h142-k-no</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>pathio-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2788,7 +3068,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnpVIWuWwKIHYtTB3Fxrel9kqEFmlHKuA2z6zzi0vOINyGt4nfz_4wxZsianr4t1Y3-Gw0s_AAE4dz-sVLOrh0CFlOi-3dHiLDzx3TGo0eaXtHgojHBTu7ZU3mHKrvS__YrXLaUULqaKKnO=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>cana-by-canitas.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2818,7 +3102,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnBpmfD0obqQbX1d95kC_ftkMkw2i0UMG1lC8VCxNoSC7ASU02aAjYqrRhB3R1dtaxRmRu35U0NnR1K4bjhHGxoUAiXC1alQ3MJ7f77zuNAKfzW_QNsbcMYROTxEjGOg7Ccs3BZvg=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>dona-tecla.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2848,7 +3136,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnd4QsAyRx_uygDe09jD26j9tw1zp8R3JFGuaCAcik8JH33mvf63s7kEuMi5jznAul0qY4D-krSMFeD_5222kAo2Lus5zz4lTq-gYYc5Hznj9pShlV0dSHP4Q0xFE2XX3BR8O31ceTFPLbP=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>marlons.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2912,7 +3204,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkYHgPD62RgZ3-FHB1TfmgsPnoLNNkVY6JjeW5l95jwnjt9oWetMzWP5ySLoNJfVIuyDJScZq2xj8QTb7VtO4STVyNFBFcy83nNkswyaK7QveYlbJY7TbS-tkf41o-vGHteP5HJ4dJMVav-=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>onda-hamburgueseria.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2938,7 +3234,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkGiHY8YHizzi_7SOJaerANYeRcl6zXaUnVrAq-lxXixWqWPp8CWhotu8jTzkE_AiJHdsT9ssDwieJ2T5UTbk6-JfJ8aJ6AbyKjspvjX_bJpDMtsla7tQVavkOi4HuthsrTaNqkpJC4dRpN=w80-h99-k-no</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>bao-bap.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2968,7 +3268,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn3tJ0QUoXcaVXonUfD8FlMLadBgREUo000OTS9Gs9ffsWd_yFSn7eAcjkKsTeRlQVC556JKMRq0tlJdN0o0VDetJ_1fhPkjKv4-nGQm9CRgUeQj7TYIryo__jPcgYnpVGahUupd1EqKZ0=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>malamente.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2998,7 +3302,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnZXGBaxdSBAh0JMtnNxnsnJJ4ixV9X1Tcse_pO-et5dLvEEATYMuoCVd9yVDP3Tm0uTg11K218Na31GWacmxep3a0bYM-d3Ee_bzQxsBFB7MWby338s4R8S9Gt044rcJhl015wNaq5MViv=w80-h95-k-no</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>paladar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3062,7 +3370,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmc5q5XyXScMicTiG65jBmAd7w9-PNhZSMTUKz85XUSqQow0gmOHytpD0jIYMPBbUOXk5A_75jZ85s0TnAa26wHBqNe0ECGP_WPS6KMmJx91nBHs6IsGA6DibiMPjJVU0QUXJ5ZQg=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>sushita-cabana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3092,7 +3404,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk6HqgyKQNNmkJE81N-7eqJKeNQAsoXpHTG9iogadUTtXPmTOSt_oQPmuDyk89eNFTaQEVIWJ2i_0_yYvJElbgtACa_-JQXTaxDO3XtqmLrIRFqdSz6ThJkLN1NXmywaqQPt_zqdk173SI=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>ragu-trattoria-la-pecora-nera.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3122,7 +3438,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl1ZX8_sLzr4ujdF4aoCy6eKyVnBRrjyoHgXbLHlKDLWhwbJPIYZxSFMGPVGWEJqPS212ZyJjeSV_RzJimhsuC3Yeey6yZzup6qjhalBGRLiNvvXyRzP5o0d5wG6TwrKaqO-VwU=w92-h92-k-no</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>taberna-la-tienta.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3152,7 +3472,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnMsCMniTc9nGfipGCfb21xx49nDQ7X1Pv_eoWAp-R4H-ZnptimbYw-Awr3mWG9qbcWH_Lo_EKQ6pYYu0qCegkm8B9NnTNofnnPUEQABuN2zeVpOuoT2YN3sDTjj4T0R58PY5wV9qj95QEY=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>meatpacking.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3182,7 +3506,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkf92i4dY2xt4t8yI42Cq5EAFEX106O9az7gaAyaqJawYYJjSEYaxkHVlZb-kbsBysfSDp65jC_LAmeO4NOueqPOR5YTpeZeWs_vMOvY8rSVMM7vinSgc2ZC2hcNAdzPBLmO53i=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>d-o-majadahonda.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3212,7 +3540,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn6OnnyMfyQgZOEHsXCM0xS3-w-emmUE1gIf-MOKe78JKyc6wae5uhQMdz67XCY4yXnDYAQlv6A_HSe2c83HpsmU-P5qy21tgp1yE7vEalNCqE2ePo_MaHDEUtPJbe8zh_yQhNHhPSbSpA=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>miyuki-sushi-majadahonda.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3238,7 +3570,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlDQV4PW5fFUC5i_yG0RpD5eFE-BbqNKpIqoUOm6mbkiClICJVQSU1vzfyotfokwp7CJO8WQArVHKNUN6vsRDgxACoBg_09pb3zhejyduhDLN-_VTms8MxO0HEBZrCuCoeUShN1X-gYMms=w125-h92-k-no</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>blt-barra-libre-tapas.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3268,7 +3604,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXlXmfzPrlkZsM6OvWHVYL0waAlxSDP4S7IIswFaJ2ZJDRJoGilEqQ0NAtgLK5nZ8eWCCkUVlvPTERuGpbw1_HIWwY2ODs4rYEVdE-Tg_Nvkj5LEmRcyNoN-4u1I0eHJZtaEWssA=w103-h92-k-no</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>central-mexicana-majadahonda.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3298,7 +3638,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkesAiRT4uZ6y8dt-X7O5XVzVOk2afWDLOI3IcLsysTk2BxV4mzqrfdXihYrNSYwPQjlRHES_Kf5K76LGD8PYJDFscflH06sssj-YUyW0ddiNJX9oOYbwxUieLxMW1mFMiTcNYD=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-namaste-nepal.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3328,7 +3672,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkcWyBTAZ2AX-3ccqQKLCtcREvg676x9BCuyTWt-wkijEW5ubvE-rN554478fn3BHZ2n27pbUtgQh6_9vGfEqSMP1lbnsrhmVj_HQ1AJEBLXuYzOQShvYr-0GNr3ehsgEzTvsJhDJbjPBbg=w80-h92-k-no</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>kritikos-cocina-griega-tradicional.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3358,7 +3706,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlsl03Te7Sk-u0DkXNkL64ETogrnrMySf7Oh9pTaJr98AwswD_Hk6TNHpMjFgKK-iFgq2V7jUK_L0INUCRzCzq4zl0aaYK4rnBFGt3dy0mNb_I_bI9CxLZisbNSrZTUajRufRUd=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>nomo-braganza.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3388,7 +3740,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmbj7R3-1Sm5SKjTnqCNnaupOylxcah3OjTuXCI8eBU907aAYJaD48GVu3IPcuzGicbwTGgH7o5pgWUOwx3VK8f27gAl5EO5mhY5-RtP8haFzlMza51lqOlABOehSS7ElxQldRdOzbfhlU=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>katsu-malasana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3418,7 +3774,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkju1XMUINev2-NRf6_cw-Z4BjilNtDpFSuHKagxWZsUO0G8eX_IHM4ZtJeFaE6lZIaZng8rcRPBN_r-WZmAfKOnv7HnT2rdBGPHsMFrxQbLU-FblS3qBqQTfE540W70rScuymuXg=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>katoyaki-japon-malasana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3444,7 +3804,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkBhhYq9wR2g8tuWuHdk4doZ63_BCSMeBjQBQhEB1fV-e-ttgoz4MX9IEpGfq6Xn8s5OkbCf9yPxC6kBMQh-VA1ZTU4HmYBoqvYrj2gDIWjFeBptH4mSLsqAtr3xXyUPYgyEfZIrjiF1v2k=w92-h92-k-no</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>99-cheesecake-malasana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3474,7 +3838,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkw8djyYh-crq1sl1tVKbEFZ3GjkqHZcfaW397KQFiF7A-4PI4phmLrz5Hbf3NkqsnSJwdeUel4b9NpBsCGqmbdNNC9JnUMoJgMMu0-MlXjZbFbubeK89Koqfi10Mhi421ciHet=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>chun-li-dumplings-gran-via.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3504,7 +3872,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnzSUZWV3XogcaNmm3ZU40lbF8K9XYGxmLB7Ltn2gQ27AteDrYOdRNsXjDu5ClCdo0AIQTsqh9xVWVWgvRNySLZEP0mTHehDLJfwT5JmOIf_nXTi8m9wNcb7s8FQyLlYSrw2G5rtg=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>mune-pelayo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3534,7 +3906,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmV3N_CIfc2NMm3zBQ-icE6L1D6hfUWk5Wxj3jg8_c1LE93EhJC_guPgtKlv9Dx-cEhy-27MHbA0ZPPuOi5RQvcXPvH7xM5Yuz6-2et_d0N6u5Y6ZXBApNMu2Vq9xTtFEaG1gBBE8Uy1Xg=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>la-bientirada-santa-engracia.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3598,7 +3974,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnVIgjeG59XiLCzCIursWh9B8es4Eevrmt9I3SyC9Xmc9HFRTNyShuujzf8adYE84a4c7hAMAAOYoPbH9FQ8mszDiaAcj-x08a4oU65Ah9VfNcca8Udcg36pgawXFeFOBkoopopog=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>udon-gran-plaza-2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3628,7 +4008,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmCuts-mY7GW4PXpSZCnq2sAiyEmttQYj7OkHtBIoBfj4J8-fPPPaHPqsBOlaG6zHsKuLtgOA15UrGDnuPEHUBliF5LffmwMXhQ26hkpoyxQqyVozB2J1ISU4GdB7UWkrBSezU=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>purnima-indian-cuisine.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3658,7 +4042,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkKIDMxwNyMceLlfwdR28lnxJciFQCFSMR9nT5948vMZDE4kT4VntIwoVNkZRCECL8YP8NwIhxt0_buRGwzjSJ5YLDzWvFp2zD5RELZvsS_koYJo9YPaPB6ibvSc5wjFDuOvCLFR2ljLylY=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>casa-victoria.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3688,7 +4076,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm7PHKOJ8ET49cQoaRaLfSfy19h_re-JgQgYQ1H6gPz8TGW6_ZjQzAylKNOLTwKoD_IQMQSLKpbKYA5dgAJS7oLcKLIC8epE5gn2HH03AXa_6tV9KGRG0Vpy7K1e-Yw10YIOqlXqRGcpTE=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>casa-palma.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3718,7 +4110,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmJCv52Jl1nqlux1v8j60mhYOZYCLcbQYthJzTuynBlfJ-DPQd2aPSmOwFQPLbmZFt381iAXUQkAg-AR1bbO6ELb32XYDmI760vH_UM1DTmo5sNBzEc2_i0gPOJUkvyXWgr9dD0=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>pury-jokbal.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3748,7 +4144,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn_Vl4ZXUbzin-34d8XsLKs7JnF_Ircd7G1nBHiTy8UlM6T8mdzJxO-NapEhSezBemErnBr4-hqxqS8QAf1WoD45Rfj81ZmHcK_ckrZVqAuXakIceAkyVpaT8R7a5nyRKR7IaqJ=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>makami.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3778,7 +4178,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmwC_QLO_9-yKQ5lMs1dE8pLKzfdNYyThA20TDutXt7IzEEtnyUhaR0Sw4fSnFbi9ckpuWZxoogreCxsZnc0by3HpAtYvQQLjLlFu-kWN4EdeGZc6WqsfKviDsx7gEpOPaKN1SA-IDPYkTO=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>udon-princesa.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3808,7 +4212,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkn-AA1-qyKZymJ8-PwpVIcXmdwY-QsTOh1GIVR8ThcBUk_C6U6dkqb7ZB4SPQanTV2p-13pxhWbdw8Izm6MKb80QjlkL0NcwJpOdIJRvJa1ZUDj0mPszIGQ0Nj2lmdqcBKTChp=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>filito-chamberi.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3838,7 +4246,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm5-HxKlYBH5WWx519MxffbXOsR1dk9GDkEWrpy9jELY5Ei2yoNeVoRfrWWrTQkBmDhzb77YPIL8nwNRLawfURm06ibpwQwo54PW9dvoEwkoxW7-kw8h1JfVoCKBfHJleaZuR-5=w177-h92-k-no</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>juanchos-bbq-majadahonda.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -3868,7 +4280,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWllUbOZlQ3-LXHQ-taWuwe2WMDKkWHkUi5rQeENxTA94etX_FFmVgxrSaEcqqhT7mrIxvOAxGptGk_Oosgb2o4axW4bq4BU_hFMNh8YIR1kEFSlNZSFO8YOkZ_9ub8_WW26PJkHrPKpMdJi=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-juana-la-loca-recoletos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3898,7 +4314,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnHKwPwIitDnGUQlNpIcTCkTY0D4I4BYZewFwB0Y6iSv6d4zGwxIqr6uaS9uONO6mDEBAwjWb78KsSLPIj0uVuw0i_Bbqk1eq9B3abWg8CuvTf6KmX5ybu8aLHkKkP2tZcJZyIDXjh9biCb=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>cafe-de-la-iberia.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3928,7 +4348,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkocwHOSO9HEQh1qlSnz8CWIZxc-MFdYpD9IMV5RuLWiALc3v65Nq5tsKoE5Xh66KSuSnwnIVLiVrzJ_BdLlrz_Ub9GZQs_Om7GYzElkHm8PG3S4LFcoyzpeD2gLIADUPVNuEdZ=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>bar-tomate-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3958,7 +4382,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm5Be-9pDkYGabcYNIJFA35FA8RxhFkLp1jIzsrThGPv27rpL_R1V0d2-QwGuW3_ZPsTqQBK4NagwByqpIHb1pcInRV-l17f58AsqQZQvDny4GGZFyCP4uCre5iQ9tjOhBnyoNo=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>lamonarracha-pozuelo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3988,7 +4416,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkgz03R-axzlIuHzOYwCFWCrr07ksXNxCclsb6YEKm6dasmVDHHj4g_lrRwKW11p3-ShxQWpsq6Ior3st9h_wv3dL4HKFE-FG-RfZ19X4eHfD6D19HZ_WQqAf1wGv1v8wP0VRaq=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>los-33-restaurante.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -4018,7 +4450,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlEHeojkbMgtWSL_o5RKGMdBmgWYWGzhOKy5c0PGBgf5Fr7O-E8EHn_V42U1ohTONmR9BcnOHnfwHYfXvhlCQOJQCn22l7iwfIXqBVoNUIJKMURX60UU3LOQJISDaMrpcdgctEj=w80-h137-k-no</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>chez-pepito.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -4048,7 +4484,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnPfVvPjgJ_jUC_uJVKmShjf3GCOvLMEdrYg_V0gpTYD-G3PSIHSKHuPDATWzP9jIrbgqUUrXLQRO0nKeReu7CMceSkRTrm71V3wM4l3wzTOOVEcOqo-i5j_tgNNWoRhnNk_ahMuQSee4SE=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>casa-neutrale-musica.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -4078,7 +4518,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnKC1T9csp_qyZuXnuQl2Uj78Yi4oPqPtyINvIYls8__qHH45Y15JOQctEbM1AvRtXoehddM5oKsLBlSKfiKUQZMezViwDTF59uR-rQlX24jlyOqqZ2G4pYmAzack22p8ulWNV4t3AxUcU=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>caja-de-cerillas-restaurante.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4108,7 +4552,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnQcPEdV7d95TmFF9-uWuiin0JSKFuLm-pvcGM02VBx_7z4FMCzrBgqoh5bsxZiaelDv0p-H-BWB1VbKIhvu3goFQ50Zp8KFRmJT7ux7w5YvTI3Y2BjlqgblNxK2sO1h3JnLm24ZTJHBJjX=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>marisqueria-moreno-iii-getafe.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4138,7 +4586,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkbWZoZ9OjPAS80GP5Q6qi-cE8r_fjKAsSva4gR4QdSPJtHhr-xM2aPU6Cy8B1L5RHN2g_ksohcBkT5MOCgWbZdHXJwvj0QQ5AswuVWXF16vc0RCOc1HBYj9YES9Rje-wEBX0RA=w80-h119-k-no</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-terraza-zen-velazquez.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4168,7 +4620,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnMAEvD3S0QBSBRq8QtB0OI1KIcCVcpGb0RHyGh5oYVS_QEy4aXNWCOjoPFcGD__XLsnIfNiDFbzH_hlTi-zU8b0kXgZ_DPsYZ_-GC2-PqzQeb3mN6lm0e2M749k3uTjvZvAN4W7DUBE5nN=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>sushi-ichi.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -4198,7 +4654,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmHXd-NYHTOm-L0Gpenn_w9j8vUuz7cm8i4256hF4TkY0AN-qogCi-h1WTBIHfgipBiH0iaVf9ET0260KXi2AwDyeOktehJw6XZXcig1-sxrjp7JsKwJPzodli_8R8N6mZl8jFmNA=w116-h92-k-no</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>la-sota.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4228,7 +4688,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnBGlI-x1cYnqirGFsfvlxJRzG7Y7Ay5H6M5rs_sS-Oylt4IQ5Yt8XT1TBpaC3TAIlmDDe6HULfBmDDKcvId_CU2-D7VsD5UOV4mldUzS37trPl4Br_TXlmszBGa3ZI9G8nqoiIfUMWKIwG=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>makkila-serrano.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -4258,7 +4722,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl7lQ_SsSMCWQKtvTRRTcGS98f2h_hHuPh8YV62t92evyLhmuY920ADdGidPZkZborinOQLo5L0BbAJ7VykhVMFLkTw6tX54gYHcq7DRrJCHASmLYPIvUxdtgfVxq_2CsdSNDrqf1BMhDDP=w101-h92-k-no</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>luma-wine-bar-brunch.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -4284,7 +4752,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmPlAg62VWjLDijXEInLzAdRRniaQPUURvDjEuxvgFy6aM-S8be7I1cgAh5WWxvcMF6eylFHSyGPUkiGOSFi07Tjt220KD7qHN76eEMOSlzEGxKUgZv168EwcYfRzKKnwMbLm6JE8bfHuOF=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>picos-pardos-sky-lounge.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -4314,7 +4786,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn2f3c-hNlVutkzKjyNC13W53g_70aLZQ4CKLedVLFNure8Pf_emTsEHX7Z-1YYhG0Vn-WTVvXjPeNq1hx84MF7J_zvq_cfpktYokv8C4xjLMeKgy52FrvH8u_urD7cvlQYFAJYlOulRTU=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>nolita-madrid-bites-wines.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4344,7 +4820,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmgMipgpDm6J8TJPWpSsg1oT1PLuxp5JO60sJeGqfSF8ZPXwQq9BPsFVqU6hfBKk1LteI1clzufs85e1J1hQCbm8XRkYC6XRmKO2l5T0sraWMFOi5jGMSWKLfEUwt6Hk8MzatVp3w=w92-h92-k-no</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>aredna-bar-mediterraneo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -4374,7 +4854,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkZs1A6whXp7NZDHhJ2Im-KO-UPn0Nf6wWLHfJ_Ety0cbvMNHZKZqJnW3JJ7U8qvk3Dz6tMPFF7cle50CnDPO_IczILRTkXpwrfqQPMmgy3CX8JWvO9oKZZ-mUWGhY58A0rct8-=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>nacha.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -4404,7 +4888,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl8FPE0oXPOvolN2G7Vfk4ZSKlkUJobZZc-_nOTt4oahrsw-MxJBNdfc8qlmvq25Z0YMo4QfQG3yzA9hBJ3dBXNunR6KZrLVO40JlsjgJSJ71v6CI-Qls65U-UOKB4oUpU4mEiL=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>la-finca-de-susana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -4434,7 +4922,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlrAxDG33xbn56W4_fehxv9kQtrQPlg6wxciPtmK-uwKjCa2CA8F4B43GY44yP6QB2R26bqFrMjcnTQzhC3OlQtj2CURz8GcnWV_DTxKTag1LbiIVvkPu1pC0UyQBpJgr8_v-7jrcZbq3L_=w92-h92-k-no</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>la-cabana-de-patones.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -4464,7 +4956,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkZrxIzooG5v2TlhYjHS48ABmycOTEjWKgHb3iUOrlrzYrAPPwSMiSI7loKfMEX6lU-_xOG0cExt0wrIuMffHz8V6W9nn0q_rWuOPN71wFfKwTJeCDiGZBO2sSvXbEfDbUGQTLN=w139-h92-k-no</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>chalito-heron-city.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -4494,7 +4990,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmg8OScFHyEfI9teI8tMgDX1bMHFKzJRa_BZ7CCbSREJlwM7ITo87rfRaZKiuBCm08sE9B_EpiX_FxbftiKnKukPxNTE68uQZ2G11-uBu2xCbAp-l4wUo8oLBiY-FaHs6653mYPLw=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>taqueria-el-chaparrito.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4524,7 +5024,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkMmSTUtFJCMAMGW3K77eUgjSJIofpF79DC4KgTGuAyUF5XpFTliDApM1xuaAS-EzO-W73XiSKacJ0ogOCmYFLtUB8GYfDKcGNVuGzQLUvnTYj5RAy-9SjvN2G2atGNWo9MRZyrCg=w80-h119-k-no</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>la-gateria-taberna-castiza.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4554,7 +5058,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnW46ixyY3-5RRAZWpa0clnsSTwxkYpzqAiXZHzG_hW82HjxQkgnJncps6LiPlk3cfjjwSxjkXAIYtihdfee8u-Ecy4O6E7RTTta8Qcrcuk1sxe9srfq55-uiwKhGcndB5kQ94oEdvikRiH=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>kazu.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -4584,7 +5092,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk9H6wPuaBE0FcapS_nYyU0kr1HN3LrncbAJkr9lU4lVlVpkQmqsxZHNDv-znnfT41eKlIHF6Hxx7dbqjKQsQbOAi0vrf-eKn6GI7GfU7vcHDitmv76IP-mR9zFQAklcIXMflEkIP-TByM=w92-h92-k-no</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>jurucha-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -4614,7 +5126,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkyyjl2Kfm1886XTk7OPOIe56-upq7u9zGDy6ai24VnZa4melfBeG99o0maCcTgE_RG8esUNSCLJFoqHmDlcmCm35vkPGH4dkYuh9gZTDaOJCAJZUtFShicHUXv5_pOMzLeX6fYMjIWSLF4=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>bar-la-dolores.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -4678,7 +5194,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnb8RzYfX852xk4Y31chcaA9RkIREQGhGFmoFFUDcv79wMlilQB-zgaCCcxH4PqpQTF7mQ20gjT87H8HzDh-pW0FgVq0IKQQv7bVGwrvh-4x4l5fQt7gxw8uKgpKYAJr18mHKsuoowkLBY=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>mercado-de-san-leopoldo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -4708,7 +5228,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm3evZ_9EGmBRW2p0oFZZxwTaZtu9MdDeoaev3Ihk1le1ynPPBeW_00PrgCtZGKSx_lWX-ZBU2C4mMe_H0UQHu9wzofxgNsnog1eGSoKgiUfGO34X5-k57eKiZnSfwGNdjHHrMJVPRYKR3Z=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>sushiaoi.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -4738,7 +5262,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnJ0_dHa6n3cQR8iZyK-RCfxlAB8hAXn3xlGGarSg2s7xi44aYBfTCD6T2xVC4z0wmTF-lfky4npCjMEI0K-cIGfsOJjXc7zG8HOQJfltC9ubBuZE4HxhML22ihyzHmZL0onHAEjMQtSgA=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>saona-las-rozas.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -4768,7 +5296,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn7JGAwKEDOJOmTP1NEUdBOAn1PZpAi-cK1D8OTS1U24fbOHPWQ3lpSl3FMh6THzMXUsQ0PQ3O3YUzlfayq8se6Em2atU5u8jFYIwwp1lML5JjnoB7KM4tdYKeSoH0cScXzvZUb00Et6BK8=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>bar-coctel-prosperidad.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -4798,7 +5330,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm5pzw3J35qdCSLGxlO0jDBRf2mNnB_ADTDrBK13GfJKcHdJAbfmpz90CH88VxMfRJZ6arPuKx_1VMkK7a-8cVZ3Bxxy1PTiakRogoxYW2i_SDPlC5pzVIDRDls-ks6hcFxLBEm5KJeIce-=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>gamberro-taberna-canalla-olavide.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -4828,7 +5364,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkFakgzAKJOM2lLqrnql-Lr0h-cxu7wiAn4zLF56L2_RjCd3WSoGIg0nO6EOnX7razK3ERnbX2EWUTduogHhQZyb9c0yyNR66ESGMlK9NXfYO5Jcsf6kwqZyTFK8Ay-5LkKRkjF7EaB-do=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>taberna-los-gallos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -4858,7 +5398,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkbClm0S7_I_GAqgb-ZMxHN3IKRzDUB0OZVquQY8ffMUhm2ggPZm_Mp44_t_ClMAiEM0ezLL2L1MAm0pzI8MYFq2azcSg12J97kULRABOR3X94Paf_4TU-V8G_WfFLc4ZbbBPpuHA=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>la-paloma.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4888,7 +5432,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk47MaevpmhZbeBq1dOJhbesUqWUxUAwxYSdBNqknAufhJKLSlgiytOh1YtvvelojBPstaqjzKfUuMaxLIvOV2B4eohnWQ3WNEQJj4KrlvPUWjSIhw6fuWJUmx4yuJHmbEYoUbz=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>ultramarines-del-coso-trafalgar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -4986,7 +5534,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnfpzlbFvNbpViJULMacs8snaVoEMuHZHerKcffJQ8ALdi_BGZtLknc-m1i-XSCZ0mV1MQIMyJ-6KvemBGVJ71vqo-tS4iq1Am470oGd0OAjtQPX3cUNN0Yqsr4mQUIQwkWHxPte66mv4Sh=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>ichikani-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -5016,7 +5568,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnbZv1QV9XfHQikQWxCuIDShQzm4s6Es4KwNPooJ_uRZODp_Kbah4BYiMTZsb2fDre0j_N53FhQbMKHs0tZGwOZUWIvND0IyXI8ED4JZfxW0bJ5QEFO4sZodGqQLJ7LE7ZfbI1v=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>xiongzai.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -5042,7 +5598,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnXO3c8vtm9JKn9BtndHHYrR9uCOW0NHdrnvt0AzcWpyKPl5uPpXdvGR8SLfcQBoxhwS0hSGzVz48sEuXXs3s4K5k38kKWdtfH-uSxDiJ9jZWNpo-DE7aehvUmf6D2P0FWVeQRf=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>cervezas-la-virgen.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -5136,7 +5696,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlr2KKoy4NHWDEVVDe_RDTL2y7AfJkg-z_Mj116RT80dQX6ThS4uue_KH4lrj8RaSFtLJ-SknxP5NmpjtIR4OA1G96guJWXqkQJ-d1sy0LCWctSHiQiYh1TyyUk8dUno1m8B7o9=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>la-junta-gastrobar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -5166,7 +5730,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWno_Fx9ORouoNDgSdb1qfhcfZmK57JzwSb2TYEUGN4HQbRtHgxJG-9LNzg86PNjCSI4QeEo2YGHvEmw42HvY6H7YzkPwl1_bW96GHTHfT-ZlLrpxaHdlZWm1pulDqse1sUmXKrC=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-allegra.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -5196,7 +5764,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmB8uXSZceBnxmGCurFGAVWRp47YbAxbmzZc3sPisF6ELPltUvEnuDT1kCSyar3RI1SMNbRUQlGxCedbXasgjS5IsW2d0emOe3WvBVa8PDq--R2gOizsUDsONGh9hezO4n-XsUErLoqGd0=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>milwaukee-burger-pozuelo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -5226,7 +5798,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkvn5AYHbfrXvI2zqfSjQpMs4s9OmkEk8io0aEnahr82vVFEhXG7YOUB07Hw4emoLWcTnGAcrwA0j-xDff_px_ATCMpGcC_ZFtExlZOnx4Q__Mu0YhYFc_JaUJwaV3gVQYScAm-LU8Xdlw=w80-h98-k-no</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>armando-restaurante-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -5256,7 +5832,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnenXRZZ_OBYerFhVBpwLXXRK-9P0JS0HOyn1PvBPR061vTJuZDmWcFCQeofA8ysflNHdYY5fVhqrpZ6gKjMe-inX5U8vDA1DU05v_Xh_iZOLHl1q_qH-OcxZmUS-VUyMUYORn3yzc4-O_q=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>ancho-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -5316,7 +5896,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmLL_jekVVNTnpVGOYwjqifT51NXYF1C5GhVEpq5v9nUDdidpy8k8PjzdBwU1821k1TWbenEvhxRRCAc2CNtK12j8vKputAt9Ez1lZKTGtE7Z3-OPJMGtwL3VKh9HR3skkjZ8KCXbXI0rLv=w89-h92-k-no</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>99-cheesecake-princesa.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -5346,7 +5930,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXcCd_cE5kNWE00PvW553rK7EyIogcLLTClCqlwLVFsA2AbSU9i2yIUTB8idfePMtoEHlTcigiYd9J24dy8u-EpcFha45kKkbVOH8BxpJZ53pJ6bbeaiajfribowFbk2TDE6w=w115-h92-k-no</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>z-co.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -5376,7 +5964,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkHi3Lgp_3Yj9wt4vgA1oSIa_JtCtj7RjGhbND5hT3yq3AY2CY9254AYshpiIazZ42rP6BeRMSm88asoQ3aNqgnJC-CFz7D2ycPcfyBVm03G4OkITFocSIG4weBMRm1FQwM--e0=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>wall-st-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -5406,7 +5998,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmfK3ecwp1KBCUDxN6dCJqA70pgrH2NfKG7lsDomBMq7fInbPd3or2ybPemLytTq26yVayvp7CmSlXk-9Pj-gr8UOqF-WgSU6MZynG6s4R0t2iSq6XBBJGi9BxeCNDM-j1M8heSbsiWKP_N=w193-h92-k-no</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>revuelto-brioche-sandwiches-brunch-coffee.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -5436,7 +6032,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkbp8VEU4GVRT19DVy7rphHluzcXyM7blQAEsobdcdpggvupAmD5UOHyLSNV3x8RNxQ3EbJZz82tWu8lqULGRZKJfYTYtwv9asVOVp0u_llO_T3wojvqXBE3NXx6UANeR4hzXAwuXcbfJam=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-el-perro-y-la-galleta-malasana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -5466,7 +6066,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmV59HL7K3xWwnxQnRu1yMRwgw1Pp7guppkyZ0vM6uhCXMg1DK4v-QUf1Sqw74nHoki79qLZdPvAMnFY5cf1_i_jgpt8gq8bfLzS7lVZ7dRq9FTgo24B6CE7i6wj9HfvYi33dmUo_iVK07l=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>xihuramen.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -5496,7 +6100,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmjJipUmK6ZvnZg1l9WfKEpLp3iXi08B0RKTsMHTp43wY3cuT_JKc9RXPBHprfJ1Maug-lLxeYB4k38KDPZTZ5c6gRRQfD9xuaKST11cJsmrO5HbChDEKlo4HVpZXCCu9EDo9yniJ4zd7nx=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>giro-handroll.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -5526,7 +6134,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlFKvu-TpV97nj0N4cmKZMQk0EmTPJ1ZvHUGOXnxK3-11VPXjJeexT_7rD4HmS9lv-rIXX94_xrO48LMlvTm2N1mulasQNy7OE8s6X7q_IHQFt-2eQYO67IstFdivepy8nVwf7PQhbrwFEI=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-garrak.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -5556,7 +6168,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWntgGk1DOhDxFjJQ7vnsTiDfbkmROiCpDMKnOx-dd5d3QOQBgg1klZTTJhPYsQhl40HLPfWEPZAuyPh9RzOZZEnpyVjSRdxdqTXlRUlolBgojEy5YcX2vVNkqZCY7MjRvbSieQNBuHavFg1=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>nolita-coffee-brunch-all-day-chamberi.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -5586,7 +6202,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmtJGLhoXbA6lnL9LruHQySC55yVSGDQCeqXD-l8zCJTrrtf3aERoaNoutAm7i1qUP_Rw9LT1gIiraeu-wgvG0cGk3W7k7SmuakGwiZ8nD8PIGstpflpsf5kn-qCvhAknnt5C3X=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>nap.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5616,7 +6236,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlVsNj5QDkjzHNbsPXWe_seVczmAf1g527WAgQKj4ZL_4k069T_4sj207bPH6MFeS0JYsNB_8hhwo4IG7zGiVIGF-pBNjY7ApB5OgOl67caOGQZ1uUY_OQqCf7PFzqzAApJkjSAh-S1LRc=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>pizza-pronto.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -5646,7 +6270,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk8g9XPieZ0rpJ2AF3CSBhvvpNea6AAADzjKNxkPykMQHg0BRTJdMIrzW54LxLzcCPJc1jbuLOBbnTH2a77cfjPiTVo_wE4cA8G6D-MgG5dwbcGkmhft8vaaV6B7nwmrGnfAYj7ZpEJqdw=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>hundred.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -5676,7 +6304,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnrA-AHwWR1yB1KcXKcQbJbENPEVkEI1jDS3YcXa1Jk4Q8KQl0YeeFEojK57RPkK6KHBLZdYMNm9InHBxbzQ1N-FtYbPkgC-B82DQyf_AXZT7SKPHEUBlVwkbx3O7SX7S_vfkr07g=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>olea.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -5706,7 +6338,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnrwfhPJiwQ71bHgktbGYa2D1xugjx-0vtQEgX1YByNiByvY5HRkI6XjWsBtstPmWKWS2NHBIE3hlwani4Vgz3lmNdd6pJZBeBis7MZI7zPe0rmzVshWGwuaKD0-A29ThQwZnUJ=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>casa-tabacos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -5736,7 +6372,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnz4wJoU_mmglk-ONZZhO7duc24Y09ZP9J7j-p4FWA9zQmmBtZZjdC2U-SrZchv61C6IB3dII_-s1Oezw6KH_wq6Gt4KejtZAXF2r69N0osmdAC3gKly0mquQivpc5Hz--pAWcjanKkPmU=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>persimmons-restaurante-georgiano-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -5766,7 +6406,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkjxoZPrOdjXH3UAEEh4cgxpFP4qhsI6XgD9iAZJjI-WrOBNWm7RcSfDJ6cG4zyDFICdq3SkgVtXhr7cvqjUS4XTJbJYjBfrSvjurCRuUDo9IVcvxTqNYdQldgJlfbRYHR-mbPB=w150-h92-k-no</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>bodega-de-los-secretos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -5796,7 +6440,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkW8R9vY9vjKJa5XWqO7If7wmEZ6MJYpy9_2cU8cMag72hx5QyTRUsmZP-FK_P9WZPqIZzPbKjn8VItPLPRwFH8atId6Ocm8vrM_INK3EUbjeSBFE6Yg-vm1aEFFwPsgkymCto=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>la-gloria-de-montera.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -5826,7 +6474,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnq-37-KgDL85yQ2uLvCejm80_jEvI2XwB0I7GIfuARfqVh_yLsD_qwtqtf9Ass9HuvXQFv_mbCP9ixfgXhqCMrXePaOC0Es3gozANSNSdo60vUzupLMxyMfaJMh0QSONVJcsKJ3WIXbNZ5=w92-h92-k-no</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>poyo-club.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -5890,7 +6542,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnwNvfM2DR0qgyLOetV_93L18yPO5xIgCk6jubKoAIculjWYvsjdPtEBRm5EKJsN6LqPHIzXGe2QN42o1mY0BOiCeWKGHM9U_GTsMgfFIP5M8mh5p3l-S8qbLYe5twK6NVtJ16G=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>monsieur-sushita.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -5954,7 +6610,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmbSDqwcVZxzbKM-LMFn37HHrZeREVLAh9uM4D-koFz4oV5wT0963iBTsZNufEQ6s51CWbOPu8xDUzr2f7YMkxxkjkQPHBdk7e4ZFFieQ8OosaEvznzniG2oB5BFdI0E2Rl8OWjRg=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>mawey-taco-bar-majadahonda.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -5984,7 +6644,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlFcfuashghttHiMhwyh_U3NAdfCGjooYGrhcW2c1HgyurCXV4hFEMgL58I5ZFxeuk0KQt0jDYx-BP8mpHnX4Hvnq0wo9ypdrOAjiJ6pO_gJUHbAqV7negns120Zvk74148WWFD=w80-h142-k-no</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>bar-trafalgar.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -6014,7 +6678,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn4O9177RvgABSCVIwLj2g1V8XzwE-ijeSAuoMTBfDo2-i0HBhJOlS9yQOmSfrV9oXsPSYBn6qtlL6i5EdscaWaT4it_hsbmQLH_AK3yl7MvgmqaqQJrNLpZwO-xZNzHujsGlfs=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>la-alquimia-vinos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -6044,7 +6712,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnddzT4JoveyUvfvdol8QFAKYHfGyE1m_hwFgdsSWt_B8jYiSDsRCUt8INx1qcMrg6sVHCg87EA-zf_CyKXU9xoebMJ0KUhmEaQRDGzLc7Xx9hPtWgIFNvyLADm1bL2dcwFd3dDjIGZ_YQw=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>casa-botella.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -6108,7 +6780,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnPjDc5bh4LFSIEKpuv05Oh4WOJJZSkppR_6SbOMQyk4v75geNMLW01jXLGK2NkaHK9HCszashkO_E80ECXTQC1FnhQLxCmWc-YtkOFhmiu3B50RUUCyg81D1fmoiA-YSIzqPJU=w80-h142-k-no</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>croffle-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -6172,7 +6848,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlGaY0aM7AgZeYu0xagcYF8GesroW3sxZGXz1JXqTmXndps7FH0vSAXvBktPYtWzoFWOVeartR0DECK9dIC-TXLRQ_6yV0pVBoxLjMrWq8jROaJniiWVJ02_GZOJtuhbwLSFuL4pnOBQwqy=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>pistola.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -6236,7 +6916,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk5ufatZmRUeksQFfy8hfSZSAJclBPfVZll6DCmHt8scoOrmnpc-oOfpcKkb1E6S3nwukJWE6IdY-GhrI2rezkOwOqA01K2j6dUv9bhiOYocICkA1H8isXl3vu66Q2kmBWsvTLP=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-parole-pizzeria-italiana.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -6266,7 +6950,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkUwVPBYFVB6T-qaqtm9ewH1mqU4jc_ORURELD3-zdJWsyICMpYpArlhFk8kpWnMD1MSceo5fDPQzfxzafI9Cz-OCKKnzq80jQe7edOCeFGNVWehTXdRX3ZAmuZuuAtlYCpH3b9IDW4da4=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>la-casa-del-pulpo-bar-los-gallegos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -6296,7 +6984,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk-uaQDG9sGGGLqhOTjREIou27tPtIePPXFmYia08XmgYhjSvDIitx5exq4q_oHtwvKv_7Q3bnR4y37tChFm2MsaJ1y4B7O6uSrgnq1qp3XdJ0CSZ0je98C1VsMWqjqzlyQ1SAg=w149-h92-k-no</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>yakitoro-reina.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -6322,7 +7014,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmX0luTULxC6m_L6d0I6vDuCNdPMpikMLmNtGb5TX0OCzSRycAkXyz5QPdeCVTkSFO96LgG6nDUnDSaKC1hs43V40zPLsQxC3e9OEXH-sNmnaNScZYT5BLzoqB3p8kqi51K2-HAnG-acMas=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>pecados.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -6386,7 +7082,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkCNTPAsIFYNaoUbXO4qVdTUIJl6inFsN8kx3WddoQgAMQLnT0rXLuDH0SYsufUx4RTC-XUNdzxsHkGqSMaCyXl02Z_iblM_asrpFcYMqaei2fhWS6xbgUkR7k_ijfVL0xmdHUgNcXhsWc=w163-h92-k-no</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>amos-restaurante.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -6416,7 +7116,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm-EVEk5BuAIf6AXhm3QeIyOeHvxnebpBg-1ruB5ejv13gTneDJ0mHUm3JIlUbN7aJNVKzyrl4bN_XYmF8M7MfBON5lUpOYru3LVUdVjDp3DiEznnpKuKOAWHKZYolFgMpBWN5nwD9tnwA=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>casa-macareno.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -6446,7 +7150,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnzzwMFMDKcKtJoKJW1Ab-fyIVb2uUg2TWHIUmMBEeeaCXQ6EmUsU5afClFpCZGrFdX1onr9TJs2cP8HTjE69Zjw46WvDv1i2jfE9YCMks7xYRrq2JdoUXbnePBoJ9iqFQz90QrDA=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>pizzeria-piccola-napoli-cuatro-caminos.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -6476,7 +7184,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm_l8AosF2tDF6Rd8f2rIGT5txcveozBmoIg_WBcJP3U99vAdS-F8gVO3La4ZJq4TbQr-lWOM4x4UKIPoMmcef5zRkP4TlTk2Af3_d6lrobAn2hZTGV-gPgPjotsDjdUTXCv0m7=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>swiss-butter.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -6506,7 +7218,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkURIoTEUuVbhHpnGkhJ4EsTSFF_C6VpoiBwU4XeqwpkIz6wz-FQXUBu82mlj5dqfCd_Ui6jvKR4wM7M6tJmrfFkuO_xjpwEsle9slyvTlI6Jqk3izsze-bide09i3pClHarXVBqXl6Qpdq=w165-h92-k-no</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>la-maruca-velazquez.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -6570,7 +7286,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnQVFs7la_iFfYM96wyzWG-p6vqUkskS2voT2pSZR2yEvjZ9vgtlpyGdZMfSpmr9C4av1-sOMJcalAtB3KGXw7iBOgxQHMxLmj811W2bbvHqhCCsWx9Z99dYGBuVENhnbMN2gn5sQ=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>brickell-majadahonda-hamburguesas-burger-smash-o-clasicas.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -6634,7 +7354,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWma_sS1qvWDv80ytQwp5uf_fWl8iQwoBGJvNC4Hrx4XYAkA1bYb3I5-g6hLIiY5etQQnihXdAajiSkiWC4k8XJJLkHIgGr2EpkPmUyNj-NT3sGnPnDDMF2cKLlGPXkmjpumnG5OKzYt52Pg=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>pizza-wallet-pizzeria-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -6664,7 +7388,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWku-kWAWPypnALdXRyOOOkAaInj4aqB_6cIEi81JZKeXltPTalWsC0GsQDy8XpYOyDUyJzXFxODnj6OREKV7ZaxUF-062gt7xhPU5jyoApacFuE5Q0oCxw0_26bfroI0efwcJKDSuqwOdOS=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>watts-cantina.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -6694,7 +7422,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmOFTKFMr8iyqEsQ3Lmptld7UFNi4jV64ev4cfA4Ugb_dtd51Ux_0kTy0YZe7LGp8d9mii2BYgAn7zl-3FWqjH1fP9tn0nangXmMd-mLUUHeADKIDXXtjJZdX8ZnuLQHUssQm2x1w=w80-h107-k-no</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>bo-specialty-coffee.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -6724,7 +7456,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnQ1NANrSZJxcFWL-uPUHiWchCc8cPoGlYTAB8VirVuldpkAqpO6I7z63xXX0HSgH6k1xJJFlKgk_1HJTt7nfFJd-2iHc5KdSMjBWrVDBrsHrAltUCjHLQWDT4eupUbJmNny_Kbgw=w80-h106-k-no</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>kricky-pelton-chamberi-l-hamburgueseria-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -6754,7 +7490,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWncEEJiMkwPNe176qLfrBwzoxQAai0gm7anSEVKOKjk0L8XgzCdFa17gTRswuu_T-lEXLzLuWO_4exJ5soNTG666KCQ_ivydO6-KWpuRe8P-tLFNBFhSZEm1OD7P7frJQCeq4jQ0A=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>pinsapizza.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -6784,7 +7524,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmhKVCQ96vsGRXz4ZTca0kqEJUUM4e5O-XlAoa08fvobVqiMARLGkNGq2v2CxRYmiOHHZwEYwYZpLmZJuVlS4Mdr6YFn1fklLd0mP064w9tmisxbEfEidkxNtcOnjRogA-4RLOs=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>frankie-burgers-lagasca-hamburgueseria-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -6814,7 +7558,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmje8PF2hqtOUeGQ580JpB_rrkTcx14yLuPtBnPg7QUJccwt7AFuodw-KnPovuUlkrTOpekt4nKw0Me1xF3XJpe6YpLzNIfz6a31Fmp336Zvly2zboNX-hc3doCWYv-Rrppz5tbag=w80-h142-k-no</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>amets-gastroteka.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -6844,7 +7592,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm6jdemr111CVr9aIMgVR0oMRY9EY75JvO9AP7O8R5PnE8E1FOlWM471fJeoIzQjAJPdwCXZgrvYLkMwrLbNC9awuKTyfbFLAc8iDkTOuE6hcb2kQUhpPoqBiFqmB7oSqiSLOIZ7j3GOqQ0=w122-h92-k-no</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>santoku-la-barra.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -6874,7 +7626,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlcAmVkL6_A26sL9OklMJkfyrQgZRJmNXXgN2OYe8vtfQfAlgUKrpxi6uHbwZE9TxMgR1YK1JdZ73Q-LJcRI44d0mBnXjWTOoU12_xOYa5rOUg3Oh7vkpSGqiorv7eXqEc26l8ajA=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>raza-madrid-barquillo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -6904,7 +7660,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlvHpMEz1IRConmp0VxcyaH0t2C163h63peWWWETTZF2zIESdQ_oUqznKyttqKHJFJ28s_hMIK_LLDOXGnx9nL8gxPZbbqDpye7PsYJNQHoKMeVF8ISLcirGHRMo_d27k3OeF0QN-BWZQE=w80-h120-k-no</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>dispatch.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -6934,7 +7694,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnmwEdQKcsT54Kf2c7IQu6tWN-Tdbm9VR4O84crwlPCJBTEYchkQfoBVPzKnCBrr_ccz8YxfJBfPwZ7xyd9zzXOS-Lq-JpnbyAqIwFwaAYF2wBUAshJ1eVRURdM8saYisdQGkmh5qaoVI_s=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>hiro.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -6964,7 +7728,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm_mZL0uZd1Lp7JTY9K2gui-k_e7BMkA6Wf-zxYqLJsX81OHbkxneGASFCaoy6G0kpl-vOpxENdhM4yPCA77F3tcsdkCN99F7ZlMIdba-6uCAu_D2Pu6ZhjuJt2XS_ddEAMUM7_Rt7bS3EM=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>myo-hand-roll-bar-garcia-paredes.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -6994,7 +7762,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnWEgZ6yjzASlMSzIbZP633oC-zJYZzlB8f3bbz6qNY4jDB5YGqYtUPt1XzpvV7OLx-QS7me6-ZtTV_YirCvKEnztMWBwhGOPhruT012nYueKE-W3CDsOFgPQkoqkehD92_17MThw8axdNg=w80-h100-k-no</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>biang-biang-bar-chueca.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -7024,7 +7796,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm0z6_e2ir2rY95KB6aXmXZ2t80FUv0xophiD_jMduKeTtUu4cANv7PiPAuqiDssEm3QaITqj1oPiwvU-PBQTV5v1UswbCIgbsupecCEEoxUsttU45kbgnROPghW2TIt74XYDl0=w130-h92-k-no</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>casa-pei.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -7054,7 +7830,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlIlCtKmXRf7qTlDHlT8-hc1qD7qVF9RB-hiJq4yyqzsnVm_MG63J4hxe3UPLSEWJ5PGrt2ZmujrTCGzT6hDAl7kmp3SzGhowvYn4dzY8v04gHIruVvlnoVeySGzpCpZop06BoqveDrftTP=w80-h100-k-no</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>sushi-bar-tottori-lagasca.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -7084,7 +7864,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkCxiUFxRw3nm4JGLZXN5Ss6qdlBDdpNX-H85Bb-cFNh27AUGEjv-Q_TnmnHFCNQNpRZ2b3JuI4hToXvCv_ajNivlqcfqFxB05NpQBcZnKL0QYQnjSfZVXSe7goHjmcgwW54q4mjAmEJVk=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>gaman-by-luis-arevalo.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -7114,7 +7898,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlP3rIVHQnWMRBK0I5bZEcTEa4FrsgQcAThLNOrhF2LxcEoVKfU6i3uImhSvHCWPnGSFoQK5pM1RwaAepgIwfXLxOalmmpeUZM87sIPk-kvGrM9mI_isSs3NTlyCLGau9ODKb4jWNIH-lud=w80-h142-k-no</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>fismuler-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -7144,7 +7932,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnitVyBt9hS3r9P1DxseAE0E9xyXBET8xnviTXG1hDByPW94Bexf1MMKfBvADoDWTK8RyzXveOackQj3XoQbtFjyYYI0bGLwZiOKt8MfW3hsTpmEXw9IH0PdiBse7OCl8OCeCSgU0OFtfA=w123-h92-k-no</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>bakko-omakase-madrid.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -7174,7 +7966,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlj65SS3CeymI9IK1WoDv0ldmp35xkmC1xT2dkCcUvupdqqW7metr3vCw0nsMQq4mCAO954XYsIAPHSM_L6muNDex9HJ6SRHtOZje7Q89T88E-mZM7HfWNGx7TsP5f9lCZyYBAucyCFp1S8=w80-h142-k-no</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-farah.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -7204,7 +8000,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkb0scJIp9D9tjVRCRzEkr1qN1aOD_hmk3g0SZhgbmk1gWtdO9wLPn100PcejbK8xZmB_YTvSAM9QNvGYpIkc8aQYdKdKxpEzKWtpK5gZl_ndWD_okp9m8Wn-_LxCQt4lBt91iY=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>casa-mui.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -7234,7 +8034,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWliggOLQTHpQ9w4rvdF6jCVdWVo6FvdxIjdEHyBKvrqyERLMeIWT_QiZefZH3Q1qQwJhqIIHl5hGVS3QFoxKriWNhV3pHYO_s4nUHnxq1ujPushtKRYpXsRdvf5_UVWAtt-FZ_X-A=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>smoked-room-madrid-fire-omakase-by-dani-garcia.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -7264,7 +8068,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlbyYjn7hBQBddUxxyin0rERnLvrGYuC6glmE37DKbq81vCYRSdKdu4Xp6990Gru6xpw7Ge5a55kVyC79XYpl3crKB-Tf4LVfU5mWyAVRq_1d4fQN46Fhs6oux41bU0jrxASQlpD_m7AT0Z=w137-h92-k-no</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>kuoco.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -7294,7 +8102,11 @@
           <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkihOJUBSty1FjBbYUhyplG2HMKWQ3GHet4XDHPduR-aBQWS-q8eo5kmBVEPLpm4V9ZHZ3EG7ySeJnhCo5U7i3nFji0XaWwNpY7UHzE6UDAlChwRVeeH5CbreOyAbxAeY2XDiSb8g=w138-h92-k-no</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>puis-thai-tapas.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H227"/>

--- a/excels/restaurantes_v1.xlsx
+++ b/excels/restaurantes_v1.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$H$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$H$233</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:H233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -491,116 +491,120 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gazteka Bernabéu</t>
+          <t>Issei Nikkei Restaurante</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
+        <v>4301</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>30-40 €</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Comida rápida</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlfB3M8j_kNFP5gTGGYpBgcbBjkWOFxx0pZ3QUn6iS_GzNcJPURnxWkzOL3zIPXgHXQcJQ6GK5R5K8S0Ti3EjF6IPv4vVZygeWUn51YAuia-eUH_KdoqkpyjfglUEsTr-_sE0F2faY4ztQn=w80-h142-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc6AjxqwqvSax4vMuR8MraBWAVGo5Z6p04i3BpWtbINCGzWFkd3YhFTlXtJhoWcS1QtgaVeqeVqgyTljAPFo-4QTxXh5p_3KqBw3XJNuanTQ8BOZM3vNuwMc_2I3sPs4vDAuEHmjKKMTgWy=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>gazteka-bernabeu.jpg</t>
+          <t>issei-nikkei-restaurante.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Pez Japanese Grill. S.L</t>
+          <t>Ojo de Pájaro restaurante</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>463</v>
+        <v>318</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Cocina japonesa auténtica</t>
+          <t>Tailandesa</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlX21tjDLll9is-08XKoxZPbpD8N5X1NMn2Dzpd0tfLhUsFpKDT0ChJ3avU1sERJZDoYzAhvsLdKwNH8uajhaJmfECPU8zl-O5U5DeQxxxwJURKzuPa4FbasWksi0XLrkkDdqa4=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdNxfkr-gYJEdh4BH8hdUfOHaowIdUZ-ZO5tskjJnUIK9ATPPtMUzo9SXeDnXn44TEnelrblbm3IhxisheC-wM8Iep129Lr5W-hEc-6wyfwu3g3lzZtEvDSeQjGNPXCEcGYetaZUFzNd2dB=w117-h92-k-no</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>pez-japanese-grill-s-l.jpg</t>
+          <t>ojo-de-pajaro-restaurante.jpg</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IN Ristolab Chamberí | Restaurante italiano y Carnes Madrid</t>
+          <t>Restaurante El Ventorrillo</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2383</v>
+        <v>627</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30-50 €</t>
+          <t>10-40 €</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm8nHiEui8oHBOfsKkV4Jfn7xyLWOLVBI6keFZwlXTOCJ3ONddDSJ0n09zl7IejlQ9Rekgc5VydQpCbmHKS0dgu2o_kTqSe8efj1czT-Z9HAFHLb4m4vFRU6GrfJLQlvJHFhti1K1l5Hk7b=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfD2UPyEZ80tldW_5soo9VFGwR3-0hb55xwecLv3iyHYeHFi-dMcOUIOtIT0BsBHw_bvWMWOCGSWIVvIeJik0J9c4-PLzOLROtX15bVHwuqhb3Nv8wHJnaUib8hi9W5MDnnM3EfrEOGJ4OF=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>in-ristolab-chamberi-restaurante-italiano-y-carnes-madrid.jpg</t>
+          <t>restaurante-el-ventorrillo.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CHITÓN</t>
+          <t>TACOS REAL MAJADAHONDA</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>506</v>
+        <v>114</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30-60 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -611,162 +615,146 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmo1LHa7IR3NsOVhITuvhLfMAmrEYA5dFYbRVABFI3eCCesuQRF40RY265H5rvfdSM4hcURfPW14BukwpDb7jv_cZ5xzMMDQOUI2hI3dNI6le_mccExPRf5JbyLdbtC4AIyqj7Z=w80-h114-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdb6LhTiea0Qnu83h217ahBWf-pSs_wybtvurgL6OeBrKhq4FnWSwffmYe8M3qr_UZ18I202BEUaW7-8AZk6BCXD_me5ajKUnZBEagI3XLhrdMQ08NxF0VH4ABFP4syQt6VrnYlzvdgzOI=w80-h94-k-no</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>chiton.jpg</t>
+          <t>tacos-real-majadahonda.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Gladiatore Ristorante</t>
+          <t>Amasa</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>441</v>
+        <v>1064</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>1-10 €</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Panadería</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkHZbLj0zXSBHRKm-kPXZ5thFE_Wgg1JOxR5nmwwNCBbv6NCz55VTx0Kq9qN_iChEBCyMcU4JSvO7OcWJlxfJz2i4BZvdX7j80bgmO2DtVGzo2lDl5ZjSnibO62w6M0HVRb9NU=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeELKtgfBOOmsJZtvjeIuy0TTaoiF3j8gMIddE66JrZJMcjhDgtdkRh3JYYY6amfwO5R93eMF8BuGJa9TMaTqY-lTuDtog5C8eHtfxnSy6LZJVsWJ7jPtVZfnM39EzLzK6uDbF-=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>gladiatore-ristorante.jpg</t>
+          <t>amasa.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Kogumi</t>
+          <t>Bar El Boquerón</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>629</v>
+        <v>2640</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30-70 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Bar de tapas</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlfes0XN9RA7B8HuxDZUED9aM5DCEh0Ou1qlfKZUx9HZmtc-AAto6Epss0iSSNZ2h5Ch01Aoq2v1-TW1TYeCCCpzEmq-RKTyeOg0da1qRyfqmNQloxxAhOM120yoC5UxwHbULndpAhsfQW9=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe_qu68HhagGJ3FWTnDatzrui0MuJa6wdsz9BKB3dzW0FP2QKC4valk7sA_z9neQNStzkept2MpHMkIMCekKEpP9NiS4XRtTMdLd1u0cjqZ2HHWLh5vDwNojQ9TMIyHAjfctGsAHxwnxE8I=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>kogumi.jpg</t>
+          <t>bar-el-boqueron.jpg</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TORO BURGER Bistró Malasaña</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1452</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10-20 €</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Hamburguesa</t>
-        </is>
-      </c>
+          <t>C. de la Palma, 41</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkOrrxc_SubrM6An5P6b54TmxEfo5XWtp7SRcUC_t3SSPtE4zlmCfVP90ctXrAiGvmpxYknTIQV0rvv80hJmdG3So2znAg7ez4pQJ-mAGN40vSE5RIFhV6J_xEpIlqYlTu4XJhZDfFbdfpM=w122-h92-k-no</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>toro-burger-bistro-malasana.jpg</t>
-        </is>
-      </c>
+          <t>https://streetviewpixels-pa.googleapis.com/v1/thumbnail?panoid=iJI2WB48mx5n7bI4nKLy-Q&amp;cb_client=search.gws-prod.grass&amp;w=80&amp;h=92&amp;yaw=242.00922&amp;pitch=0&amp;thumbfov=100</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>San Fries</t>
+          <t>BURGERJAZZ™</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>327</v>
+        <v>741</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1-10 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWliQD6qcC66QiWNiLuVPsApQDMNDThZL9CEzd61CeqREYzP_XZZeJzYLHdEwY9GoibQxU4llFPeeXzxvrXBoGRxbQ33p57NlkFTA2eCO0dEpRCXwEw7Tu3WB6LGlDdA6JJB2t4bpY0I42Fo=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc0Hz2eZOqVvOasFhekSJfYfDnJ-Q89G5yjplPmw_cK2NwRVarLwExpc7DVPaYOisOkJGkT8JfhxZLd6cC2glUHoI8oRRPuY11YSoCfr1xwby34CH-ETZ3Rc1hpmQyJvM07wGew=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>san-fries.jpg</t>
+          <t>burgerjazztm.jpg</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Tender Club</t>
+          <t>Gazteka Bernabéu</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -775,138 +763,138 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Pollo</t>
+          <t>Comida rápida</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkNbqQgA82izjyqQ7T3jh5JF62Ng2hg-dEKNqNHnVXivL_S8eIMIp1KXZqpG9PMEpchRCzvY1fIkRz0S8x41UbMB-Ei0MTzAcfYdkLjwWB5e5vcFvauUNt_aoswNqS8Sc72bT_-_01Qn7kr=w80-h142-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfatk6wK6z2esA9ASdBs_QxP2oAI7vnFqKjZcmyesKO1DXLbT_ML9C7R0jvry8QVcaOXWKa7FxEue9kX6rPArI4RSxitoR0oP5Ja4a9XUVQZJZzoAoAxNIUIXwyvfS10sqjxPyAnbX2Tij1=w80-h142-k-no</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>tender-club.jpg</t>
+          <t>gazteka-bernabeu.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Corchito Bar de Vinos</t>
+          <t>Pez Japanese Grill. S.L</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>424</v>
+        <v>469</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-60 €</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Vinoteca</t>
+          <t>Cocina japonesa auténtica</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlf4hIuCqeonBhL4_vnQQJo_Jgiq-7k7vzTWKaCzCDAjf7XnA3BsiWJR3MxLboWYuvAE11RU7lugXdr5VtMzM2VRCvlPxnEcOmsb0Og-UVMi5Vxcq41ofEXIsoZzEyLAVHnR2YG3Y_wfY6a=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeCsfpL7kWBvSqb7_lgYIS2gWKC2Aumdk7uG78syiD7OM4ImRwRFIdVTzQLZycpTe2deWhBVb8hF1lJmI9nmcf6FPtpIiog1FW23pvlaXxqNGDaxV4LsTIesntdcLMJaSs2SzHy=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>corchito-bar-de-vinos.jpg</t>
+          <t>pez-japanese-grill-s-l.jpg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>La Firma Tacos</t>
+          <t>IN Ristolab Chamberí | Restaurante italiano y Carnes Madrid</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>157</v>
+        <v>2486</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>30-60 €</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Halal</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm-GAgKSx_6pGIvrY-fwQeAgTVD2p9sDx_GO2h6lSDi1jqdGQtsdY0purM6EXE4_2eb4hW9WI37Qna9UX_ID3yT_7aTmRnv6vopSL3duzGg69Za-eU6JXePvYdjcVF0Nt4n_oTofbs4neo=w80-h99-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdnMhFUwSTIMrUupftlpAtrFlqDS_iVxUtSXcFHzZh6dktH8mT1U_2p_fuBPQHlJX_dDkiTqHrWOGTdkbCPdzicNgOKmm3ZpWjba5pmNDlBwPYGu6-y04urDrcQZgANy2Lt7xR5vXuPplvm=w184-h92-k-no</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>la-firma-tacos.jpg</t>
+          <t>in-ristolab-chamberi-restaurante-italiano-y-carnes-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>QIQIHARY SUSHI CHUECA KOREAN BBQ</t>
+          <t>CHITÓN</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>11432</v>
+        <v>559</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-60 €</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Barbacoa coreana</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmj-Y0JkO1DAbEGhlGxwJGOwsRfc0FHBkYvNEJoldnZYUzJu6r9UaD6iV310ywwUO0bphYlR-hzGChNkI3ZZLE1sYtFfRkguMQ4aq6FXp5Dud7yPZNuQOtkKjCPBOWgLU6YilbUyxVUb7EK=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcAkfBzj3Oo_qe6ehPjQ9g9yTP4X_xvlkttn8JaZgoS--VdsStaXLirLiEU7K447ORLz-ALMwJDqd2sLEZnATPNm8qCgKFtQvFlLahbXfNYNMNRRA64rUnguiC8gKa0OucP6qov=w80-h114-k-no</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>qiqihary-sushi-chueca-korean-bbq.jpg</t>
+          <t>chiton.jpg</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>La Notaría Madrid</t>
+          <t>Gladiatore Ristorante</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>761</v>
+        <v>452</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -917,56 +905,60 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnEr8EAJge9c1ZdTjKKMfPZRwValWIgMc7i4zYu_l8lT_3mVl_OORqlEA6Xqkp34yAThqRQ1uez_HNBqG2Qy-m6-pvskFQYJEbweya6RUaIQNIdTs_v3ZO2Bnc6IM8oYVNzyobwpg=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLedfHS-h9xigVn-I1vvXJ_Q3ud6fAvJhX3ueQTvuCciIEnGYyIWjP1ubnrxcqYDoUNbrha1nJdCqAjpakvhiMfPqO72u6X-_u4MPxNi1LP8o6zUSlW5BmoW7HGN4q4CdhapoJQ=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>la-notaria-madrid.jpg</t>
+          <t>gladiatore-ristorante.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Carúpanadas España (Chueca)</t>
+          <t>Kogumi</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+        <v>681</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30-70 €</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Comida a domicilio</t>
+          <t>Japonesa</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl3oebDfIzvKtgFU0MAh3HaOxZM7yYC5GSdVGqIbbXN_5Coj8DDm86M7_btOMbxZIi9Z4FzPog7GKa1Wgi9PMWata04BPesFdhlo5if8MMj8patB2dn3mVZB_nTEPfUK3TKVwjU0CRkhkE=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdVMDMxmssIeD9PrIHhT62hxjXmUswAqhXtCXTMeBXIAlQXlef_wTG5M203at1WrQbvCBo7SzQtwO3nVIeARYLPTy1VgMfI9XtKR3RJQY1tCh83JeXArLtgfJZB5VnPZjPPjmN6u8e_m9Vt=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>carupanadas-espana-chueca.jpg</t>
+          <t>kogumi.jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Mr Sando</t>
+          <t>TORO BURGER Bistró Malasaña</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>347</v>
+        <v>1593</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -975,62 +967,66 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Restaurante de comida para llevar</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl-3zeT25APhrnQP8E9uUtqf95Utk3aKQSUTxmqwAjN34VfiiXSUkzkT-OWzrSDMQY-eD_QEWx0cZC8w6MMA-UcHkHvZ3hyI0I5BIvXuqq-uYCpsMDymNhf2TI8aE7WFmBy4qap-GnuJFfI=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcGZnEWlngUPF6WwvGVSf54kJXlXp6pC1OR5MBlLPEa-YT13zN9Pufn6IfQNpwiMIAykry9YUa9Fu9OHCMYbaOIUxCDWKMoKWVAwGZPPTWTSdFhLr_foNKBIO_NiB-vmksSvE-ws1RQLKdF=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>mr-sando.jpg</t>
+          <t>toro-burger-bistro-malasana.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>DaBaobao</t>
+          <t>San Fries</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>131</v>
+        <v>370</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>1-10 €</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl4FpKh7AICaKjIUFMj5tBqb1sfmMDZbMqkA1_0UkfTS-X4ooPPGzyPkJwz2dI7FXi4EWfm_5CMyK0Wnan7PZK8BplVMjkwR7VFWr1-cRkR26PNfNafHbE79CT2HBpWCf14_eJk1G3QULmu=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeDqvmWjws8SkfgbkPmwP2APQVv4zQcoVbzDSQBl5OrLsg97s1V3dAv1w6o7cIxqihWFbyDHHVjc8okT2TLoshOLlXAlwgbUdldGDwoQ5KbELsILXAJGr8S6vAJ7TY6zLScYRXEpj_Euotn=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>dabaobao.jpg</t>
+          <t>san-fries.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>My Pasta My Art</t>
+          <t>Tender Club</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>19460</v>
+        <v>111</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1039,66 +1035,66 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Pollo</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkd_BuP-WkpM8ScXE57Z3RD5URopXudPGw_c0LmaRSWn3fX_QH65dPK9r2V5vmJsYuFGX1fYzdC59LEsbbl7wcPZtznjIGh62uewrXTIIL7Ac4uhQ0PlQiQbRieQsaLuN_V0h4Db-FKfEUn=w129-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfLv-DMPz6SSQc5iDUhNgRRyRj9JzbYtpFja46g02d8btrihU4Y0llXcxK_ubirWj1nighB-R-AzROdUEegkXXcrQlwFxOCaNj08atn0Q1VheETnlzsvTKeowjJTlGZkPrjHfReAq7CPdA=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>my-pasta-my-art.jpg</t>
+          <t>tender-club.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Roost Chicken Barrio de Salamanca</t>
+          <t>Corchito Bar de Vinos</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2861</v>
+        <v>437</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Vinoteca</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn5ah8Haqruhu7ysJOzmAwIvA45ZRrkc9qAEb9Oc9_q1S22CW8jngrohf_aCg0AN90gLWXYD-pxxYk8-NL78nzfPFis5RWvQg02-uMWmujU4eqoyyFkj2paFRkeT7uR0KcFP_miluF8uTH9=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfs85zrKK_oVBJaeXAqGMnZdMMjCXwrtabDpP87l9wAGI-nMsHr-2lU3RRx-FsTWVA7-j08QOEKxm-RuOmP2kV18OUtL8HBLAYKSg71oln0vzKzD_QaG3R5i7zeXHvJO4DAJfb6unVhXQn6=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>roost-chicken-barrio-de-salamanca.jpg</t>
+          <t>corchito-bar-de-vinos.jpg</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Nube Madrid</t>
+          <t>La Firma Tacos</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>566</v>
+        <v>208</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -1107,70 +1103,70 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Halal</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkisWZP9CAgvBBI6lOTokvsuc8iWJDx63mHdwNrqUHTVN-9HBxas17haCkcO_LQ5ku_c2ExK8i4lDkKhNvo_JpnJeWdkHuAJzSRARXaOCSKhnuHy0paoxmMH1Qo4Yn-JklFehenVwNbC38=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeF1foim7_wJVKDz03LBtE40ziRvkMitBcgNSfVdZQB0yGWiyku4rrj-XjuJF-whHiUhU6AfRgUFHOgG7KivNifOe6CaIk-bRMejTQOIdjDsJk-8TFpyPsUi9XYWcR6uK15-3_Pu8Mw96s=w80-h99-k-no</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>nube-madrid.jpg</t>
+          <t>la-firma-tacos.jpg</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>小笼 Little Dragon Plaza de España</t>
+          <t>QIQIHARY SUSHI CHUECA KOREAN BBQ</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1526</v>
+        <v>11854</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Barbacoa coreana</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkHhkXY3Oi7dQSd8mLL4_-qT1otCREc89WUbTgVuS612Uxc3oqqafEOtO-cuciXu_rfL3fIjPMdeh60f8tAmyRfZaGWrJ6w5lB4YJGlDohm_ntRPY9pHrAmrppu0iVxCpA6mNWoIdZmZVix=w92-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeZzvb4k-YMnMS_v9dvGy1QMnda7Vn62SawfIULvucPypOQrdW3KlRLFeC26KbPPp46aa7_yIisNCuhIxFK5HIk9Tq4XW-cxIA2DQuy89DHT_uMNCwVbbZoTPROMc99rTXvpMww6yv3gCI=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>little-dragon-plaza-de-espana.jpg</t>
+          <t>qiqihary-sushi-chueca-korean-bbq.jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Restaurante Varra</t>
+          <t>La Notaría Madrid</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2477</v>
+        <v>787</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30-70 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1181,200 +1177,192 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmdi2Giy1td-Ot-2bvUB0oe_qplDSOO2i8LYumqRmc6MmsK4TbJic0HlqPnZMZndGkSZbPYTpYpUslfkSbh6MQDNlCCyMWwrza8JvfGe-COtQ_V-RqOixp60oidonc5iYy5g2o=w91-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcjeBqItw7vE9Ir7gofBOmZlYxYmmKiLVRSTorp91YaKtPUc6x-ZA2rGrKhlstfc2fdv0UF4CDoxSr5whWCeR-HTlhHE31QsbKY_epXZrzdiDVOzmuexU9ocxl6dcT-ZpYKVCkWbw=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>restaurante-varra.jpg</t>
+          <t>la-notaria-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Taberna Nonnetta - General Castaños</t>
+          <t>Carúpanadas España (Chueca)</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>652</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>20-30 €</t>
-        </is>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Comida a domicilio</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlBNQiEpQlt2pVKyUPnVJ0teuErK93bS6ZERJyyshiG6iP7pWEz8rdnQlv1lLVR2DbwfKE8QvM8ghYZVZjLtpGsXnjrcRG9GMkyaHEi6JfJmDGOvtutFVjUPMYw8ZeIH12ihTx_=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcUHYSvQxjB8BoMHrDbps8iYFi4SPjSBRYR-gPfk7flBYqWZSrqYshQg5Vhsbnen6LvagT_2oIi7KsLX-kuBNcYtXWwV-bnk4Gv7H8CS_3SutMXMPTVMq_JTLXxnXNVAQl2IAAJe5M9DgQ=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>taberna-nonnetta-general-castanos.jpg</t>
+          <t>carupanadas-espana-chueca.jpg</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TOOM Deli Libanes</t>
+          <t>Mr Sando</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>138</v>
+        <v>356</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante de comida para llevar</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnRawVHcm_5aYV4jrJjVI3UiYbPscHl5pM18x1Rg4MQOaP5CN7rPGmhusGjgXyKd1OqAFt_KAtGpp9qnYyyV6lV_s-koe1beWeWDBMDi4fe05bz2dUblxYTKBfVKH6Es5z3rXrVcrAm_rsU=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfExIgLM5ZdLS2biyD9yLZvGCJkd-0ncpmp23ZQ4NA8FcZJpGFI6dlXveXIoh-ygRQTWQDEEJjxEHBwbXfGWkmPzxVH_mvH9EJr5CbckcyRcEqLyZGwUUT7TXtns6RGldUn1MaY4Tig7T3r=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>toom-deli-libanes.jpg</t>
+          <t>mr-sando.jpg</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Ni-Fu Ni-Fa</t>
+          <t>DaBaobao</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>307</v>
+        <v>142</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>10-20 €</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Coctelería</t>
-        </is>
-      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkY6ExIlVNRxE0TDdrqrMOWLsToGzc5mhcRTmmo3QspzN3EPG-s_kJ0HWY2eyVSgs_87TrsAl8ac4OqVtSS0NiUn7TynDRdUKDhe_n4J_tIABDHXGSu0DQ7cGFFjmH09AfZIHl2=w85-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfLCV3VoHjoyYBnD-TJz217PjhFA3yIOrhnAqZ1pBDtim53FpXiOid_Bos1_ZezXi-lQFjEdrtM3RJFQ1poBxcMe5oDblPmoKDjupUl0eQM3fEokbI84cX5MJqN3wv9DMFg3QizjOPVW32K=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>ni-fu-ni-fa.jpg</t>
+          <t>dabaobao.jpg</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Coctelería Salmon Guru</t>
+          <t>My Pasta My Art</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4935</v>
+        <v>19802</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Coctelería</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnUvsYEH822UCNYMQvmkn905JyHWteB7RsSe_NGFSiP9NogTE9o-GviLIW7_6heq2To9F9u923j5BPMr--Mq3zj46kMndu7_m3J4an3ycnhHds176amLPytTfiWTVUd4SSwmqU=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeHIYJsX0G1jmAyommjHgvgEQxL3Q3KBTKgqwTgG-x0pWAsc179nlvlVPgRgRRjEUhAZeBOajRYh23GFCxX5GCnMnsn5Zg5-Oimv8FzV4H2J7ncE6uexUlteYTZ5a_BSVWbwl9l2NylMOCJ=w129-h92-k-no</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>cocteleria-salmon-guru.jpg</t>
+          <t>my-pasta-my-art.jpg</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Gaston Wine Bar Madrid</t>
+          <t>Roost Chicken Barrio de Salamanca</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>452</v>
+        <v>3140</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Parrilla</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlnkCCLSMJX1A6ZkXqsxnaVZw6n914CEjlV38BG1sr7bMRyCfV_MzQUTOeLStH_2bRAzYROhV3SXDTBJnQrAJoYIr8ygyoB1jwyFJdvVMDRE2qvRntdxxtYdpZ8GM2EZPZFevo6=w80-h142-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLczgpNBQn_5oI_Uqwbhb-M-9f-39_YgZ8zl4lM_BkJTAaczGx7bVibKInkwtYfQq1EzzsmuIyN75Y22g20i36-Y17FNRN9E0J3g2gw31AVcRd9PBkoujsxsVvQDyAYSHO7IYAznUzDH8Wmq=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>gaston-wine-bar-madrid.jpg</t>
+          <t>roost-chicken-barrio-de-salamanca.jpg</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Marciano</t>
+          <t>Nube Madrid</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>416</v>
+        <v>632</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>20-60 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1385,26 +1373,26 @@
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmk0Q8gbhK4XLGSZN_Yp84gjq2DZ_NFkPyri-F5bEnm_6AwkY-H-9MYuPVsqKINK699KdeZ4ZzBi3QNxqtoXsOjqh55bAmx5jlFlVm7LKaCOS89r36sjRZiBkfjA8Nz_lAvbAx2sOicOg7h=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe9NRVriCIDo4upLR9P6RWoA6lQH38taZppGwjNDtAqp6KLvKoVRWDKh2GfaAL5vRmzdDIJS_lesVUHbXO_lfbyiGUx4tKxfAxKRXbiLNoLRyDVCOr9hnH_-qVBZUxllbvOWaD-hnsyOxs=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>marciano.jpg</t>
+          <t>nube-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Rambutan - Thai Canteen</t>
+          <t>小笼 Little Dragon Plaza de España</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>70</v>
+        <v>1718</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -1413,66 +1401,66 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Tailandesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlm4XzuGcMPUq9gLRi1gxetjbKPopFw60973p-9d0H6M0Dj-ngEARyHVZOEvIVuVIZpMmxbCI900J77QEQjKsDhqULVbHlU0KcwqJJuTivoPuAajzkUNoqcp3AkoqFn6OAtmbU_Lc0SSuA=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLd7Loc9sfx5Wqgq-l2jpKMux3gpURGsleG4Cg8DgNO9dG0OsxB0gApyhOq7bA0Bzp-pDW_-bFuxVaQBZ7QDGWYrbf3zxTNiS32WaIXJA29nvf2awBPEE3QkO6GKAGynl4XiOFr5sL9eanf2=w92-h92-k-no</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>rambutan-thai-canteen.jpg</t>
+          <t>little-dragon-plaza-de-espana.jpg</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Donzoko</t>
+          <t>Restaurante Varra</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3023</v>
+        <v>2496</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20-40 €</t>
+          <t>40-70 €</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Cocina japonesa auténtica</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnCw7pu_OO8x8TLqZDrsACWkPzAdUAFedVcNt8ubt5tL-iXDhPLNlj-W76mC03rqVFIE52FrxqvKbV1vgABapITRjF-iAXcp42fl1Aqh8NzzgKVyjGvrQTFhV3IA4eD2kaS-QZW=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeGCt62jhcfB3HhO1ZKUKcCcL_mXgDnI1zebuuD76BUBXhlbXxGFK9CC0G8pzlUnlAsl0sCr6BWV_7ooe--o3hj7RysWqzs671rvG6kpPQ8CDkgYi-g2VVwpl-cMJhm97Mhl-8=w91-h92-k-no</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>donzoko.jpg</t>
+          <t>restaurante-varra.jpg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Restaurante El Nautico</t>
+          <t>Taberna Nonnetta - General Castaños</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>4.3</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2518</v>
+        <v>693</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
@@ -1481,266 +1469,270 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Mediterránea</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmQ8ikwImCTt1cBgtRyQhENG6-2QykxRrxACFA0wivqYGhoy4Zm8u6AySmUU9ZZQLd7Dhn6mDWBAKyq49cyDLyE93rDFs_D4kBeRbDsCsLBbGVlZxLhI93RoNQdNhzcD52cO_t95A=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfePjEqkqqxYTsBd6E02T9m_sRUX-JZRWlrlqYHB0Iul_zOuyg4l7P29norXpcrFs9GJ3Ltoeisc9onlSvkH1nwZINWQ01wZ7iOLd5lLx-A3_0i7EXiEiYH7z-vTgnXEuMSaK5N=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>restaurante-el-nautico.jpg</t>
+          <t>taberna-nonnetta-general-castanos.jpg</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Em Sherif | Restaurante Libanés Madrid</t>
+          <t>TOOM Deli Libanes</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>589</v>
+        <v>234</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>30-80 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Libanesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkhYfQYp_VGbC4cI_8i1cVUZ6QduuNLujWYfiokTaou7wFSEUErtuZB4I77uzUmEG0FtPNdWonbC2zsrbxqCjKDR4MYZVz9f0zFoqvIZNAo9jdTJFKrExA3yyHF-HYAdTN4cvV4ozx_3wE=w80-h100-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfZUY2Wykvoy6VWDGOT833S-9-xmWJcL-OtTny5wKVcc2yasxc5cqZcTWFXuyYZcYo8wVOQsFb6sU6Cj9Qs82YVK1qkh_EFcDaYORXrLa4LUn5WaK61ENbMRoryiFMbnnFTBdDj9iPJAVmS=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>em-sherif-restaurante-libanes-madrid.jpg</t>
+          <t>toom-deli-libanes.jpg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Yothai Bar Restaurante Thai</t>
+          <t>Ni-Fu Ni-Fa</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1662</v>
+        <v>312</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Tailandesa</t>
+          <t>Coctelería</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkfyC4CzI9Zu0URaLokK8L9MI_8TACewdQl_LIs6G10K5g5S3N9_RIJGOE4Fo2XatA03mkRPWqyBHgzIdi_t45g7sn_ndSYh0RYh-sSz_2WPru3PVsHmH2e86yDuWYa8KrFjgiI=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe1qe8OwlurOdb2TKAj9ncM7k0HPjNxScPeaF7VDN_QTDyQlEi6Jc0GkjmuVMVwORSDR8cz3SAlJqxZ9EP06V7j7XJI9cvZGe7tOe8HskXsqmUq8EHpADpdQygg50jv56QsFXGt=w85-h92-k-no</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>yothai-bar-restaurante-thai.jpg</t>
+          <t>ni-fu-ni-fa.jpg</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Santo Dippeo</t>
+          <t>Coctelería Salmon Guru</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>4.6</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>194</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+        <v>4975</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10-20 €</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tienda de postres</t>
+          <t>Coctelería</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmCPLJADlJX_M1DyFdcpBfzhnu-ug8dXSJR0etbZJ0Ot4XarBBU0z7fKBkfZH6lpx9GAHHUpVqhVWzb97hpyTc-XGvlbBHOiYSlq5cqDha-SlY3vdRHp0VY-VH7RcAx2v2l1MuW0y-bgHLZ=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeQIHNtEqh-tbAxkCNLj3_K8x1oEUvyN5kEAgIP0spLIjQjVZPbZFs3YkoSnzf8V0XkHaio_LEa8KFZ69m16tDLmmH9QRX-0LyvJv-BXKS-jSLb9cqc2vPI5_pFoq3s43cbQlk=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>santo-dippeo.jpg</t>
+          <t>cocteleria-salmon-guru.jpg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ConCabeza Taberna</t>
+          <t>Gaston Wine Bar Madrid</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>195</v>
+        <v>464</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Taberna</t>
+          <t>Parrilla</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmUOp8ST-KCzvMCboPkZnPCdLtK-7N2bpGzwfYo37W2ZIXV-f2fazSnJoyAauBpvkz7ucY8s3P_R8Ui0E5N9iUPiHr5IC-1n7V6KObIqb3bTcCgHMWfUe5Z_eIEJaDSViLCJCP5=w145-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdnDj7eLnO1tDP5Cu_MwUeEbuYNX5-f5wnlLihp1pG8Ju40yDKyW7W5KbrJK7aHGh-7gbz3cXLG4dUSxrmjkwNW5fyBCwaYk-4L9FgjWFsVsvCEVA9MPfdMVb4rX_g5_ErsuwKD=w80-h142-k-no</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>concabeza-taberna.jpg</t>
+          <t>gaston-wine-bar-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Taberna Griega</t>
+          <t>Marciano</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>2337</v>
+        <v>463</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>30-60 €</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Griega</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk27Y7Vpu3S54ik9krMdvdkA8oF3ovWDKoU1n7p80_2-qSK2Id-WKyQGvSLvUYOnTMJm9wB3EM862oVmHcfnKJHg2tC71d-9mLEol3LgO3OoErTEWenSOp92PR8FySfFRfFrK-A9xMHI3lw=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLd0I2d1oZS3__PPu5jmRgFhnr-hDgjKoiEbAZxwEknzRv2HeSKRgt26E7nLNcc2lCXqJtMvVswqtrd5pirl8eRS9xly4VkIPOLyqeTTsY_Eg6tNr2kHyprMGmucnxCZzcd29t_sSYWdkpNK=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>taberna-griega.jpg</t>
+          <t>marciano.jpg</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>FU CANTEEN</t>
+          <t>Rambutan - Thai Canteen</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-30 €</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Tailandesa</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmxglAiKV-9DR4uYKUWuu4_9TJ3-rRImBmIfV8fI0abPnv03EpeevrZldJH3h-GA2wBCK3DWBFNQtXbNH-jykwLf48hFud7AOStLGhRCr1PceXvVXIXAObwys34eSQJRUL3TNUavx9oKqQu=w80-h99-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfTsIy_OWhKE0I34qt5oBt2wuUGjbAs_tf_cNJ9MH2vZahQt1hIPVnCPQKCFzHSWWc4-LXOmkv8RvwsAjg4tJ-pb-P3PY6uDUEUlDstjjWXKrUqDevJCFbuwBV5bkguATp5ruP6E2OKMBs=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>fu-canteen.jpg</t>
+          <t>rambutan-thai-canteen.jpg</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Treze Restaurante &amp; Bar</t>
+          <t>Donzoko</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1958</v>
+        <v>3066</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>30-60 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Cocina japonesa auténtica</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmjNTtqWfeSvvaHQF_tTYm1zaxYNl5r6lrcRKPwMuB6S_Be4IpA_gWJ1htpyrmXdHHuyhzYY0UbiBK1wCUtVuKOXOlqrNtviJwCMFGWIcWWqtLBDRVL7G2Wxhj5llqyZHbSakas=w164-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcHXhy8zusVKHnzmxwq2E0JKilwya6VN3fUWAn2zcsuCIIeJco_D0etz55Bruj7zOmmKXvIyA3js2yNB3t2YjLpp8kn_5MtP00oGr-Ja9nSyrx89bYe1jVbX5Qi-Cd6rtuJp_hu=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>treze-restaurante-bar.jpg</t>
+          <t>donzoko.jpg</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Taberna Tempranillo</t>
+          <t>Restaurante El Nautico</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>4.3</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1404</v>
+        <v>2540</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
@@ -1749,134 +1741,130 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Bar de tapas</t>
+          <t>Mediterránea</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk1ZKvqvv2h_sEVE_CWGc_wD-mbLAJRYB7Yq30_1YVt1NwR2vrwtrhfvmycjDh3f_XZulW6cgYUrBa3rlpMjeVIiZerTOzQMinTB1Ora2UACeNngJ6RWgeQFvHS-phRuAxHgInC1XS9kPMo=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcwjqImiXuWcMFrR0dkbLjgq5QaizJYQHiNVE8fU6wqhYT99mkf30QupRnosxJ097soSi2jXTQBaV0UtLOO0pVm6QMprPuZPXrTgRUS0y3Dd2aFTKiGMaTkS4pgOjoBlKdJmVd8=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>taberna-tempranillo.jpg</t>
+          <t>restaurante-el-nautico.jpg</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Origine by Salvatore Romano | Restaurante Italiano Madrid</t>
+          <t>Em Sherif | Restaurante Libanés Madrid</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>777</v>
+        <v>663</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>30-80 €</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Libanesa</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk9QvvPBvPsUGBJQ3HBa7zqrfzJX7s7Gz-A2DSO-9wRJiMqbPqkWGXc3YQLRm9-o_se2OdxUeobAV6OfbLoI-cJoLAbLX4I1WuZmBjRfRLbFb2ZaI8nRqQfseeM62tJSMwACMXywlmn38VS=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc0Ii_KmLb1o5WKx5ot_GK4JbZ8T88nI3lyqM7zFdegk0U5Kocx4BvtVusdC5lO0HOzCSFBUsuoEFyodqS8SH-CQ4LY93ZE78X15SWR2XLNJDUerfxS7ljCIeuJZlJqiBZsTiysPk-fHLE=w80-h100-k-no</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>origine-by-salvatore-romano-restaurante-italiano-madrid.jpg</t>
+          <t>em-sherif-restaurante-libanes-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>focacciamo</t>
+          <t>Yothai Bar Restaurante Thai</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>684</v>
+        <v>1682</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Tailandesa</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlLr7nE9Jsc3FHBP9-Ntg5JbHH_6NPBy6DMHMblF8m0R0CkI2G311Q84FKPFvsGcA0GMv2FmRUg6hDBm8G-n5VdnFIi9oNcW6ljr1q_9zy9586n1m0u-s40X_14IBQPo7zeKP4CnpX06v8=w98-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLftEjMBXf3PZGr0_o2VPVIpyhN4QEDT4pHaek5HqVEQvhJFUrijpZk6OFZCGN_9HyLlrTURedS93Q_OYlwH2YGbZ1IunvECVpLZor3rKcQ_L34MvYOWrfbTESPrXVEAX3JYp4nN=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>focacciamo.jpg</t>
+          <t>yothai-bar-restaurante-thai.jpg</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Pizzería napolitana Rifugio</t>
+          <t>Santo Dippeo</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>992</v>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>20-30 €</t>
-        </is>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Pizza</t>
+          <t>Tienda de postres</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlWcnKG-qIpU01KKny__xDUXCmG077WP525QDx4XLOygo7mtDgbKyVw-fLUZ0_yig4CDiObc1WLYg5E0xaIAeypfO5xlNIQMQxsljwyJBsKM_bnaWbKxfD1UiED5HUeUYj4jE4tew=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdldtLWmYMkLhoSD1AW0Sx4dPndzBbR6dVDj5oiD2xfqODLKW15szwmFnOvQwGwm5ynxlwzDb-S0-llNpubhlHUh-8Q3NojBz2tVc_3VcupYFUJsaWWjcs9YrxyQNaK3NIL6fdevimG7tWS=w80-h142-k-no</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>pizzeria-napolitana-rifugio.jpg</t>
+          <t>santo-dippeo.jpg</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>King Sushi</t>
+          <t>ConCabeza Taberna</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>447</v>
+        <v>220</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
@@ -1885,66 +1873,66 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Cocina asiática</t>
+          <t>Taberna</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlV3j5B8mFPlxcDsVlHDyFEb0vjKso2C2MGbpP3eIxOprzfS99gh6QqDZaMHpO61wGcGmDoWMVpJrGORje5Uj4oAcWq9gC6dsiWhSrWVcjesYvPCxCxVpcSh5DM779y9c8TffMDa3mkUZVc=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf8PiM2PUvme-7lxbXRLe38Z8hw2iWy7GOpBPxpaqvzHXM9CVc2_hKW-y--EX6M-RA4mr9OliiOZeHJoD8rBlBDAKwHndT4ywoA2gbq5K-yTIHx0_ogW8Lng1uOmvQUNNlfQdZF=w145-h92-k-no</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>king-sushi.jpg</t>
+          <t>concabeza-taberna.jpg</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PAIPÁI</t>
+          <t>Taberna Griega</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>2591</v>
+        <v>2355</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Griega</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlTNvdXadSkJ_d4XyV-qQGCLO5DgnvIeLIWaH3S-Ha4jrLJzGg1N_qn_yoImBqEU2LL1LULv-kasUo9vqrYpNEhg5e_Jrv_9KK6GgR7AzH97s01-X_9BvjBf54lN04nemKlLGqYGgy3cksL=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLexwEm90QeBq50ao28J4rm2_eZS1eK-17ImYK9vCfkDzuIfw-gkyAYg2VY8owT8Kn4uJDSirvTN20NNQYzN4fjEV049R8dcH-ySZZ9x7lVhnvPCVOjWjicTZTlvDfh40MoYmrZz_n3sMruU=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>paipai.jpg</t>
+          <t>taberna-griega.jpg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Bar Serranito</t>
+          <t>FU CANTEEN</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>110</v>
+        <v>169</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
@@ -1953,138 +1941,138 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlOVj-9SFQH7dd0UMPSeEkH9TvOzYYKg_5uFm8MEACAQikToPp4xVJsHZ46LCWymiwNcV2yJ3eTvFUEXYxzIBBg8KPbrdh3heSAbSNk1oOhavq2PpnkSznLTFl8_Xs5k-dVk1GEr6H7cVc_=w80-h119-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLevyrFroYSAQUGCi_rG6PflsdPHCZJRiZ80LgMG992mIPnxNsVimcKBJyPi5uYGCdTXzo57ItSFZXTjJLDykUTAtSs2CZRTo6qctRpbJOoO07Ovyf1GRgz7I38ZTAEyXmfaAejjY_33t9a7=w80-h99-k-no</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>bar-serranito.jpg</t>
+          <t>fu-canteen.jpg</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Terry's Bar</t>
+          <t>Treze Restaurante &amp; Bar</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>3332</v>
+        <v>1968</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>20-40 €</t>
+          <t>30-60 €</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Bar de tapas</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlKHTaJRabiMzSQEPClvsuS5-Hlvd2MrqL7wb5lx_ovoXFXYsD7Cpp3OkLbDNEg0qvHn2oAReAfli_ZvG7xKczkFxmUV4Vflblcrl3t346oVz4NtcVdxuH6VCAHAqDRD-KO2_xNnY4BZ7oM=w92-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcRabUDa72vv2M7izciTDflxsGjllPvTNOTWOnPx9hbZDOo7qvLW3H4PdbtyAxLJ1GeULfC42xNkNBM34eSQhg0JFIil2I0XD1Oktnx1j1AREa-ZUU7wIPK2GnV0vviCXAJOFpE=w164-h92-k-no</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>terrys-bar.jpg</t>
+          <t>treze-restaurante-bar.jpg</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>AskuaBarra</t>
+          <t>Taberna Tempranillo</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>1174</v>
+        <v>1417</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>30-70 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar de tapas</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlE7osT86fCOxIqk_sa3L8_4T4hI1fVgJmvCzrnV-5ZhfP7s2au62CxgDXkUOAWqn2iTjXvFc0ybOJ3S2VbOuexJyUEr_AOI-RD40RToFYOgyoTdaukY_wReBiVnVTMzaKKxI8Bkg=w80-h111-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdXD78pDmw9y2_cmApha_GINrLxvENgGyry-kHXXCiFMZBjphuuNsK8sBuS1KEKsFCtRdfqGVPa7RzhNkUKUcFvE6nwRa29eJTYq3V__ISnzem76KhlHLYlQLLR6yRta9Rv2uVshv31nmIe=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>askuabarra.jpg</t>
+          <t>taberna-tempranillo.jpg</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Sushi Tairyo</t>
+          <t>Origine by Salvatore Romano | Restaurante Italiano Madrid</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>6205</v>
+        <v>865</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sushi</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWme_a8-dIKs_E823qJQlmIusGwdnOSktBCRyAaXPNk7l0eXaT5rFJHafDJ44nVyZxGwIBtQYhjFo4izvBlG57nQR9mvm_5qtabM0gJJklkKXk18Iv7_3AmOL2HJnQZMKoz6JpTniJnuuRnE=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf3Pz5lyM3S5ZO2RsInmeUz5HxR9BL2A-3MkGoA4F3m4mlJqoX28bNyql8m_1XxHCNy0mph7avYcy1e0CS6COowevb8AcooSVwJMVjPqbijNmOJI-rO02I0rwtSt5gqFP-N86R_iZxpGstI=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>sushi-tairyo.jpg</t>
+          <t>origine-by-salvatore-romano-restaurante-italiano-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Claxon Majadahonda</t>
+          <t>focacciamo</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>462</v>
+        <v>698</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2095,26 +2083,26 @@
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmp0Dq5wwAAqP047Sa9lbRQGMhMlFF6PoKOX-MthEAp2ElqzNzcDJ8BGTWU8yyCPCGgkyhc7zOpUaGXj62aHET7RevUBJsdgGN5WPazJvIIUANcQ7UP7w7MNDc4TknZD5lIcBI=w80-h166-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfOGGYIGA8ByGFAqwDkAEIlM0F_pHRIDXNqkMhK3NOZsDkf8fa-mmr3wCA87oWzJLa8suNFdN37K64yx7fnwDK7o5zlGyPbVqCrD8SzbONk6Aq_jK3apg_jehhSky2pAQXB2DWTgafY1S0=w98-h92-k-no</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>claxon-majadahonda.jpg</t>
+          <t>focacciamo.jpg</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HUNDRED</t>
+          <t>Pizzería napolitana Rifugio</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
@@ -2123,70 +2111,70 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Pizza</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlqvuWyMY1fNty2AxogW9ubwCTp2R-Bl5Yt4d_JDDbZ37uERgnXING_F7off_8Wchse5FF6-_j51sEGpQuPsVtX4ZXkvj12RBgTqAsnTDCqD3TqZz4QVHy-zM_F07dkJBF3mI480yLV3rMq=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdnkeOn2waSRpMSzabCGqF-Cp9j0xI1FhGBzt42Z7IK_BnII7KtI84KuHTxr4ONyZzAUpASi-N7Hek06RoLA-8fTizaBXXOX9xMQvnjN6oOWnqQipdyyScroxatPXV2xfA_M6k0RA=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>hundred.jpg</t>
+          <t>pizzeria-napolitana-rifugio.jpg</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Restaurante El Ochenta</t>
+          <t>King Sushi</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>2636</v>
+        <v>482</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Cocina asiática</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm2Aef8Ar-B0N9kVoZfRtMeKdkfSU1Rv2E0pXEIaRAQVcJT_y5paz6OHZWCn3idoxB3S-H3r6i7DS74CmL3OkR46yj_EAdNxo98UWq1XQfqd2y6VHk2D2TpwG7FJcg0A8JkrNlS=w80-h105-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe9fzo-Mhgcsvl0Gt4QtRJm-Vw3A4YysP04sbZFGzSI5PXOzu5kgQ2syUDBhweTaJcImubcAfpRhahJGxUXnDOOW-4-aN1DSziRpXTYF75r6QeZrL8sow_InfQjM4ghFilL2UEW9UkL12yg=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>restaurante-el-ochenta.jpg</t>
+          <t>king-sushi.jpg</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>El Viejo Fogón</t>
+          <t>PAIPÁI</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1420</v>
+        <v>2609</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>30-60 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2197,98 +2185,98 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnNFE3zupO5sonInSOkuDnY4rJcTU-kLvcYWWKwHjAdtDXAK-Be4FTIM4XPOXKpYxcCK5TnUp-09E3vvVanTUWBayeQKC4rgyGLV5x2K6hkQy6TOh2MIr4Pkfp9auhGSMD0x55902YnzwgF=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfnwcLKZIPBSEzBLFs3dA8qauCWhlPy8UK68Nv6-GWHrCue__7ZoqbfDhbJnLvub_RLRAzMC0E9YLmDF04QnXVQugkwpuw5XIEgU0XpltdJUyEpiChXIjsi4gV5L0tqZc1TQ_GwFBkkZMk1=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>el-viejo-fogon.jpg</t>
+          <t>paipai.jpg</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Panorama Restaurante &amp; Bar</t>
+          <t>Bar Serranito</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>3872</v>
+        <v>147</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>20-60 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnsSbvWsmT9SrN832ThhsbKmJ8jCssBoRr01x1UZt8hfkQ4J2zkvwxm4LMhlntvoYZyZe4gAz9dfI42rfQCcGnQR6_w6tYW5oKpmbxF5V_mumF3nP3JmlUPxOuep7w4uNcULmMf3vEZQk8D=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdpWx2uQgCSPqwPawJXQpgCTjPdp90MmquUvwb2lrbTlMOxp52quRSvIMaImF6kl_5ef4mySQa8hXouaeYWSRkNqMDo8W_LcxJ9tfxm44lYvUax5x5n0HcJaK2IOeJX4unzTO4OOPktzR5I=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>panorama-restaurante-bar.jpg</t>
+          <t>bar-serranito.jpg</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Toque Restaurante</t>
+          <t>Terry's Bar</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>1123</v>
+        <v>3380</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>20-60 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar de tapas</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkAocObmo0dPpYGdkGASwS0WpZpXDCvhcih7kmsPugAUzK_GeHebA6cqMPIfhtzu2Yz-ddL8ON2A3gUKpf7Q4Otkx90BLWamVflVXBUbnqyWjMYkJFKXnQ0hKpK6x-TCeZnmwJB=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdyyLKC76v_n2d-BJ2tvwVaK2FjbVwhUkQihEqhHtbDNtTxTpDUF5m3VJfOYzaQjvBsOwrWASqwhgLZRtwDfPUi03D42Yyg6xlO0xcXbD9__iJ16aWkwhXjW76I6lNIbZZKQr2eAkP05ZtG=w92-h92-k-no</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>toque-restaurante.jpg</t>
+          <t>terrys-bar.jpg</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Anónymo Restaurante</t>
+          <t>AskuaBarra</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>2610</v>
+        <v>1177</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>40-70 €</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2299,64 +2287,64 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmSdvYFozmJneo7atba5yrADFNNeMOzSE-0hCt0l6zwPMuKF0JebI8nyX_kgLrvXwMRMB5hYe5bvI7LL3UP5Q7KBJvKGehgG0Rd7d2ULieoTw4XJOX-1vKSxJLmSsaWqqKzAk8e5A=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLewM8yjrVtCIDUmMp1DAAKKwosqAqrn1t_NZz-1iSuaRpJpA7IsGcmpDmgK6L8xzlaXppNGmr5JeBvSUhMw3liZxwXCrFsQeuN1cf4za4F7j4J6OWtQYjz51HBwoo-0b0sfgMbomw=w80-h111-k-no</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>anonymo-restaurante.jpg</t>
+          <t>askuabarra.jpg</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Caiño | Wine Bar Madrid</t>
+          <t>Sushi Tairyo</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>578</v>
+        <v>7893</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>20-40 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Vinoteca</t>
+          <t>Sushi</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkRged6vZfwV8acmz5sANZsjQdrWwTfOUC9tptiypFYrkKekmFuTjnlyZRN7AzQ51sUCrxPiqeob5_aNjSu4ikxKVd6E1tIJ-mT5b-o3-KQdOstxRKlnFo-mm835Okp-JrdhKF8rhFvFak=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdKx7miVGNShZq6jiMRqHWFwfqKkidI1Vzc3gL6CTCL44tnEg2edl8k_MDS6pQCLVD0dJ5aWtNuFEv5Z5U37etS8OhFThGFn40hxGni1iwNrSad7JmFjbABhrFLP4KjoF7yZBUcVPxYO4PJ=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>caino-wine-bar-madrid.jpg</t>
+          <t>sushi-tairyo.jpg</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Manifesto 13</t>
+          <t>Claxon Majadahonda</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>680</v>
+        <v>474</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>30-70 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2367,26 +2355,26 @@
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnLU5fDW4gCa7K3ogMe5_YUS68pQxnKLDfdZ1X7KjlTaDJN4jf1Aum4bvpDO2mE7i-qRCLRPdvOS9CXdULy1_zp-8RiP1RS0WCdu23dCtmQbSQaHjpBuVCsV2pjg08b-NXA7B-k5iD9Ehm-=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfxcDIv_DErcPHGwLsgNTRrdSIlCDu6KafxCG8Q3SW1sNpolQHbSmbOVlCYHd2b7ks19tvb8KxV72vrqkh7j6B5A_uW1lZmoZ4StLPL7yX4USYgFNAgyuhv7KsXAS7aGSTb-wE=w80-h166-k-no</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>manifesto-13.jpg</t>
+          <t>claxon-majadahonda.jpg</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Boom Boom Ciao</t>
+          <t>HUNDRED</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>8969</v>
+        <v>1393</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
@@ -2395,32 +2383,32 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlP49Dp3D7ZPPtDQRyL1xpQayqhOLcQXpvfckXy-o8PTKi6XEbqpafQm5pLU68ClytxsiyDDyjNzzi_40C03pygKqEaDyVUXEuRM-XO7rdfQwgP4dOCZWww64mXlI6a5CDVi50cKROQHLcP=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLflpiD6RTbG36sDZzA5B8f2geXV_2LjneI-pz8IA_hxONBjVXZ8HZBP0NYF1BNt79r6bUAnEEJ-K-06RsilWQqyKjyVEhGrfnw-dlMxMiZ7HYC3rqWPRZKNiY38AYI5HDLYpTtQ8LzyBJm2=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>boom-boom-ciao.jpg</t>
+          <t>hundred.jpg</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Restaurante Her</t>
+          <t>Restaurante El Ochenta</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>5718</v>
+        <v>2649</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
@@ -2435,264 +2423,268 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlwVBMO-Yg4m23n5QU27_ywwLv6MjbnwpdAavuS2alv_NbMlC_LWP-GOQkvSsXN4i6ac88fhm_SrF41n1zCDcew8ppzVjf3gRuDB7CBm8yDBF2qfmFziMES5hA4udUWxos5z-QxMbWHQ8k=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfdeGbZVp1MuaCZObvp_yeLmzAUGL8_4OPwR1Erael8PO2L4AU7WLGc0UiktwrjEhe6_F2tdrZ_6Qj1_Tz9XUrVB7LA0Fp8B1hLCCIAZx-dwwJG28FslFOfRbHTsWjR9d87c7Vw=w80-h105-k-no</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>restaurante-her.jpg</t>
+          <t>restaurante-el-ochenta.jpg</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Camping Osuna</t>
+          <t>El Viejo Fogón</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>2617</v>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
+        <v>1427</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>30-60 €</t>
+        </is>
+      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Camping</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnRrCwFHzIvMehS2tzHDOyc_Vk1Lh_BVlxUKTinG8qViomg8HoiHRCrz0J9lJ4n-MTOCjeYnzLby4_rETR99WtIOzhG01Tc39fRfS5Lgl4E1sce6-vQfKFQBFYqIr1BTpD7dnuwag=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfS6a9ig-DlukwPP--mb0n_qjQJ7frZgjA8O9tLn_-UfLXxGaLwXTdQ7WeHQLt-ax9JafahSGTwWpSa_ON3kYhU5bmyzv5lPb3PCjhZH4Tb_-inDpkHMGOhRIo952JBfPQZfUOxZnx8QXWe=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>camping-osuna.jpg</t>
+          <t>el-viejo-fogon.jpg</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Bella Napoli</t>
+          <t>Panorama Restaurante &amp; Bar</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>559</v>
+        <v>3953</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>20-60 €</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnFRqNqk-V0i1f_YJ631kNUUilPJliAiqPNV5YCo2fKdpb6o-hEHiq1u55pY5f_6zz7gi0c3SQmkrlhKh3ZgreMGXWtvY_jkRhJjhz6oghv_4E-pooUYGauMCkrfWFFa7k-hfSw=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfjJBsGkQcejRPpZsaZ6MgPbUFGrOpi0C46IChgZ2DR8NRWnn9sswUzSiH_sMrrYrmlPlJGu9pRrRtHXXMe6cRlLChdq9dL0DNI_G1dR2v9zdoYeYqYukFeXVXSCtxec6FIfM_iYoJW9L77=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>bella-napoli.jpg</t>
+          <t>panorama-restaurante-bar.jpg</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Baoyilong</t>
+          <t>Toque Restaurante</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>994</v>
+        <v>1127</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-60 €</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnlsMGELEWE9aKdFfKyu7TBeCCW8L482KqEyQVWeMb14jy_vNqEiIsi_8aaqP16NvIbqnim-Fod2BEZYQWhxjcYt067vNUR6UM6BJW_E202vG_USQ8fBP-QwDIQswU5_dpwEKJPaSeaJ9Ek=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeR6XuvB5yJcFtp-mJJgcV_U4sOIecz0hySl2TkoO-GPo7k3OrU91siFNNlHiWYJTmUOvYBzbmzlKbV4g1ynaw0lp56RQtb3d-WgV10O2PQXshBf1lJ4KIPsPB8taVEb-_m3Ga5=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>baoyilong.jpg</t>
+          <t>toque-restaurante.jpg</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Street Food Burger Madrid</t>
+          <t>Anónymo Restaurante</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>1288</v>
+        <v>2644</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>20-40 €</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm7z2Nyg2ftwfln3bBZdLnbdS9X-pdxvp9_vMWjzBk6D5csgDaRjSKiXMUsYsT74KmBE6T54VVUE0GCmcuQQwtrr3JZbk8IzSQ8-8Ez6yO08qZXGAHxpls7lnVWKzWa9hk9usYrDj-J0Emx=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcOR0QBWeEn1FOfmF2Fn6mIfCYqcKOWXsVOETKrEdxWP6u8ECrMiSuqVJyxcU6h622bQU2QxdgXKef_4D-ayo_Zg7mq6B5_9Ix0qprKd54K2YwPGeEmnVQYnOdUqFIX_Ipcuitr0w=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>street-food-burger-madrid.jpg</t>
+          <t>anonymo-restaurante.jpg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Bar Gyoza Go!</t>
+          <t>Caiño | Wine Bar Madrid</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>3339</v>
+        <v>606</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-40 €</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Vinoteca</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkRg_1Y8J9uHKodHJfBShMqAP3GgTDFrbXYPUv_608i--0asMtC8sPFuA12q6uDOVK1c4c_i1NKMHQNYDqS7gvVS4w-dD9LuMw4jnMozUPPeK1AwbOiJfWQxdRt7cJIKvzAPb2Qlbkcouv2=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeb1g2hSICUY4DPa7ICF8pn-bb7JmLBhlm5bToBmAq1GziA7vAZzC4MbWGiuEGbEO97rNVLzc4Oi_7zSaGMlgSIwLVngpAaquq79m473KqE2Wbuh1StffxnGOLiekuXTJ8mpOs4XRJVDsY=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>bar-gyoza-go.jpg</t>
+          <t>caino-wine-bar-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Grab Sandwiches</t>
+          <t>Manifesto 13</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>381</v>
+        <v>707</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>40-80 €</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Bocadillo</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlTZGf4ze9lFibD27PYW_a1mC20CfzFkCs3J_tV2NJ2Y-6ivi5Uugj7-avuI463g_cZWe_h_IVHYjkl-QercEs-uojCHJisNBQpv2OHYPmMbR6gUt-FaiVh6w7KzYxAQ3ut7oKXcWgiZv4=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeZUENnOwTZqbwEjgXSGC7dnyTpeWVw-hjJ5vLBlUQ6ClKt3nTgh2oLzXB4wD6dO3KjJbj5NTkzX-wShBrRPl6sMUQFzivnTPVLwTtQNmSElrvnacrWDNotTq4vjsS2UsI2n1bxNZXhLDxN=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>grab-sandwiches.jpg</t>
+          <t>manifesto-13.jpg</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Mami Tacos | Taquería Malasaña</t>
+          <t>Boom Boom Ciao</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>4101</v>
+        <v>9316</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Mexicana</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkByzZcBkqqx3Az2VQwQVP1nCeAjkNHtBMZs54G9kPnIENtQHq2OjJDRD4Intr3NK-8UfbMGMJaw03Qvy44HuyM930ByTgtSc-JCu6SNQpN3Mx8ShXfSvuG4mdIWAyCuUqOmphR=w80-h99-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf5k7Cr7NVcEzW_Lv8M34kYaxIGW7nkwChoTCZIq4E6GVn73HrX10z3wefzIS4lOgTzBSQpdDK0sRS98PVkUgdsayp4GWEylcWKVZEkwoWuK-FjcbUkocbOCn4dqaYct5sHWzdb2b6Vhgth=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>mami-tacos-taqueria-malasana.jpg</t>
+          <t>boom-boom-ciao.jpg</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Baovan - House of Specialty Baos</t>
+          <t>Restaurante Her</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>402</v>
+        <v>5862</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-50 €</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2703,90 +2695,90 @@
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkZx2O3GuBREi0Jzfprb6lFJ8h1iZq3Fmgbf0npBv3jp7tq6u1H3IgiSHCAfwDMz23XCb_lA0ueYGWfm4lVN6a5FjeIsEPzH1WHXt9ZnEmrCryYqZkBSlvJrxm8ot5nmcJHjreTgyQXheqn=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdLxFSGfJpjVHaFUGW1ydYHQOHmH2-Y-2BxKhMQ74fF1dCilROfhFJ8heVRfIHDAu1G_JE1wXZHmjBpdFUfDA7lpkCXD84Em-O3YI6oYplNOob1A_D3rKDm0Q9McNCkNMoEwS3I5Hqm8TA=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>baovan-house-of-specialty-baos.jpg</t>
+          <t>restaurante-her.jpg</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Diurno Restaurante &amp; Bar Chueca</t>
+          <t>Camping Osuna</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>5190</v>
+        <v>2638</v>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Camping</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnwbJiPMNL5ptMl6iCjm1WJY_B3ZXGEMD5HHvhWjkoctcIIo6OLWdHhvRXmpvLRpSEKhdHgz3d-1p54X9gW2VuLv0teF1-68DZAwGQaqgqu5PkooPWx3x_PxajLT28vrO0t1zO-EIKE2VzP=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdHKpju2U9wxn4UpfIrJjPxU_JncLO3LNLCaHypml13UuV8y7hBWG3CMwrQXZ1MnxhYmiRNMHGPTAOcMXMhYS8-VY6_JL5XANVofZLybVi_epNPcn1tot-8KKW7h-H49hWMNgI3Zg=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>diurno-restaurante-bar-chueca.jpg</t>
+          <t>camping-osuna.jpg</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>MANEKITA bar y restaurante</t>
+          <t>Bella Napoli</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>255</v>
+        <v>567</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk1MCs04BjRmBatN7S3P1K2KH1vV6TJkWrQx_H1Oy0egqYJfVsiu4SB8nbRQYt3oz3CRHbCLX-fIAWe_Gz_kkFBXbl1xeaOfhiB9RDGn8GS_OZBNF9xpQDHl3bCMfren1xiADI=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc9OOqyEQOtjoPmp7pFkSz7IYlxbgQywppVA55dSs48M-T82J1ifcNU9I23MP7wrTkjqG3KJnHhE37caFBg77y62hch5wyX9nkasku_OhJfWrZ-hMggg96mrrJlfRZvx4P_kdj4=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>manekita-bar-y-restaurante.jpg</t>
+          <t>bella-napoli.jpg</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Mandrake Greek Street Food</t>
+          <t>Baoyilong</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>1222</v>
+        <v>1046</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
@@ -2795,168 +2787,172 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXX9WVrg23tR2HOaoYtdoT4KhmAhUln4Wirmkid4JvAhgU4edss4bjhmZZYGRkGLsz8KuyeA6u21QoHXtwjQ6Tp76LdbL0NJF-pOwSmqKm36c8DS70vs7QGL-y6FLZwtA9VJvoCp-qjhfZ=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfbhUdOq70jqWfoSKZ8d9_8qS0Y0dCZFJ8HfGd8s0p_kOutCDw-WVNBQDS7nGSXlvuQJ_twcFrH1yTGT_wG8jtX_689aUjJ0c4eR8qJzWKdJBqHoam4u699qITF661NjPbP8ZrvhP_XeUNL=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>mandrake-greek-street-food.jpg</t>
+          <t>baoyilong.jpg</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Ficus Bar</t>
+          <t>Street Food Burger Madrid</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1913</v>
+        <v>1314</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Coctelería</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWluryhDJy3uag9kVnydbCSP6OLuMlyI8B3fgT6hbGL-sHwuxRnjV9kYhVm84PHr4xP03vpzWBc3MMZAQWBVrlesdRAg8UmycjDiXpujYkXxXPEMpMbQtWmyMC5sOWtdSC6wA99_oydsg9Q=w80-h94-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLddCC5FXUqdmRIg7scpf_4ONdorwbu39igSBzoWMcyPo490dmOGSKWqvDwzYayAQCZe0Yag4FKLCP8b6yqBD0ec9ErTuenJj4q3kXBExEcYFADuiTdCfIJAmfvrgLK9csFefnlShAl3nG3D=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>ficus-bar.jpg</t>
+          <t>street-food-burger-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Snake Bar</t>
+          <t>Bar Gyoza Go!</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>673</v>
+        <v>3365</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>10-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Coctelería</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkeUkUNQ8GOKA_4astHDIGV_76be9F_o8YHuwPruINSk8GKRAG33w3VBm8myrEdtmMfu87fnR3sow1_BABNThxGEB6md-fPRTrCrjxJ7fH6Eo_wtdMKSU755LfVG_0Vr94eOY8fqst_Ccpf=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLftB9QySRZbJgnre90Pqbksps8gWVKfrwmHZJZtzQTZE1qan2_2ozaPsydUf15-njF5St8beClZIrif86E7NB0toPXsVzys2zdujSxB4y0emkfNf_vpoZ9YSoYFItwyN-2hhFUCjvrxHAtv=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>snake-bar.jpg</t>
+          <t>bar-gyoza-go.jpg</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Dolores y Lola</t>
+          <t>Grab Sandwiches</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>892</v>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Cerrado temporalmente</t>
-        </is>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>10-20 €</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Bocadillo</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWne6x56TKstVCstw_ByiI2TQWAwIVVqO4Rr0OjpEdYLNcJpGNINdvgVkBszRVQGnvSPeQnHj6qqN5M0-le7DbHtGH4LcOeR97axShRzyJP-g6XzxS2Q1qUc5rFPrGtC1s6RTQkGCg=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLecAIvziPhfX4yt1ldMoQfGFP2fJYBDx_XO1B4S2Z0P-11DJkxOm-gh5u02YYR-I6tx4pKUqketU0YgYRZneWjeK9ww9KK76uoWotC3fymtvt9UCFBl0PsIy1VR2zsvwA-wFO2xD2VUzzw=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>dolores-y-lola.jpg</t>
+          <t>grab-sandwiches.jpg</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Tribeca Bistro</t>
+          <t>Mami Tacos | Taquería Malasaña</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>461</v>
+        <v>4249</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>30-50 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Mexicana</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk7X5chstch91wBI--xlpKSXSzlxlWnkqSCo2tZVVtEmdvPn7W8PRszSBVT_b19QBwudDAf5-HSMHkTRS33E6XQfRBZNmGX9bVJsu6X3D_darGFQ2K_UkzLjianE7IRf9yEpt_xt5ZAjTCa=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf8iJwiGMqbTahrHCtJRd2PgERc1332ENj4Ru0reIVeQJRq1X4yCftBUfiVZyfnLeSOAk2tZbucF3GM93m1ww43EIDPFVcIq_-JWRRN-qo6C97xrS8XwGA90sXwcTDgwOVXxxbl=w80-h99-k-no</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>tribeca-bistro.jpg</t>
+          <t>mami-tacos-taqueria-malasana.jpg</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Restaurante La Montería</t>
+          <t>Baovan - House of Specialty Baos</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3418</v>
+        <v>457</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>20-60 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2967,94 +2963,98 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkQ7yja7pMzZdaXzfR5TLNrD_TXh0_YaBksjJIv2na_7OIyO7TdbEf_d4gAEUkGi7USLAv5Rua2OArYWAkC_7TFpVGEDYjOGkH6G8wcK4de--rn7Q3W8dBm4opd0Z4UrErSD5mPlQ=w147-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcUj0kMrlsDErIUhIQklAl3m8m5DP4SmS82N15l6owX_hkYm2zRWoC02jK8KIm9qbuwWtAV2vbxmJ5dwS6-VdYUy9j4uPHi8ND94Y2jRgRtJtEqHZynIlFXzE6NKLmEyO0eKI_NpRwxMd9L=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>restaurante-la-monteria.jpg</t>
+          <t>baovan-house-of-specialty-baos.jpg</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Pilla Tortilla Fuencarral | Tortilla Madrid</t>
+          <t>Diurno Restaurante &amp; Bar Chueca</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>212</v>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
+        <v>5233</v>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>20-30 €</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Tortillería</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl6gGRZ4Q_HqxG7DzPCN2iwClmZWaEf982DoUNPNHE0NZufcYioYmLTPmWzeIo6_rEV6jv2buotUQV-KGRJ2PHmAxlgcntcOjb7u8uQ7CUHrYmcIb8_CMeYKoj8YUblGGfpyZXTpwTiGywb=w80-h119-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfX6U2zyfoq-8PLcrmWbB_dgp8aiaBCfqn105tS1Y28UteDQKWEFlxgZlDTYoQH9pPtSzJ7hd3Ec2Q5JyY7ptKLROr2frEKb6uexBTxa1Qv07EbSqNg57de_eB0oHBjFqzSRHzH1SLhObmA=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>pilla-tortilla-fuencarral-tortilla-madrid.jpg</t>
+          <t>diurno-restaurante-bar-chueca.jpg</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Pathio Madrid</t>
+          <t>MANEKITA bar y restaurante</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>373</v>
+        <v>274</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Japonesa</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlYkceBYRmvLkpw-OQEfiHKNL4DZOFf5jaKHCSlKN4lAb7c-ns2ZU5jhzrWYr69Z23FVLv1QTW_vTPqscDiuT7CK7IFb-EfSLJYLMUXkOL9Yl5WIkYOnXT9oWKmpKZwDwAJ4hoq0Ozi8BWK=w80-h142-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe8-UsXSasB8gK4fJH92gnwVbkSdFXmqtTGEi2zOVSspCHzYe1y_Zmt2P_VaK1LBPbQyBz0_we9BhXtPcRBZm-SbfQtj1HT2OMitR96kW0tFzvIkXRnKBNAyRktnw63I_yZBy0=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>pathio-madrid.jpg</t>
+          <t>manekita-bar-y-restaurante.jpg</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Caña by Cañitas</t>
+          <t>Mandrake Greek Street Food</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>903</v>
+        <v>1234</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -3065,464 +3065,456 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnpVIWuWwKIHYtTB3Fxrel9kqEFmlHKuA2z6zzi0vOINyGt4nfz_4wxZsianr4t1Y3-Gw0s_AAE4dz-sVLOrh0CFlOi-3dHiLDzx3TGo0eaXtHgojHBTu7ZU3mHKrvS__YrXLaUULqaKKnO=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcAsBMP0TTTYPbUcnK22OYZ4LfGcCCJPdVTL5FI4o7W1Ja8XlJaOvLdr3HQ7gqrmqgzjRmxRhVCDMftPLsuWHNWRC07CzpccE46PK_iG1c1_ysVoWsr4V6AtUM0JZo7Pc1CYHLV=w80-h92-k-no</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>cana-by-canitas.jpg</t>
+          <t>mandrake-greek-street-food.jpg</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Doña Tecla</t>
+          <t>Ficus Bar</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>3210</v>
+        <v>1924</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Coctelería</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnBpmfD0obqQbX1d95kC_ftkMkw2i0UMG1lC8VCxNoSC7ASU02aAjYqrRhB3R1dtaxRmRu35U0NnR1K4bjhHGxoUAiXC1alQ3MJ7f77zuNAKfzW_QNsbcMYROTxEjGOg7Ccs3BZvg=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfACFF2fCf9Z9pYt0bimo5cssWOS7jAHivcMcv9B_0dcfKap8hciSgA2OdyZesgML1yGcEQTRHKXhzUaLM7uwtgXGYT-wb8YVk6BPwnr5kkATcBrGiLpCDUFak-e3arxUoNS6iaY1FiJn0=w80-h94-k-no</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>dona-tecla.jpg</t>
+          <t>ficus-bar.jpg</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>MARLONS</t>
+          <t>Snake Bar</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>398</v>
+        <v>850</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>10-30 €</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Americana</t>
+          <t>Coctelería</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnd4QsAyRx_uygDe09jD26j9tw1zp8R3JFGuaCAcik8JH33mvf63s7kEuMi5jznAul0qY4D-krSMFeD_5222kAo2Lus5zz4lTq-gYYc5Hznj9pShlV0dSHP4Q0xFE2XX3BR8O31ceTFPLbP=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc7ptfAoPMA9StL5ZinHGQlBMRP_Hu72ZadwL1vsLMd96sAItVTdGBL21ikXc3eGpWbymK3xY6eHj-hd_sxuCRu-OOZD5v2--TJBk7RVRFG-_z45KzsaPjvhCDIc8Vx0HK5zZyAlCv20KU=w92-h92-k-no</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>marlons.jpg</t>
+          <t>snake-bar.jpg</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>K'era | Restaurante Georgiano Madrid</t>
+          <t>Dolores y Lola</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>269</v>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>20-30 €</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Georgiana</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr"/>
+        <v>892</v>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Cerrado temporalmente</t>
+        </is>
+      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkT1zb_x5NbP_-6zUcq90hTsv_iMT7gneNCycCDWdq6CgHrjqm7kdchoEZXBCoq239QRLtiYqoYDEL7D2dGYUytVSMrLvpcCldv92tfbPDsRortPPW9HkZ36saAC2IhkcG7pYpslSyzoGq5=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfkZhU3Y7HNrHk2LnN9rw7WpcDFFgrAXrTjFWuj8SbzwpFUD4OZerhXpbQVyb-Zi7ODKYK1veMK6uu6i6Ye7fZa0-jZvtW8Vuck5JTtZ_NnY-wqDoZnxciYZ8eCzcSIAJ08uJaKLw=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>kera-restaurante-georgiano-madrid.jpg</t>
+          <t>dolores-y-lola.jpg</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Onda Hamburguesería</t>
+          <t>Tribeca Bistro | Restaurante Barrio de Salamanca</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>154</v>
+        <v>503</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>30-70 €</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkYHgPD62RgZ3-FHB1TfmgsPnoLNNkVY6JjeW5l95jwnjt9oWetMzWP5ySLoNJfVIuyDJScZq2xj8QTb7VtO4STVyNFBFcy83nNkswyaK7QveYlbJY7TbS-tkf41o-vGHteP5HJ4dJMVav-=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe7rXOpsASO8zlnSDMChmTP8_oBs-wqPVF5hy-c1wY2kp3TrgwIsO8SH6OdQASg7VkE_hO1lFKKsUt-ais7zATfsxsBo3gqD2c_I1tvdET10j5jYiDj9gdtA0SY4Rk7dkTr1qUFM50_K4eU=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>onda-hamburgueseria.jpg</t>
+          <t>tribeca-bistro-restaurante-barrio-de-salamanca.jpg</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>BAO BAP</t>
+          <t>Restaurante La Montería</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>292</v>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Cerrado temporalmente</t>
-        </is>
-      </c>
+        <v>3442</v>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>30-60 €</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkGiHY8YHizzi_7SOJaerANYeRcl6zXaUnVrAq-lxXixWqWPp8CWhotu8jTzkE_AiJHdsT9ssDwieJ2T5UTbk6-JfJ8aJ6AbyKjspvjX_bJpDMtsla7tQVavkOi4HuthsrTaNqkpJC4dRpN=w80-h99-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeJzoC6Zj2GOrv73zDj8kU4zk5c7HBBCJkG3CkvV9auLNtSOMutI0Gp6f6ERAkag6iGYjomiGSfFbnucCPxE6vkQqI6Exa4w6s7KOHpDx6mbWhPPIlk_xu4DZQWsi476taWTjLM=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>bao-bap.jpg</t>
+          <t>restaurante-la-monteria.jpg</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MALAMENTE</t>
+          <t>Pilla Tortilla Fuencarral | Tortilla Madrid</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>20-30 €</t>
-        </is>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Tortillería</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn3tJ0QUoXcaVXonUfD8FlMLadBgREUo000OTS9Gs9ffsWd_yFSn7eAcjkKsTeRlQVC556JKMRq0tlJdN0o0VDetJ_1fhPkjKv4-nGQm9CRgUeQj7TYIryo__jPcgYnpVGahUupd1EqKZ0=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfL7OLlSuRhqyqvNdN0suLcJlQHAxALb70WHa7-3JXtyQs8RzueCvYFNqOenSjSovomcYhvJhHZi-HOy29PAbfquWrjv4M9QxRjiY0YM-bNCrQYEDGtL1-ggctRqBmv72ncCcxpd7FO46ne=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>malamente.jpg</t>
+          <t>pilla-tortilla-fuencarral-tortilla-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Paladar</t>
+          <t>Pathio Madrid</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>129</v>
+        <v>418</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Cubana</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnZXGBaxdSBAh0JMtnNxnsnJJ4ixV9X1Tcse_pO-et5dLvEEATYMuoCVd9yVDP3Tm0uTg11K218Na31GWacmxep3a0bYM-d3Ee_bzQxsBFB7MWby338s4R8S9Gt044rcJhl015wNaq5MViv=w80-h95-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLefLobRldi0hN6SziuPgGSmJDwzAR0Bge2QxmA55g8cBnFF0bYivMJchdWaQypH_SCLRkJ5N-DvDp771a0DOfnhoBqykxwvPXjAZecCcLdcLtmYxwTH_znTAn8TsV-H9klU_X-SpgOiQVcp=w80-h142-k-no</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>paladar.jpg</t>
+          <t>pathio-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Velarde 13</t>
+          <t>Caña by Cañitas</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>1084</v>
+        <v>926</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmkIB-mUbVbRzOS9e1dZOnqcyfBHyXA-dEodnkZoUW2gNaFbNDFk3b9CrvvzK73GXh0jXuGmin0dcUqivmjoxrnocxslJ9PDUMJzR_hwHuMHoLR_SLo5cTHMPHRFqzs8avZdmaLHSbodzbD=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLd62cdhulwpcRbGRLbLXHXzuL37a1MxYIvjnc9tWdoo2y4g1YqR39-_Yaouofbz-mLBHh3jQlqxmkau88Wi8N__Svu-KikIYmMZL60JMe13KFliRWN_YyH2g_dL9KsnjYBIsvcfNumT8JU=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>velarde-13.jpg</t>
+          <t>cana-by-canitas.jpg</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Sushita Cabana</t>
+          <t>Doña Tecla</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>744</v>
+        <v>3230</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Cocina asiática</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmc5q5XyXScMicTiG65jBmAd7w9-PNhZSMTUKz85XUSqQow0gmOHytpD0jIYMPBbUOXk5A_75jZ85s0TnAa26wHBqNe0ECGP_WPS6KMmJx91nBHs6IsGA6DibiMPjJVU0QUXJ5ZQg=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdoaD4Fzj6sNxjI3VQoY091576vJsekDKBD1LkcBrg3qXNvUQDy0T0bzjurRe7hB3gKFlgbzKtYj61Eiv__3ukoTAMUkme5ahmiu2-XsKZy4A1pkq2E569eaJncicYkvJvS_7z9xg=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>sushita-cabana.jpg</t>
+          <t>dona-tecla.jpg</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Ragú Trattoria - La Pecora nera</t>
+          <t>MARLONS</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>875</v>
+        <v>454</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Americana</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk6HqgyKQNNmkJE81N-7eqJKeNQAsoXpHTG9iogadUTtXPmTOSt_oQPmuDyk89eNFTaQEVIWJ2i_0_yYvJElbgtACa_-JQXTaxDO3XtqmLrIRFqdSz6ThJkLN1NXmywaqQPt_zqdk173SI=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdV0ZDvjp3DZAUcv_UoBVgjzXDqw1OT_ZzGsnxc5u4atqLf0ScyGWW7w7R3NBEWYE9oIq-3i4B1aUGiPqb6VYjHFj8mLr4Jt9fdyUYFvBNafyZBgWLt3EMrJOMjjfwh7gUjjXYKVx2vxCTw=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>ragu-trattoria-la-pecora-nera.jpg</t>
+          <t>marlons.jpg</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Taberna La Tienta</t>
+          <t>K'era | Restaurante Georgiano Madrid</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>3727</v>
+        <v>304</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>20-50 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Parrilla</t>
+          <t>Georgiana</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl1ZX8_sLzr4ujdF4aoCy6eKyVnBRrjyoHgXbLHlKDLWhwbJPIYZxSFMGPVGWEJqPS212ZyJjeSV_RzJimhsuC3Yeey6yZzup6qjhalBGRLiNvvXyRzP5o0d5wG6TwrKaqO-VwU=w92-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdbGY8OZuQdsW1ZCIXFtIi2vqcpRe9EplSdNOK5q5LH_q0xi-uWQxVAlaiM7G2pTryqGW7VUslsocWedj_e8Izpv25m4Dqk7Bq0yGQnyA3idwuoQiRJ2ggLYhasNyJgjpbea6UfQBh4hPc-=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>taberna-la-tienta.jpg</t>
+          <t>kera-restaurante-georgiano-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Meatpacking</t>
+          <t>Onda Hamburguesería</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>507</v>
+        <v>175</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Restaurante de carnes asadas</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnMsCMniTc9nGfipGCfb21xx49nDQ7X1Pv_eoWAp-R4H-ZnptimbYw-Awr3mWG9qbcWH_Lo_EKQ6pYYu0qCegkm8B9NnTNofnnPUEQABuN2zeVpOuoT2YN3sDTjj4T0R58PY5wV9qj95QEY=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfiJQg5VaxLn-jaRk1ynmZ1fZOYitljvnJt4PeuDSFg_NbEOxb1-iqEawojwW70OJliV3Kkcb1SprfRtcEZqJknie5muyBFN9UbSimKVSTeVsB6GDVNLwbLhV9Soknhq7nyFRHtJkxFN1SB=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>meatpacking.jpg</t>
+          <t>onda-hamburgueseria.jpg</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>D.O Majadahonda</t>
+          <t>BAO BAP</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>1876</v>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>20-40 €</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
+        <v>291</v>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Cerrado temporalmente</t>
+        </is>
+      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkf92i4dY2xt4t8yI42Cq5EAFEX106O9az7gaAyaqJawYYJjSEYaxkHVlZb-kbsBysfSDp65jC_LAmeO4NOueqPOR5YTpeZeWs_vMOvY8rSVMM7vinSgc2ZC2hcNAdzPBLmO53i=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeiLOb57Yt4YLaUrbcZKCcfKlQmG7iB6CaVPYb7bjQuFWk8ra3DU0dtxfTcuHB0efex_MYl8k1rB3uOYQYTIIbi8lZvzAPuODGRP_kSRrpgKRPI_57cpJ_hCo4cprK9QGU9sDK3LNkcpmKd=w80-h99-k-no</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>d-o-majadahonda.jpg</t>
+          <t>bao-bap.jpg</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Miyuki Sushi Majadahonda</t>
+          <t>MALAMENTE</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>689</v>
+        <v>132</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
@@ -3531,130 +3523,134 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn6OnnyMfyQgZOEHsXCM0xS3-w-emmUE1gIf-MOKe78JKyc6wae5uhQMdz67XCY4yXnDYAQlv6A_HSe2c83HpsmU-P5qy21tgp1yE7vEalNCqE2ePo_MaHDEUtPJbe8zh_yQhNHhPSbSpA=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcm609Se9Q1nMvXxcU1NzYz4ODbjKcslMRcDU-RQyzSZ9W629nfNZEmvzVBIuLZHLyrs1jXih7CW8DlHhbEWT0OwGZ6BSfztNUXg6eEeyOBqgPfjt2_xTIcuhO1DPSDyG59FPrXG3Lmdn4=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>miyuki-sushi-majadahonda.jpg</t>
+          <t>malamente.jpg</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>BLT Barra Libre Tapas</t>
+          <t>Paladar</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="D93" s="2" t="inlineStr"/>
-      <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Cerrado temporalmente</t>
-        </is>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>10-20 €</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Cubana</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlDQV4PW5fFUC5i_yG0RpD5eFE-BbqNKpIqoUOm6mbkiClICJVQSU1vzfyotfokwp7CJO8WQArVHKNUN6vsRDgxACoBg_09pb3zhejyduhDLN-_VTms8MxO0HEBZrCuCoeUShN1X-gYMms=w125-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf3EDtV1k-daJOaMEeYq9sx5lq-X8UMEhjnr7HrAyYwl5LOafNeOgJbuWMD2rJDBO31Nbfcy5BqrEk7dbPbN2YDyJ8dqSoDcQBN4mwpHh7LMB_Jqs5OYCMcc-IOUhYNW7W8iMzT4SQKZUQU=w80-h95-k-no</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>blt-barra-libre-tapas.jpg</t>
+          <t>paladar.jpg</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Central Mexicana Majadahonda</t>
+          <t>Velarde 13</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>1801</v>
+        <v>1101</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Mexicana</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXlXmfzPrlkZsM6OvWHVYL0waAlxSDP4S7IIswFaJ2ZJDRJoGilEqQ0NAtgLK5nZ8eWCCkUVlvPTERuGpbw1_HIWwY2ODs4rYEVdE-Tg_Nvkj5LEmRcyNoN-4u1I0eHJZtaEWssA=w103-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfgqUz_JcNFJ88CX4GWOjmbNMzD3mQKzA2WqBvSlMZkIFPvcqNf1JfYThEXrHJaRLXtAM0mVjrF4J7DMKSmjdboNM3R0lFv2xMI4KZ9apjMmSbWvfL0a8IFGbRCVA8PeFvSJB6O-uXFOtGj=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>central-mexicana-majadahonda.jpg</t>
+          <t>velarde-13.jpg</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Restaurante Namaste Nepal</t>
+          <t>Sushita Cabana</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>1619</v>
+        <v>812</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cocina asiática</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkesAiRT4uZ6y8dt-X7O5XVzVOk2afWDLOI3IcLsysTk2BxV4mzqrfdXihYrNSYwPQjlRHES_Kf5K76LGD8PYJDFscflH06sssj-YUyW0ddiNJX9oOYbwxUieLxMW1mFMiTcNYD=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc9oE_SvDE6G6lf57T7x9AEahW7nuAaAbEcODtxE3lvxk_Uc9EMAH8WnF8KYT8sKVr6GOAy6UJv7N6vtn2w2WpWTraGdfizexh7pOuKH00WtQ5aTcOUrOm4Xa_jv-rRFHPOh--BeQ=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>restaurante-namaste-nepal.jpg</t>
+          <t>sushita-cabana.jpg</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Kritikos - Cocina Griega Tradicional</t>
+          <t>Ragú Trattoria - La Pecora nera</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>3424</v>
+        <v>882</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
@@ -3663,66 +3659,66 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Griega</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkcWyBTAZ2AX-3ccqQKLCtcREvg676x9BCuyTWt-wkijEW5ubvE-rN554478fn3BHZ2n27pbUtgQh6_9vGfEqSMP1lbnsrhmVj_HQ1AJEBLXuYzOQShvYr-0GNr3ehsgEzTvsJhDJbjPBbg=w80-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdk2xvNgk_XBEp9tyCKza1o8NSA_ax2WfubznZMWpQwJaVXoVmlvjmEqQfoOof95vCsQMIo6Ow9G4adyosAQnzHzqL3qJpqzkV6hAYd_dKiN7zTakrX7yV5CSkX6lMS7m1qrptX_l5yIms=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>kritikos-cocina-griega-tradicional.jpg</t>
+          <t>ragu-trattoria-la-pecora-nera.jpg</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Nomo Braganza</t>
+          <t>Taberna La Tienta</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>1003</v>
+        <v>3785</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>30-60 €</t>
+          <t>20-50 €</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Parrilla</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlsl03Te7Sk-u0DkXNkL64ETogrnrMySf7Oh9pTaJr98AwswD_Hk6TNHpMjFgKK-iFgq2V7jUK_L0INUCRzCzq4zl0aaYK4rnBFGt3dy0mNb_I_bI9CxLZisbNSrZTUajRufRUd=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcvvMKSExt1k-yoaVk8DFdPrFMqP63L6mxEBEfvLYZ1gdkTlcUbhtqqevMwgmIk6EWmB9j60wubZAEDyyFy_kQQJKhypAsShJ9s7PZU9k5LLiZ0ogmmHbtz_1iBWJb-fJGnlL54=w92-h92-k-no</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>nomo-braganza.jpg</t>
+          <t>taberna-la-tienta.jpg</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Katsu 勝つ Malasaña</t>
+          <t>Meatpacking</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>1037</v>
+        <v>659</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
@@ -3731,36 +3727,36 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Restaurante de carnes asadas</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmbj7R3-1Sm5SKjTnqCNnaupOylxcah3OjTuXCI8eBU907aAYJaD48GVu3IPcuzGicbwTGgH7o5pgWUOwx3VK8f27gAl5EO5mhY5-RtP8haFzlMza51lqOlABOehSS7ElxQldRdOzbfhlU=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdgrW7wdVvtXIv0sqm_ndv1FnfFJUo1nsf3aqZTWzL_xk-eA5BRZnC2yK2bAXgyYbkXh9DcCxoy6AfzeAnV6xNqaD4ShQFCNdvFYbEM5HHLhww1Brh3dJO9OWeqNfTGEYhvb7CZwVq_LAZ9=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>katsu-malasana.jpg</t>
+          <t>meatpacking.jpg</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>KATOYAKI JAPON Malasaña</t>
+          <t>D.O Majadahonda</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>504</v>
+        <v>1890</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>20-40 €</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3771,90 +3767,90 @@
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkju1XMUINev2-NRf6_cw-Z4BjilNtDpFSuHKagxWZsUO0G8eX_IHM4ZtJeFaE6lZIaZng8rcRPBN_r-WZmAfKOnv7HnT2rdBGPHsMFrxQbLU-FblS3qBqQTfE540W70rScuymuXg=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfoCCj811TNYARt3ZJ8nQWvmGF9ROvTu7YrGuOnXWeMaDZ6j5f4H_H9Wc8hr863tUOZhY1wyLM-Wydh_S9zJXnOJXz_Ry0Kxe6iJ3M9eFCufThDj0F_0sh72mZ5nyeuxo5CAGkG=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>katoyaki-japon-malasana.jpg</t>
+          <t>d-o-majadahonda.jpg</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>99 Cheesecake | Malasaña</t>
+          <t>Miyuki Sushi Majadahonda</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
         <v>4.6</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>1595</v>
-      </c>
-      <c r="D100" s="2" t="inlineStr"/>
+        <v>771</v>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20-30 €</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Repostería</t>
+          <t>Japonesa</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkBhhYq9wR2g8tuWuHdk4doZ63_BCSMeBjQBQhEB1fV-e-ttgoz4MX9IEpGfq6Xn8s5OkbCf9yPxC6kBMQh-VA1ZTU4HmYBoqvYrj2gDIWjFeBptH4mSLsqAtr3xXyUPYgyEfZIrjiF1v2k=w92-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcVHZ6GLtdgUb9OYbA-zy12CAwKNqGH6mMMtf9CXKsV6f4aUjkUzrqiZRY1FHSMLLukmkfWeJUB-oXvifoZE8tvQEC06Gb8vB1fw1BeYz3kL2Mzow_WGUCBMz2zR_WmKuVPg6mORvQ0_ks=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>99-cheesecake-malasana.jpg</t>
+          <t>miyuki-sushi-majadahonda.jpg</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Chun-Li Dumplings - Gran Vía</t>
+          <t>BLT Barra Libre Tapas</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>871</v>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>10-20 €</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr"/>
+        <v>118</v>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Cerrado temporalmente</t>
+        </is>
+      </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkw8djyYh-crq1sl1tVKbEFZ3GjkqHZcfaW397KQFiF7A-4PI4phmLrz5Hbf3NkqsnSJwdeUel4b9NpBsCGqmbdNNC9JnUMoJgMMu0-MlXjZbFbubeK89Koqfi10Mhi421ciHet=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfdqZlT-Le3mWCd8ycDURriORBUyvvLRhd2gmfJjLFIC4LHWJL1wrhxHUZd-0Kder7ht4QpH_Ch7wQ9oHHvSgyf8LAdOBt3S1ywf_t_MwMMQoPeP-VV40oEUZgtxZJPtkcJj2aD9oIHI9I=w125-h92-k-no</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>chun-li-dumplings-gran-via.jpg</t>
+          <t>blt-barra-libre-tapas.jpg</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Mune Pelayo</t>
+          <t>Central Mexicana Majadahonda</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>1326</v>
+        <v>1806</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
@@ -3863,32 +3859,32 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Libanesa</t>
+          <t>Mexicana</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnzSUZWV3XogcaNmm3ZU40lbF8K9XYGxmLB7Ltn2gQ27AteDrYOdRNsXjDu5ClCdo0AIQTsqh9xVWVWgvRNySLZEP0mTHehDLJfwT5JmOIf_nXTi8m9wNcb7s8FQyLlYSrw2G5rtg=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfZo7PQaodFOkTRuhKVdw50UlWxISbrGjoHWVUK-n7v44cJRcnErevBEUKC2BWRWbNd9A8yLOz9eGjNE6MU5chXFGKmbwwu_iuys-wAGyheQ2fTalMi3GJZkB71jNBhzJti2rcFLQ=w103-h92-k-no</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>mune-pelayo.jpg</t>
+          <t>central-mexicana-majadahonda.jpg</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>La Bientirada Santa Engracia</t>
+          <t>Restaurante Namaste Nepal</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>2753</v>
+        <v>1632</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
@@ -3897,32 +3893,32 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmV3N_CIfc2NMm3zBQ-icE6L1D6hfUWk5Wxj3jg8_c1LE93EhJC_guPgtKlv9Dx-cEhy-27MHbA0ZPPuOi5RQvcXPvH7xM5Yuz6-2et_d0N6u5Y6ZXBApNMu2Vq9xTtFEaG1gBBE8Uy1Xg=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcbrM_D-J_ee2vsEdZ8MRG3HZeQEH61blH5myY1FGYNhAzcOgLahjbJ0ZOpVOjj1gRSiijOxpbqSoRjX7kW4iBpBzW6Qnwd8ThboMn3XN0JRo4uKrrs9fSHVLIMLcYdnb0AIBBh=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>la-bientirada-santa-engracia.jpg</t>
+          <t>restaurante-namaste-nepal.jpg</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Alright Majadahonda</t>
+          <t>Kritikos - Cocina Griega Tradicional</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>169</v>
+        <v>3458</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
@@ -3931,270 +3927,266 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Griega</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnlfFBhr8Z17rxHJBGLbRuxV7Zj0KR_ca5_PRoOTipnFsdjbBLJTsK_2edo0DgPkni-vLaonSkeMNfuL6G5CTGumkL9xd1F8st7yi_fNMjUYne6brKJPhf4yVAWfpkib-hzMV9msgRKaerB=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcRz6k1XG4QFalNodzKMc74H1ZNecXA8ZGiMzIlOwQc0o2xdAFW3nTl7quJmbbeYeM6TlEwERPv40YZOIKWmqw-zdhzxnf62bXB2kbE1qPtHX2cQYokYFfhrGKKO1YvcKgRRByoA2L_G-zW=w80-h92-k-no</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>alright-majadahonda.jpg</t>
+          <t>kritikos-cocina-griega-tradicional.jpg</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>UDON Gran Plaza 2</t>
+          <t>Nomo Braganza</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>3422</v>
+        <v>1027</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>30-60 €</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Cocina asiática</t>
+          <t>Japonesa</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnVIgjeG59XiLCzCIursWh9B8es4Eevrmt9I3SyC9Xmc9HFRTNyShuujzf8adYE84a4c7hAMAAOYoPbH9FQ8mszDiaAcj-x08a4oU65Ah9VfNcca8Udcg36pgawXFeFOBkoopopog=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfSUzsNFCpC2EpxdCYPm1zY0RP9aK5WbXRAKWFis_cY7NzO69tVX73Z4cM4pVTj2Y0i6fdnnw0kJ4pNCpcZv6kCmG5x3gD-ki3lxQLE63m76yqBd_ajN9QPMZ2u_B9tMPPTP9_2=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>udon-gran-plaza-2.jpg</t>
+          <t>nomo-braganza.jpg</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Purnima Indian Cuisine</t>
+          <t>Katsu 勝つ Malasaña</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>3903</v>
+        <v>1056</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>20-40 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japonesa</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmCuts-mY7GW4PXpSZCnq2sAiyEmttQYj7OkHtBIoBfj4J8-fPPPaHPqsBOlaG6zHsKuLtgOA15UrGDnuPEHUBliF5LffmwMXhQ26hkpoyxQqyVozB2J1ISU4GdB7UWkrBSezU=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcPFEVPZu8WdMsjuaKGE1VPlSiAqvS_AZYigVdfD-2bQ-5F3LpxPKfWM4m6QxixUiSb9H-xMj0T6Oh9v6vhh4_g8qdb4gpI8eAl1X2Sri7dhG5BWkL8vr27gayTl45BM0PJCHVh8Qxr8DE=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>purnima-indian-cuisine.jpg</t>
+          <t>katsu-malasana.jpg</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Casa Victoria</t>
+          <t>KATOYAKI JAPON Malasaña</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>381</v>
+        <v>514</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Cafetería</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkKIDMxwNyMceLlfwdR28lnxJciFQCFSMR9nT5948vMZDE4kT4VntIwoVNkZRCECL8YP8NwIhxt0_buRGwzjSJ5YLDzWvFp2zD5RELZvsS_koYJo9YPaPB6ibvSc5wjFDuOvCLFR2ljLylY=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLekhrIF8O10JHq7ByX22HSc72mta8Ac2oN6jpN8Lc7zrReh9lL5b0w7tv0DuS2yVJfkU_J6wMsJpzOyxWMlSK1hTGBxfUv-zkbsshGk99n8Fc_7ER-k_3o5uh2RGX7WmCU-jYj9Kw=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>casa-victoria.jpg</t>
+          <t>katoyaki-japon-malasana.jpg</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Casa Palma</t>
+          <t>99 Cheesecake | Malasaña</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>10-20 €</t>
-        </is>
-      </c>
+        <v>1641</v>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Cafetería</t>
+          <t>Repostería</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm7PHKOJ8ET49cQoaRaLfSfy19h_re-JgQgYQ1H6gPz8TGW6_ZjQzAylKNOLTwKoD_IQMQSLKpbKYA5dgAJS7oLcKLIC8epE5gn2HH03AXa_6tV9KGRG0Vpy7K1e-Yw10YIOqlXqRGcpTE=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdfcCDr_3u3ZoGihf4zKyKCZd7BYtbW7lapqutjZswuYIEXKzcPUaNaPchEEWNOCfzaWZ5jvPWPPilKV1Cm4Qu8nkG6uf2Yvh4V38LgFAzoDPMWSuoPK91fm15NfRF4BAmjM93ksdHWZTz4=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>casa-palma.jpg</t>
+          <t>99-cheesecake-malasana.jpg</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>PURY JOKBAL</t>
+          <t>Chun-Li Dumplings - Gran Vía</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>850</v>
+        <v>885</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Coreana</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmJCv52Jl1nqlux1v8j60mhYOZYCLcbQYthJzTuynBlfJ-DPQd2aPSmOwFQPLbmZFt381iAXUQkAg-AR1bbO6ELb32XYDmI760vH_UM1DTmo5sNBzEc2_i0gPOJUkvyXWgr9dD0=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeO1IPF1SyZnzs58PXhnwJu28EOwPzz-y4UgMSEaim3bSpIVNZe0OXrfJnEKYLdMrDjPu9kuMccHxLYuoKHzkD9ItjYAGmNwTicvhPmVGiufIMMrhcpAwIM7V7MmRyRmq6qzzq1=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>pury-jokbal.jpg</t>
+          <t>chun-li-dumplings-gran-via.jpg</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Makami</t>
+          <t>Mune Pelayo</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>2706</v>
+        <v>1351</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Cocina asiática</t>
+          <t>Libanesa</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn_Vl4ZXUbzin-34d8XsLKs7JnF_Ircd7G1nBHiTy8UlM6T8mdzJxO-NapEhSezBemErnBr4-hqxqS8QAf1WoD45Rfj81ZmHcK_ckrZVqAuXakIceAkyVpaT8R7a5nyRKR7IaqJ=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe4gx9_tx7SOpj3GpQHuckjAEs4TdAL1ENZ2sp0ph9Zbghnki9ziqVWXBFs-9ogmT6r7zwjmL9pjjzgVEA3-MmbMt5H2R27pHo5aPSN8v_8dXFxORpWyNG6SaUWbl6WQId0eeSBNA=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>makami.jpg</t>
+          <t>mune-pelayo.jpg</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>UDON Princesa</t>
+          <t>La Bientirada Santa Engracia</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>547</v>
+        <v>2765</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Cocina asiática</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmwC_QLO_9-yKQ5lMs1dE8pLKzfdNYyThA20TDutXt7IzEEtnyUhaR0Sw4fSnFbi9ckpuWZxoogreCxsZnc0by3HpAtYvQQLjLlFu-kWN4EdeGZc6WqsfKviDsx7gEpOPaKN1SA-IDPYkTO=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLelGlcaD5Pznl4_Q7tHL23aT2UEyGDzeVJiJ1-Le9Na-Aa0RDlXt9qolakegHcYw4esd-JbC8imToHIyONd3Q-aaa8UjtjwirEfqQE3T-4GQMCVk1dWTRPMif1n75XpV-X8zTHSxTkrTTY=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>udon-princesa.jpg</t>
+          <t>la-bientirada-santa-engracia.jpg</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Filito - Chamberí</t>
+          <t>Alright Majadahonda</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>292</v>
+        <v>177</v>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
@@ -4209,26 +4201,26 @@
       <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkn-AA1-qyKZymJ8-PwpVIcXmdwY-QsTOh1GIVR8ThcBUk_C6U6dkqb7ZB4SPQanTV2p-13pxhWbdw8Izm6MKb80QjlkL0NcwJpOdIJRvJa1ZUDj0mPszIGQ0Nj2lmdqcBKTChp=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe04HzSHdqcaIBOx24aCc-XGalR0uKfazbBDoEdtOaJ0Sd4kITvlA2Qu6a8ZU2xoat1bsNYW5gLlz776Z-16ecnQySoqkzmum5P8NsC7_Qx8ZDmdAHwgisJkK8aVYxEAXsCMyNFhUEbWAHx=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>filito-chamberi.jpg</t>
+          <t>alright-majadahonda.jpg</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Juancho's BBQ Majadahonda</t>
+          <t>UDON Gran Plaza 2</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>2866</v>
+        <v>3501</v>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
@@ -4237,32 +4229,32 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Cocina asiática</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm5-HxKlYBH5WWx519MxffbXOsR1dk9GDkEWrpy9jELY5Ei2yoNeVoRfrWWrTQkBmDhzb77YPIL8nwNRLawfURm06ibpwQwo54PW9dvoEwkoxW7-kw8h1JfVoCKBfHJleaZuR-5=w177-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfasUifRdPMQHv-wJGV9moNBnzqmpOc3EuvAuuButvjhOiGf5z64r8zbJjSHLOKcVlDimTlPmPES-Ycz69cBwOf7lmLMDPBVKfaF8rvZqpO7sq75DQJmoVyZSwfl8T9AdzM6cvf1A=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>juanchos-bbq-majadahonda.jpg</t>
+          <t>udon-gran-plaza-2.jpg</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Restaurante Juana La Loca Recoletos</t>
+          <t>Purnima Indian Cuisine</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>8313</v>
+        <v>3951</v>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
@@ -4271,100 +4263,96 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWllUbOZlQ3-LXHQ-taWuwe2WMDKkWHkUi5rQeENxTA94etX_FFmVgxrSaEcqqhT7mrIxvOAxGptGk_Oosgb2o4axW4bq4BU_hFMNh8YIR1kEFSlNZSFO8YOkZ_9ub8_WW26PJkHrPKpMdJi=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe0sseOCaS11003FjGuekH9spRhO5zABtSn78_I8J_2I4oy3af5V5fyxfwqnJV3RNOMMngvQXKBMEBL2IGJR4J9dSCZG9PskYdasNJksnDI8lw0dXgKmpBq1kMNYUlHBFLOros=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>restaurante-juana-la-loca-recoletos.jpg</t>
+          <t>purnima-indian-cuisine.jpg</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Café de La Iberia</t>
+          <t>Casa Victoria</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>1592</v>
+        <v>401</v>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>30-60 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Cafetería</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnHKwPwIitDnGUQlNpIcTCkTY0D4I4BYZewFwB0Y6iSv6d4zGwxIqr6uaS9uONO6mDEBAwjWb78KsSLPIj0uVuw0i_Bbqk1eq9B3abWg8CuvTf6KmX5ybu8aLHkKkP2tZcJZyIDXjh9biCb=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeeE_51acJ5eH4MqWXabklxiL60fT69872Ttv7lSb2k8uCDDQTICqCTnyI2Vdu-9iGNHIaS-d5WtZ_WmMWZwREvyycUayhSslflM6MosUbQAWdADXH3KsCmOWFA-579p9_EmDQwHt3XHCAq=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>cafe-de-la-iberia.jpg</t>
+          <t>casa-victoria.jpg</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Bar Tomate - Madrid</t>
+          <t>Casa Palma</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
         <v>4.3</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>3786</v>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>20-30 €</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>Bar de tapas</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
+        <v>158</v>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Cerrado permanentemente</t>
+        </is>
+      </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkocwHOSO9HEQh1qlSnz8CWIZxc-MFdYpD9IMV5RuLWiALc3v65Nq5tsKoE5Xh66KSuSnwnIVLiVrzJ_BdLlrz_Ub9GZQs_Om7GYzElkHm8PG3S4LFcoyzpeD2gLIADUPVNuEdZ=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfle6kddhwfCV1birCF4tE1niuTAMlcmI-86lWDV6gWkk4Sh3OOtVXnXg4axI0gNThXRn_h92X0VOZlyjanZC9Dvysz0NUXJo88SWe8_iQb8y2gHSgsxd7EObIjd4J2L69dR2X6JSHv3Do=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>bar-tomate-madrid.jpg</t>
+          <t>casa-palma.jpg</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Lamonarracha Pozuelo</t>
+          <t>PURY JOKBAL</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>341</v>
+        <v>878</v>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
@@ -4373,236 +4361,236 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Coreana</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm5Be-9pDkYGabcYNIJFA35FA8RxhFkLp1jIzsrThGPv27rpL_R1V0d2-QwGuW3_ZPsTqQBK4NagwByqpIHb1pcInRV-l17f58AsqQZQvDny4GGZFyCP4uCre5iQ9tjOhBnyoNo=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfec6-LmwEH2RoMFjc3kihT-J_fo1Y-D93bwr81xvSZnhd3hl7wLzRZ_cl5Sf_QmmuCASbSawHOCwGi551MZ_MN-Zlq0E7lsqaCj2kK9lH9o0TV_E9Jp6adleYZnpARO2N2pFZK=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>lamonarracha-pozuelo.jpg</t>
+          <t>pury-jokbal.jpg</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Los 33 Restaurante</t>
+          <t>Makami</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>2258</v>
+        <v>2751</v>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>30-80 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Parrilla</t>
+          <t>Cocina asiática</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkgz03R-axzlIuHzOYwCFWCrr07ksXNxCclsb6YEKm6dasmVDHHj4g_lrRwKW11p3-ShxQWpsq6Ior3st9h_wv3dL4HKFE-FG-RfZ19X4eHfD6D19HZ_WQqAf1wGv1v8wP0VRaq=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcd9A74yYdUzsE3UHGnsysYEwmnsZKy3hGkgFY-PtwBFpPTw3qbMh6vUDNDwy5Us0UGijnETWVGRKAZevHS3cor-uVnf4ZbTpmFqpNoPrf1f0ReMDckduR1XLiFbJz8lu4L8wF2=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>los-33-restaurante.jpg</t>
+          <t>makami.jpg</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Chez Pepito</t>
+          <t>UDON Princesa</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>1172</v>
+        <v>570</v>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Cocina asiática</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlEHeojkbMgtWSL_o5RKGMdBmgWYWGzhOKy5c0PGBgf5Fr7O-E8EHn_V42U1ohTONmR9BcnOHnfwHYfXvhlCQOJQCn22l7iwfIXqBVoNUIJKMURX60UU3LOQJISDaMrpcdgctEj=w80-h137-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfTwnVMyJnAQ2-rbznZX5etf6QXyzYXNnZaRn856x6Zf7Q0zF4nch7J2FnqepXMk4WrMCZs-xJA-lozKOvL03e7AIYAQeDPDC-xC-ZMlRBwcDOwag1GNADS3PSYP6tw4teGWyOUwGUdi-DH=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>chez-pepito.jpg</t>
+          <t>udon-princesa.jpg</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Casa Neutrale® Musica</t>
+          <t>Filito - Chamberí</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>950</v>
+        <v>316</v>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>30-50 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnPfVvPjgJ_jUC_uJVKmShjf3GCOvLMEdrYg_V0gpTYD-G3PSIHSKHuPDATWzP9jIrbgqUUrXLQRO0nKeReu7CMceSkRTrm71V3wM4l3wzTOOVEcOqo-i5j_tgNNWoRhnNk_ahMuQSee4SE=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfBPMzY6cU2usAjgVVzPyJ3-odE1WRTbJag5grk3Ze5XDkZboaBWWzVUiVpH4BG3gNoaMKhbFMLfS2sBUIkWV5hhZ1qJQTCVjhJ974gNTR4CIConuCg2A5cz96ESMOYk90fXE0EP0nj8c-V=w80-h141-k-no</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>casa-neutrale-musica.jpg</t>
+          <t>filito-chamberi.jpg</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Caja de Cerillas Restaurante</t>
+          <t>Juancho's BBQ Majadahonda</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>295</v>
+        <v>2873</v>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>50-90 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnKC1T9csp_qyZuXnuQl2Uj78Yi4oPqPtyINvIYls8__qHH45Y15JOQctEbM1AvRtXoehddM5oKsLBlSKfiKUQZMezViwDTF59uR-rQlX24jlyOqqZ2G4pYmAzack22p8ulWNV4t3AxUcU=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeGnS9ioHmouKg0m6MKFYh6I00c2_xMEE5XfFjnfw6x4QjzlzUJqGwHn77H5jZ46-8mQ5EHZG0CgxCWlYrVzK_qSxNpEk7_6dX_XjKVKOTMmeb4LqVAn1qwhC9awnNXSXDLpj5K=w177-h92-k-no</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>caja-de-cerillas-restaurante.jpg</t>
+          <t>juanchos-bbq-majadahonda.jpg</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Marisquería Moreno III (Getafe)</t>
+          <t>Restaurante Juana La Loca Recoletos</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>6957</v>
+        <v>8361</v>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>20-40 €</t>
+          <t>20-50 €</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Marisco</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnQcPEdV7d95TmFF9-uWuiin0JSKFuLm-pvcGM02VBx_7z4FMCzrBgqoh5bsxZiaelDv0p-H-BWB1VbKIhvu3goFQ50Zp8KFRmJT7ux7w5YvTI3Y2BjlqgblNxK2sO1h3JnLm24ZTJHBJjX=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfVxWBflmjtHH3hFG0sSesnGmnwB-dz4vxwCkITtTjmAt-zDz1Pi0GfSdvvgwiRBnro4wghMghwRmo-SYa48ZlYCgNLGNNbOMl-4bHppYufI5nS3VLPouGIy1wtktf9dOuT2yqY95JHLb-9=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>marisqueria-moreno-iii-getafe.jpg</t>
+          <t>restaurante-juana-la-loca-recoletos.jpg</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Restaurante-Terraza ZEN VELAZQUEZ</t>
+          <t>Café de La Iberia</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>586</v>
+        <v>1605</v>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-60 €</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante de cocina castellana</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkbWZoZ9OjPAS80GP5Q6qi-cE8r_fjKAsSva4gR4QdSPJtHhr-xM2aPU6Cy8B1L5RHN2g_ksohcBkT5MOCgWbZdHXJwvj0QQ5AswuVWXF16vc0RCOc1HBYj9YES9Rje-wEBX0RA=w80-h119-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdesadUovz27jx8mzDAgKoU8ObbG9yOFzS92xfqNj7xbAT9UiF3PuLMH3wOgyPBkwnv1cXTcox0vys-V60eQh98wATKjfX_Fb5ON7PtnytVNAGzyK9bXjQVxGTVyNpiRr2n6qeQz_i6E7gs=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>restaurante-terraza-zen-velazquez.jpg</t>
+          <t>cafe-de-la-iberia.jpg</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Sushi Ichi</t>
+          <t>Bar Tomate - Madrid</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2502</v>
+        <v>3839</v>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
@@ -4611,100 +4599,100 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Cocina panasiática</t>
+          <t>Bar de tapas</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnMAEvD3S0QBSBRq8QtB0OI1KIcCVcpGb0RHyGh5oYVS_QEy4aXNWCOjoPFcGD__XLsnIfNiDFbzH_hlTi-zU8b0kXgZ_DPsYZ_-GC2-PqzQeb3mN6lm0e2M749k3uTjvZvAN4W7DUBE5nN=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdDQz1FieNnTt4_BxCOt8EM2r5tS2qHfCuYaSOZNOz5kpwuKkaNQmF1c_znqFmvuO9O1-yiv0--9OggZidc2LhmeztSxL6kZGyAYfhz2hmoGyLg8lq_lozbMKZtZnlJW6hndPJe=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>sushi-ichi.jpg</t>
+          <t>bar-tomate-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>La Sota</t>
+          <t>Lamonarracha Pozuelo</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>589</v>
+        <v>350</v>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Parrilla</t>
+          <t>Japonesa</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmHXd-NYHTOm-L0Gpenn_w9j8vUuz7cm8i4256hF4TkY0AN-qogCi-h1WTBIHfgipBiH0iaVf9ET0260KXi2AwDyeOktehJw6XZXcig1-sxrjp7JsKwJPzodli_8R8N6mZl8jFmNA=w116-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcNoIaab5-D7PY8e8QYJ7fFQv_upt8DUKn9-v_ckemZo95qrtvHyHNVTHoNH6NeDvAy0ojmYDwhvWnfMQIek9SCkmXJ2huPGCanpR9Qr-WceGd4VQBsWVlzTKxrx47R2skCBAx8=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>la-sota.jpg</t>
+          <t>lamonarracha-pozuelo.jpg</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Makkila Serrano</t>
+          <t>Los 33 Restaurante</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
         <v>4.2</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>4307</v>
+        <v>2321</v>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>40-90 €</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Mediterránea</t>
+          <t>Parrilla</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnBGlI-x1cYnqirGFsfvlxJRzG7Y7Ay5H6M5rs_sS-Oylt4IQ5Yt8XT1TBpaC3TAIlmDDe6HULfBmDDKcvId_CU2-D7VsD5UOV4mldUzS37trPl4Br_TXlmszBGa3ZI9G8nqoiIfUMWKIwG=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeKRNjgIoWSbzZ2xe6JTPz0dRmCPnK1qWOF8EOF938pMAdEE1hAUs8nKe4NmigQt6kKjxhnpmT76WyJIHygVCQ7av813bvn60IEEweYT0xnJCAl-jqBVFwf2yayQE3sZ1PlAstt=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>makkila-serrano.jpg</t>
+          <t>los-33-restaurante.jpg</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Luma Wine Bar &amp; Brunch</t>
+          <t>Chez Pepito</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>308</v>
+        <v>1192</v>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
@@ -4713,66 +4701,70 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Vinoteca</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl7lQ_SsSMCWQKtvTRRTcGS98f2h_hHuPh8YV62t92evyLhmuY920ADdGidPZkZborinOQLo5L0BbAJ7VykhVMFLkTw6tX54gYHcq7DRrJCHASmLYPIvUxdtgfVxq_2CsdSNDrqf1BMhDDP=w101-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeZS9LJAW7D2LWsyJANI8WJEGRv1IieP4x4_pLSR2e-la85rEy4HC82kzcWfvhEG4QaXEhIS1DqWwp8Q9JAJ8vcHRJGX7cD9e6w7paUbyaX6T3HrHRBIqSKHl16VZSsDJQFIk6z=w80-h137-k-no</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>luma-wine-bar-brunch.jpg</t>
+          <t>chez-pepito.jpg</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Picos Pardos Sky Lounge</t>
+          <t>Casa Neutrale® Musica</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>368</v>
-      </c>
-      <c r="D128" s="2" t="inlineStr"/>
+        <v>1133</v>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>20-50 €</t>
+        </is>
+      </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Lounge</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmPlAg62VWjLDijXEInLzAdRRniaQPUURvDjEuxvgFy6aM-S8be7I1cgAh5WWxvcMF6eylFHSyGPUkiGOSFi07Tjt220KD7qHN76eEMOSlzEGxKUgZv168EwcYfRzKKnwMbLm6JE8bfHuOF=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeTBA-j7jGekodtwnH7qN2N5vaPXKCewHagdfTJa-oEB6CuqullwFeFhOrn1sTf_MGxUSLuCilOPN81rbQa7nP2Io0wmGx6UG-3W-aXDe2RmAR2bxrUaGEz63PDztj17-ct70Eyw2gEZn0t=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>picos-pardos-sky-lounge.jpg</t>
+          <t>casa-neutrale-musica.jpg</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Nolita Madrid | Bites &amp; Wines</t>
+          <t>Caja de Cerillas Restaurante</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>30-70 €</t>
+          <t>50-90 €</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -4783,64 +4775,64 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn2f3c-hNlVutkzKjyNC13W53g_70aLZQ4CKLedVLFNure8Pf_emTsEHX7Z-1YYhG0Vn-WTVvXjPeNq1hx84MF7J_zvq_cfpktYokv8C4xjLMeKgy52FrvH8u_urD7cvlQYFAJYlOulRTU=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcSUKeMUXOut0KXyooo3ga4lLICZz1yYGLL12H8bnMWhQZTd7A-ZFLn3YWPJWIDBEM1tlyb5FUSgQraGRhR-E1Pz7QcXAGgqSNrZq5DEovTQwE8IhPPpjsuKBgGu-UQJ5EN0W37a0OSe0Q=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>nolita-madrid-bites-wines.jpg</t>
+          <t>caja-de-cerillas-restaurante.jpg</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>AREDNA - BAR MEDITERRANEO</t>
+          <t>Marisquería Moreno III (Getafe)</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>1112</v>
+        <v>7016</v>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>20-60 €</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Tapas</t>
+          <t>Marisco</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmgMipgpDm6J8TJPWpSsg1oT1PLuxp5JO60sJeGqfSF8ZPXwQq9BPsFVqU6hfBKk1LteI1clzufs85e1J1hQCbm8XRkYC6XRmKO2l5T0sraWMFOi5jGMSWKLfEUwt6Hk8MzatVp3w=w92-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfIUQhdpRuOgLGCbKphX7h_5b9oAngmpSuBZjOudH1fJgUYK6FRYbaN6gbZJ0A3qDS2B7m5frrPkbCi2SkR_IHH5ESIiVRA-WZLyBtiIoJjOQ1vNIUAETKvLcWDkpfrVRCmJwX-wwHzyW6X=w200-h92-k-no</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>aredna-bar-mediterraneo.jpg</t>
+          <t>marisqueria-moreno-iii-getafe.jpg</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>NACHA</t>
+          <t>Restaurante-Terraza ZEN VELAZQUEZ</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>772</v>
+        <v>601</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -4851,26 +4843,26 @@
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkZs1A6whXp7NZDHhJ2Im-KO-UPn0Nf6wWLHfJ_Ety0cbvMNHZKZqJnW3JJ7U8qvk3Dz6tMPFF7cle50CnDPO_IczILRTkXpwrfqQPMmgy3CX8JWvO9oKZZ-mUWGhY58A0rct8-=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdSXGXKQQjVuyGL2h5lmJwJvB4ywen3qkNXjNjdCTUgI-e4DP-ODOItuUUNGrk3UsWUfB4eRjUBLhH9ZE5zzS_wmb0hrQHRZ2xcNIyFlKD15ygVTzRRBhiziLYcFXLrm1z-nsp8=w80-h119-k-no</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>nacha.jpg</t>
+          <t>restaurante-terraza-zen-velazquez.jpg</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>La Finca de Susana</t>
+          <t>Sushi Ichi</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>8012</v>
+        <v>2704</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
@@ -4879,308 +4871,308 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Mediterránea</t>
+          <t>Cocina panasiática</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl8FPE0oXPOvolN2G7Vfk4ZSKlkUJobZZc-_nOTt4oahrsw-MxJBNdfc8qlmvq25Z0YMo4QfQG3yzA9hBJ3dBXNunR6KZrLVO40JlsjgJSJ71v6CI-Qls65U-UOKB4oUpU4mEiL=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe-WdbPLOVeYdBQmyt8_BVcvOIA2kfc58KoeX8CdsY1hSc1hmee95RpXKrwdjbGAVWgZFNoLKKJHC8MVg_BbDFCIF818sGnvdPenAWb2DrQcpzptiNR9U4QhwVlOkuEsckTXAj4QW2e0Cnp=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>la-finca-de-susana.jpg</t>
+          <t>sushi-ichi.jpg</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>La cabaña de Patones</t>
+          <t>La Sota</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>89</v>
+        <v>592</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Parrilla</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlrAxDG33xbn56W4_fehxv9kQtrQPlg6wxciPtmK-uwKjCa2CA8F4B43GY44yP6QB2R26bqFrMjcnTQzhC3OlQtj2CURz8GcnWV_DTxKTag1LbiIVvkPu1pC0UyQBpJgr8_v-7jrcZbq3L_=w92-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfOOxL95I6gzW8HojA8l6Z3D4v9jLxzeCU4s2-VsRumTciXqhiGhZFD8oyzm3XFuVf4WMtGO1GYLoVM-RPs7ep9fwrUwZuw7oq6Zyx-RfiqIhcgNha4U0MJMEpXAAbf5zRT12e9Ng=w116-h92-k-no</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>la-cabana-de-patones.jpg</t>
+          <t>la-sota.jpg</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Chalito Heron City</t>
+          <t>Makkila Serrano</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>2748</v>
+        <v>4335</v>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Mediterránea</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkZrxIzooG5v2TlhYjHS48ABmycOTEjWKgHb3iUOrlrzYrAPPwSMiSI7loKfMEX6lU-_xOG0cExt0wrIuMffHz8V6W9nn0q_rWuOPN71wFfKwTJeCDiGZBO2sSvXbEfDbUGQTLN=w139-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeeRUUwFQ_SpsmWTyg-px72sbS0h0FI_9oJcDepdCk1EMVrA25oJm4mtq1_bqFzUnsNGs58n77iiVLaThmjf9VNm55AwBL0OUHw-pzpBYLAQPjlX7u8qtc94pzDUXC2sH2nyW-ZuS0mQSbp=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>chalito-heron-city.jpg</t>
+          <t>makkila-serrano.jpg</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Taqueria El Chaparrito</t>
+          <t>Luma Wine Bar &amp; Brunch</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>2811</v>
+        <v>327</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Mexicana</t>
+          <t>Vinoteca</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmg8OScFHyEfI9teI8tMgDX1bMHFKzJRa_BZ7CCbSREJlwM7ITo87rfRaZKiuBCm08sE9B_EpiX_FxbftiKnKukPxNTE68uQZ2G11-uBu2xCbAp-l4wUo8oLBiY-FaHs6653mYPLw=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfF298uAV3kJ4I5p4eu2n0IRn_J_fyIZI0NN_KHLxmiKURzQOeQdXvWld5bp_Flb_s-fLFNMNMbKqmAxjoWln29bmneIJVkOghLnVYIDWJARFZdOChib3VPwGQueS0DTjQ6wyndXaMTIpWn=w101-h92-k-no</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>taqueria-el-chaparrito.jpg</t>
+          <t>luma-wine-bar-brunch.jpg</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>La Gatería - Taberna Castiza</t>
+          <t>Picos Pardos Sky Lounge</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>510</v>
+        <v>375</v>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>30-90 €</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Lounge</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkMmSTUtFJCMAMGW3K77eUgjSJIofpF79DC4KgTGuAyUF5XpFTliDApM1xuaAS-EzO-W73XiSKacJ0ogOCmYFLtUB8GYfDKcGNVuGzQLUvnTYj5RAy-9SjvN2G2atGNWo9MRZyrCg=w80-h119-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLejQiZ1N2uv_z0wyIGayCm8ZHvR-O9la2gYiyGe7ka9WR0hxJKCZ_y9pQVLytKxLWPFLJOXoBnH83yTM_ZmugdkoyUheef0tHcgj1145qV_q3yQhbeixJcmPf4nupLpLq8Dq219lh4JqCg2=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>la-gateria-taberna-castiza.jpg</t>
+          <t>picos-pardos-sky-lounge.jpg</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Kazu</t>
+          <t>Nolita Madrid | Bites &amp; Wines</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>1133</v>
+        <v>379</v>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>30-70 €</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Sushi</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnW46ixyY3-5RRAZWpa0clnsSTwxkYpzqAiXZHzG_hW82HjxQkgnJncps6LiPlk3cfjjwSxjkXAIYtihdfee8u-Ecy4O6E7RTTta8Qcrcuk1sxe9srfq55-uiwKhGcndB5kQ94oEdvikRiH=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdJTDs-XrUiraiUC5HeX6Z3cR_ZBi_u2zZARBSzzxFygvVJi3GgKnh-N2o3_rJEvWwNTkUTuHG7GfmOCyk__DUoXZU1-za_-hntogD9XM3i9ibZ4NwbxQ_LQ3Crye3kFFjnLLTejO-6eI8=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>kazu.jpg</t>
+          <t>nolita-madrid-bites-wines.jpg</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Jurucha Madrid</t>
+          <t>AREDNA - BAR MEDITERRANEO</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>2786</v>
+        <v>1246</v>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Bar de tapas</t>
+          <t>Tapas</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk9H6wPuaBE0FcapS_nYyU0kr1HN3LrncbAJkr9lU4lVlVpkQmqsxZHNDv-znnfT41eKlIHF6Hxx7dbqjKQsQbOAi0vrf-eKn6GI7GfU7vcHDitmv76IP-mR9zFQAklcIXMflEkIP-TByM=w92-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcPyNojU0hK84rZb3JaCc4alHLDbVfzuVdEq2SjvtoCeApB4F3ixhtrHgIacOtf7Fdg8lqu31cx6adCwgOI4q3wKQXU-CCR0v9_PYpQmD6T6AstJCsaPV8vuh9VcFjUJrTHL8oI=w92-h92-k-no</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>jurucha-madrid.jpg</t>
+          <t>aredna-bar-mediterraneo.jpg</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Bar La Dolores</t>
+          <t>NACHA</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>3069</v>
+        <v>790</v>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkyyjl2Kfm1886XTk7OPOIe56-upq7u9zGDy6ai24VnZa4melfBeG99o0maCcTgE_RG8esUNSCLJFoqHmDlcmCm35vkPGH4dkYuh9gZTDaOJCAJZUtFShicHUXv5_pOMzLeX6fYMjIWSLF4=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf00BWmkG7wSGU9Ms_gtW05WiinxNrMcP2XBAQlos4huA9FJfBWTQcIimzsVzViVM_HFBefhG53oaMMk8NIRNftM4bLNI_OJ3OATBDshXUbL2Se31sCutf8L-7rOIWeMvnRmiRw=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>bar-la-dolores.jpg</t>
+          <t>nacha.jpg</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Tasca Barea</t>
+          <t>La Finca de Susana</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>996</v>
+        <v>8167</v>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Bar de tapas</t>
+          <t>Mediterránea</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnAarH_QCN_94bWRcAXHIg6gkcMzdUEaUjTYwgg9tgVDDRTdQ7SBnyKCq5PltK-HX2bXGyqKC2aZwdVJ3IoMG5wZeaEDBhxzxKLgVtbpJkXqzFG6FqDsYvpQpoKW_D2Y8mhKJliFg=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdD13-R0VcTFGRIf4cpjvUEtxv_qU7WuUg7czMu6TXJPACG4Tn9__L2yaI_s5MueIBGVm61eD3pMkiWHLg8PRQR2rJafDZ7sCwwWT9Z6kuXQGxi4HXJyB7b32G9Ftb_hKnxEkCFJPo2s30=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>tasca-barea.jpg</t>
+          <t>la-finca-de-susana.jpg</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Mercado de San Leopoldo</t>
+          <t>La cabaña de Patones</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
         <v>4.4</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>1222</v>
+        <v>97</v>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -5191,60 +5183,60 @@
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnb8RzYfX852xk4Y31chcaA9RkIREQGhGFmoFFUDcv79wMlilQB-zgaCCcxH4PqpQTF7mQ20gjT87H8HzDh-pW0FgVq0IKQQv7bVGwrvh-4x4l5fQt7gxw8uKgpKYAJr18mHKsuoowkLBY=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc0tz45fwdP8zb8IO69gX00Z6K1CKFTfjuN6GhzkDFoBzkLH-C6rf3QOnHfzg25MZ4yPLc9voRGuD00BZNHcvAxiXEEkkeKc3O-CZO6Ai8ENYfw5KaLKSM8g1gNVIf-uWKhxjFNQocYy8qN=w92-h92-k-no</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>mercado-de-san-leopoldo.jpg</t>
+          <t>la-cabana-de-patones.jpg</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Sushiaoi</t>
+          <t>Chalito Heron City</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>10611</v>
+        <v>2875</v>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Cocina asiática</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm3evZ_9EGmBRW2p0oFZZxwTaZtu9MdDeoaev3Ihk1le1ynPPBeW_00PrgCtZGKSx_lWX-ZBU2C4mMe_H0UQHu9wzofxgNsnog1eGSoKgiUfGO34X5-k57eKiZnSfwGNdjHHrMJVPRYKR3Z=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdRmv6lgf9QwYGvD4dmU_rs4po4-BY71U9U_SaO_J9ktKzwQ8Z6q0aSrVIRDTPDyDzc-CUMf_cVyOmihDAn4_Nudx-gkCChmkUESGfybjFlosw8iwzaoAHbeJEYXVq2MffNSjDm=w139-h92-k-no</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>sushiaoi.jpg</t>
+          <t>chalito-heron-city.jpg</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Saona Las Rozas</t>
+          <t>Taqueria El Chaparrito</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>1173</v>
+        <v>2836</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
@@ -5253,32 +5245,32 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Mediterránea</t>
+          <t>Mexicana</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnJ0_dHa6n3cQR8iZyK-RCfxlAB8hAXn3xlGGarSg2s7xi44aYBfTCD6T2xVC4z0wmTF-lfky4npCjMEI0K-cIGfsOJjXc7zG8HOQJfltC9ubBuZE4HxhML22ihyzHmZL0onHAEjMQtSgA=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcvx_IZ1ePLRXQ6_JnSFK6nvBp4DP3ponMLA5FeSlGJynSU9nUCmhD9vGdei0p3Q3s9LPEsYTVFnIY6sWEUrvbzgblLL9OiG3cP9G6jhQnxVRJFGngroKS2sRgUvCJevnN9faHGWQ=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>saona-las-rozas.jpg</t>
+          <t>taqueria-el-chaparrito.jpg</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Bar Cóctel Prosperidad</t>
+          <t>La Gatería - Taberna Castiza</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>152</v>
+        <v>598</v>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
@@ -5287,100 +5279,100 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn7JGAwKEDOJOmTP1NEUdBOAn1PZpAi-cK1D8OTS1U24fbOHPWQ3lpSl3FMh6THzMXUsQ0PQ3O3YUzlfayq8se6Em2atU5u8jFYIwwp1lML5JjnoB7KM4tdYKeSoH0cScXzvZUb00Et6BK8=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcBI4HIQRoiDsGLHo4mA7a4HLhX01lXP6mDxKJKWK_nlTvnWBzW5pWacTiaJw6F2ihzad4gjK_kXF5doUcqJn9tEG727WnPEYlDa-umeKyXsA2c1Yqq78dV6MJRZzlM9M2EFixiSg=w80-h119-k-no</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>bar-coctel-prosperidad.jpg</t>
+          <t>la-gateria-taberna-castiza.jpg</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Gamberro Taberna Canalla - Olavide</t>
+          <t>Kazu</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>1250</v>
+        <v>1146</v>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>10-50 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Sushi</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm5pzw3J35qdCSLGxlO0jDBRf2mNnB_ADTDrBK13GfJKcHdJAbfmpz90CH88VxMfRJZ6arPuKx_1VMkK7a-8cVZ3Bxxy1PTiakRogoxYW2i_SDPlC5pzVIDRDls-ks6hcFxLBEm5KJeIce-=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe-9wFo27k5DDvdnc1uCz2Yd_kuwuzetsnWdFfv4i_gOMyQ0ltShYVlJU5ysy1iz1EqD1AjsRWXsaDrcFe0vX8mY3lp3cUVPOkA5_xlwb_dY0qmuL_hJ5NbvPhrGntXI9-V1IexUgSg-A5D=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>gamberro-taberna-canalla-olavide.jpg</t>
+          <t>kazu.jpg</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Taberna Los Gallos</t>
+          <t>Jurucha Madrid</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>4317</v>
+        <v>2839</v>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>30-50 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar de tapas</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkFakgzAKJOM2lLqrnql-Lr0h-cxu7wiAn4zLF56L2_RjCd3WSoGIg0nO6EOnX7razK3ERnbX2EWUTduogHhQZyb9c0yyNR66ESGMlK9NXfYO5Jcsf6kwqZyTFK8Ay-5LkKRkjF7EaB-do=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLflF8__ij3_l3iWXxv6Qm6J0sbRbys9ANF5c7Au1z_-N3CyP-BYs0CGb1NUZkXOZY6VMXitpkWhpz8Srx6qqcj9D-ZIerJeVK8PK8MqKBLLVLeFkYqIfoZHp9rPPpPno360L_ArnDEKgq8=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>taberna-los-gallos.jpg</t>
+          <t>jurucha-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>La Paloma</t>
+          <t>Bar La Dolores</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>1647</v>
+        <v>3101</v>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
@@ -5389,70 +5381,70 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Marisco</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkbClm0S7_I_GAqgb-ZMxHN3IKRzDUB0OZVquQY8ffMUhm2ggPZm_Mp44_t_ClMAiEM0ezLL2L1MAm0pzI8MYFq2azcSg12J97kULRABOR3X94Paf_4TU-V8G_WfFLc4ZbbBPpuHA=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf3axs8bXRJB3iE0Tm4MhIV8t8FncRKbCxgMKHkVhJfXmxtqHyVEw5Ud5-bH15NWhvtNtWDf8-GGTnTktR_NlWb5GSeAPSMMZd88ZaJ39AINoM93NFFHkgDmGsh07A6RRa-7F4mW1DoYZc5=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>la-paloma.jpg</t>
+          <t>bar-la-dolores.jpg</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ULTRAMARINES DEL COSO | TRAFALGAR</t>
+          <t>Tasca Barea</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>1542</v>
+        <v>1000</v>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar de tapas</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk47MaevpmhZbeBq1dOJhbesUqWUxUAwxYSdBNqknAufhJKLSlgiytOh1YtvvelojBPstaqjzKfUuMaxLIvOV2B4eohnWQ3WNEQJj4KrlvPUWjSIhw6fuWJUmx4yuJHmbEYoUbz=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdXqaPmOZMk868IqSJQWirqDPIazB6RmIj6Ec7Jji3FMfY3f4FlngVg6ASLTAFi2B_3hiy7MeuO17TddAgJSDhIYatanM8pGNZZONTemO5vUSbO0330Mdoh3pjWmWye0RWsAzS-CA=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>ultramarines-del-coso-trafalgar.jpg</t>
+          <t>tasca-barea.jpg</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Alto Bardero</t>
+          <t>Mercado de San Leopoldo</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>1265</v>
+        <v>1246</v>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -5463,94 +5455,94 @@
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWncge-M6-K7-6By88NWjHdcyAixskpW85BFTfbi7asBGnUeMLKkPuR2TV3T31BcfN0Q9lccUGomC8LijjzSA3kVUUxpsXaSsmQOptrjIYRlKhjvb0kLUgHyGWTV7cCtKSXMF13YFQmJyo1b=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcQwbyctyfo5BvbVXC9-D-676f0F06ktpRkaSTlEQAmetXtfDLbO_FBU27FgrzPqRmLlQhOcg1vub50buwJnySzlTtPSEYR9pF9UTe6Dq7us1Xx_X3i3IXv3b0qytOqP5fGk-C-wjTRET0=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>alto-bardero.jpg</t>
+          <t>mercado-de-san-leopoldo.jpg</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Taberna La Cortá La Latina</t>
+          <t>Sushiaoi</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>1243</v>
+        <v>10806</v>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Taberna</t>
+          <t>Cocina asiática</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn5phprnXu109fjXyyxpJdNYWkIYJ9gWqWU8Ljhn0lpPmB2bA0vaCMpNZ2kwEO6MFIUcExJQ7yVtR1E0Yv_0AgBeabXj-c4poMH0MCK_qvR5ew6PZ7r1JR6V8AtaZR0BeIzb2XqNX7FdQF9=w80-h100-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLceS8HGfA1buhYgHkmBQccoigxoko8_05d_fw8DeOWjGMD3IxBhQQun4aR_G9ylX9f8Vw4h81jIsugSkL-CiHSGQmYkdhoKFJGacwBLUAMendRoHgvDEAMeJCRONEbfcuh09YzljlLEGZCC=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>taberna-la-corta-la-latina.jpg</t>
+          <t>sushiaoi.jpg</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Ichikani Madrid</t>
+          <t>Saona Las Rozas</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>5509</v>
+        <v>1192</v>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>30-50 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnfpzlbFvNbpViJULMacs8snaVoEMuHZHerKcffJQ8ALdi_BGZtLknc-m1i-XSCZ0mV1MQIMyJ-6KvemBGVJ71vqo-tS4iq1Am470oGd0OAjtQPX3cUNN0Yqsr4mQUIQwkWHxPte66mv4Sh=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLd2eBHNgXNXmuml6MYLvqF1Tq0Y7S-8s_E3zgwwiFf454AIJWSWyJH-B19dU3ArySPGFstb4YrP1QTDdKmBIE6kjnUN_EKvpPGil_cjK-9wYt-lVFdmPKAM9-NRT1bdQ0WKfqK9p0JpEMY=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>ichikani-madrid.jpg</t>
+          <t>saona-las-rozas.jpg</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Xiongzai</t>
+          <t>Bar Cóctel Prosperidad</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>2744</v>
+        <v>163</v>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
@@ -5559,66 +5551,70 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Restaurante de cocina mandarina</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnbZv1QV9XfHQikQWxCuIDShQzm4s6Es4KwNPooJ_uRZODp_Kbah4BYiMTZsb2fDre0j_N53FhQbMKHs0tZGwOZUWIvND0IyXI8ED4JZfxW0bJ5QEFO4sZodGqQLJ7LE7ZfbI1v=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfNx6SId9T1W8GDjBARdEHB6E-XPbYHFK4TitINO0NjpcyUY5bjzYr9T2aoq1IfggIDjKsvc-AVEykrnK4CuUUzNnAXAIYWAtUrakbnUdXFoWzOkxJkgDmZy2yK2NuUVvL-0AbYrXPI4P85=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>xiongzai.jpg</t>
+          <t>bar-coctel-prosperidad.jpg</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Cervezas La Virgen</t>
+          <t>Gamberro Taberna Canalla - Olavide</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>3069</v>
-      </c>
-      <c r="D153" s="2" t="inlineStr"/>
-      <c r="E153" s="2" t="inlineStr"/>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>Cerrado permanentemente</t>
-        </is>
-      </c>
+        <v>1340</v>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>10-30 €</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnXO3c8vtm9JKn9BtndHHYrR9uCOW0NHdrnvt0AzcWpyKPl5uPpXdvGR8SLfcQBoxhwS0hSGzVz48sEuXXs3s4K5k38kKWdtfH-uSxDiJ9jZWNpo-DE7aehvUmf6D2P0FWVeQRf=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfFD2u-_yPI2tX7nAYnT6ocSYOSLKADnALYNQu03iWe3PASGASiteMPN8HLeL_SseF1e2QfZJJKxN9NjBa5Oh-k6Avo-44bEDFtckX1m-OS_EU0aMTFSManJia_NROMGYQxRWcMB8ztbS4v=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>cervezas-la-virgen.jpg</t>
+          <t>gamberro-taberna-canalla-olavide.jpg</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Vrro Serrano</t>
+          <t>Taberna Los Gallos</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>6094</v>
+        <v>4376</v>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-50 €</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -5629,124 +5625,128 @@
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmSwI0jGilx4_UgYWqHzMRkIKCM-ZckIUCYGWXIRAWfwuhdohMWRM2BUjDWhJkIgc-CfRsQCMZOdKSJtXkDPVfJWwClvSxStE4xuTi5ZeCG4WSPDrRIVn72rgOMBCYk3kMMn88ORYYpGy8=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdAHu7fFfv11OcPDPqmJfBwC1Cm7Apb-evAjhzjSl89-o8h328tgPxpM7-NBFfDF2HBLQ7li6fAK12iatol1W4H-pTHnTcUqeURqrDjcLGnnILmjJSGcQZhWqsOFZMCee5VanIQefqADZc=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>vrro-serrano.jpg</t>
+          <t>taberna-los-gallos.jpg</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Amasa</t>
+          <t>La Paloma</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>1059</v>
+        <v>1665</v>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>1-10 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Panadería</t>
+          <t>Marisco</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlStWxnhGdyC12lYEQE_0tTF5C6GjX-RC2e_vZTMlnpESPzDUut114TUCEJFESn8Q3ZAUyPr3HxBOiRDEDQU90EZmhxlN0X2RxLkSJCtOuWEdsCuW4t-3zdaaBki3ynrVM2JFg6=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLelTBi2qnjqHAy4KQh8OjxJfgB_rXeGnnBek3svH_Kzu9xHqRo_K7kT3ru7af-S8DsmrOEsxTi-6lMCgTWV5l5oon14bPp-VjEp3HIi0eZN9M6yGiuU5wla8hDhT9zN491MkuaDOA=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>amasa.jpg</t>
+          <t>la-paloma.jpg</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>La Junta Gastrobar</t>
+          <t>ULTRAMARINES DEL COSO | TRAFALGAR</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>206</v>
-      </c>
-      <c r="D156" s="2" t="inlineStr"/>
-      <c r="E156" s="2" t="inlineStr"/>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>Cerrado permanentemente</t>
-        </is>
-      </c>
+        <v>1653</v>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>30-40 €</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlr2KKoy4NHWDEVVDe_RDTL2y7AfJkg-z_Mj116RT80dQX6ThS4uue_KH4lrj8RaSFtLJ-SknxP5NmpjtIR4OA1G96guJWXqkQJ-d1sy0LCWctSHiQiYh1TyyUk8dUno1m8B7o9=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe6vVumrLuRufF-5_cVPgBcjffb7EdKSpEpMSqylhWvtJ60vTqk4e1XckijTX8XX6Xtlp-MDvKTGHspC5kB8MZgjaZzGmagaee-HMME7Uq3Os2zJwCLaE6S4FMqOegvx6Csqopn=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>la-junta-gastrobar.jpg</t>
+          <t>ultramarines-del-coso-trafalgar.jpg</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Restaurante Allegra</t>
+          <t>Alto Bardero</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>4256</v>
+        <v>1310</v>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>30-70 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWno_Fx9ORouoNDgSdb1qfhcfZmK57JzwSb2TYEUGN4HQbRtHgxJG-9LNzg86PNjCSI4QeEo2YGHvEmw42HvY6H7YzkPwl1_bW96GHTHfT-ZlLrpxaHdlZWm1pulDqse1sUmXKrC=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdlCR38UvL_SYl8Lhmxn9-b-qpWhMKERH2O9GsL_F1J1kofdb2NhwOhdAbf4Om6iyGsL4bqoD_mQKQ40o8Kq0OHUABLXlTcacgPJ0x2kHqHIgGx1YbzbdbKBVKIlC7Hct3DEKnJ7o1DAJ66=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>restaurante-allegra.jpg</t>
+          <t>alto-bardero.jpg</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Milwaukee Burger Pozuelo</t>
+          <t>Taberna La Cortá La Latina</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>444</v>
+        <v>1351</v>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
@@ -5755,232 +5755,228 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Taberna</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmB8uXSZceBnxmGCurFGAVWRp47YbAxbmzZc3sPisF6ELPltUvEnuDT1kCSyar3RI1SMNbRUQlGxCedbXasgjS5IsW2d0emOe3WvBVa8PDq--R2gOizsUDsONGh9hezO4n-XsUErLoqGd0=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdZpT58_v8qQPcje7dumN9E54hF8V7cy3Dda1fyFdEQGOc_K02QpthnBgQUggRKai0VIKOQU5hY8ceW3ADdW3HGXVVDVoJKlMEDUcUT-lKNNv2mQH8bAiPFEU3sBTAEPUBTXNRslWyKsmMs=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>milwaukee-burger-pozuelo.jpg</t>
+          <t>taberna-la-corta-la-latina.jpg</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>ARMANDO Restaurante Madrid</t>
+          <t>Ichikani Madrid</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>238</v>
+        <v>5827</v>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-60 €</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Japonesa</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkvn5AYHbfrXvI2zqfSjQpMs4s9OmkEk8io0aEnahr82vVFEhXG7YOUB07Hw4emoLWcTnGAcrwA0j-xDff_px_ATCMpGcC_ZFtExlZOnx4Q__Mu0YhYFc_JaUJwaV3gVQYScAm-LU8Xdlw=w80-h98-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfmkS3s2Puc2eDXtl6CyzP6ZQykmwvDyol93Zy7zreKh4KMWQ6Idy8LVUKPL0tATuLay58DECFTm1S4eKUON-DwGQ6w8yAABGKy04-NBZOt9bzVz3Y7HHI4bE-u1oafZdQ49ogx8uLXF4se=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>armando-restaurante-madrid.jpg</t>
+          <t>ichikani-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Ancho Madrid</t>
+          <t>Xiongzai</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>184</v>
+        <v>2756</v>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante de cocina mandarina</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnenXRZZ_OBYerFhVBpwLXXRK-9P0JS0HOyn1PvBPR061vTJuZDmWcFCQeofA8ysflNHdYY5fVhqrpZ6gKjMe-inX5U8vDA1DU05v_Xh_iZOLHl1q_qH-OcxZmUS-VUyMUYORn3yzc4-O_q=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLerTbDBsAOazeKBRt-dqD3HhZvgoRQadHtaWqG5ESJaIdgyebPJaHoghPbJ1X1ayG5-ButNgFIb-EIFg97oVIGPeTLtgEYyJwYQtUFAmqRifTIg3dujAjcraSrZshcT9NbgE_mp=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>ancho-madrid.jpg</t>
+          <t>xiongzai.jpg</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Casa a La Malicia Bar</t>
+          <t>Cervezas La Virgen</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>220</v>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>1-10 €</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>Bar</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr"/>
+        <v>3068</v>
+      </c>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Cerrado permanentemente</t>
+        </is>
+      </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnoM7GFX6wuXrrknBjx0V2m6tLyKDasI1Btv4bV4DACMLJ5CVVtiHH8uqmKCMEwiQyHLp2lJG2iqO-fHDgEw_fZ7xIoPcOO99CJhMotiz9CFYHmVyEZ6avLtDhegArjCOkg3bsJ4Q=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeYKs7lc0UUBpvEFvdvhXvQOLndZmbU1zUTiNubhbHIHtu9Jzkt4ZWIC_rXJCUtyI_s9CN4emAO1gL5e28BQHSerhn1AJ3_DnEDuHu7Ejey8kSr7PXhBm3DkZnaFMGgg3NSsmJa=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>casa-a-la-malicia-bar.jpg</t>
+          <t>cervezas-la-virgen.jpg</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>99 Cheesecake | Princesa</t>
+          <t>Vrro Serrano</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
         <v>4.6</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="D162" s="2" t="inlineStr"/>
+        <v>6147</v>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>20-30 €</t>
+        </is>
+      </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Repostería</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmLL_jekVVNTnpVGOYwjqifT51NXYF1C5GhVEpq5v9nUDdidpy8k8PjzdBwU1821k1TWbenEvhxRRCAc2CNtK12j8vKputAt9Ez1lZKTGtE7Z3-OPJMGtwL3VKh9HR3skkjZ8KCXbXI0rLv=w89-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeGZ8RDo0-C5_TOLMN5s5yKf6x8KJvu0X6NxOTiyeYka6ivIilipSKSvcgtQBa4mgqS9LzijDsfGPFYChIjTPr2RSz9lgJVgHlAvcyW9iLmrY6GXjnqoG5OWxEId672_Q3QIMmdJO_QIsY=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>99-cheesecake-princesa.jpg</t>
+          <t>vrro-serrano.jpg</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Z&amp;Co.</t>
+          <t>La Junta Gastrobar</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>1316</v>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>10-20 €</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>Libanesa</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr"/>
+        <v>206</v>
+      </c>
+      <c r="D163" s="2" t="inlineStr"/>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Cerrado permanentemente</t>
+        </is>
+      </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlXcCd_cE5kNWE00PvW553rK7EyIogcLLTClCqlwLVFsA2AbSU9i2yIUTB8idfePMtoEHlTcigiYd9J24dy8u-EpcFha45kKkbVOH8BxpJZ53pJ6bbeaiajfribowFbk2TDE6w=w115-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdRdQjrY1AW0qWUolQ5k6bzL1LahCcAz7joa1E2hSaaO6rjZfcDQ0Es9PlvLNnSVUV29VYtzKklzXY4SKvrRhlnkJj86HbZoWITPOcYy1Oa8RsZwZaCgMl9jtfJM8F0Q8m9Bx9q=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>z-co.jpg</t>
+          <t>la-junta-gastrobar.jpg</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Wall St Madrid</t>
+          <t>Restaurante Allegra</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>419</v>
+        <v>4560</v>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>30-70 €</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkHi3Lgp_3Yj9wt4vgA1oSIa_JtCtj7RjGhbND5hT3yq3AY2CY9254AYshpiIazZ42rP6BeRMSm88asoQ3aNqgnJC-CFz7D2ycPcfyBVm03G4OkITFocSIG4weBMRm1FQwM--e0=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdKRhUncsnnLzZdN-rLtFF3UpIGfH-Jv-hjYwEzPe8ThRe7wHVMwpjAGtL6u5YN--KEX0z5b7GMS_mmnF2xvbOOycuRGRaX0jE38UM7lmYnDaOqEFVmx8_nahwawBVk0RpSJItG=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>wall-st-madrid.jpg</t>
+          <t>restaurante-allegra.jpg</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>REVUELTO | Brioche sandwiches, Brunch &amp; Coffee</t>
+          <t>Milwaukee Burger Pozuelo</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>390</v>
+        <v>509</v>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
@@ -5989,32 +5985,32 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Brunch</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmfK3ecwp1KBCUDxN6dCJqA70pgrH2NfKG7lsDomBMq7fInbPd3or2ybPemLytTq26yVayvp7CmSlXk-9Pj-gr8UOqF-WgSU6MZynG6s4R0t2iSq6XBBJGi9BxeCNDM-j1M8heSbsiWKP_N=w193-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLefSW7EE1jOtMDMouUnWCR-ehtsx_DN0qS2KnbFmqPeFaGgy4SJ1D_VZDgkDTUzfakzy2M3ZUxgZRMQ4RcZAph5VcLBVcsL-xKoi-h2ZhapDs6m2w8JC_OHayvvKRP_8B5h_ZfjRQzNnFk=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>revuelto-brioche-sandwiches-brunch-coffee.jpg</t>
+          <t>milwaukee-burger-pozuelo.jpg</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Restaurante El Perro y la Galleta – Malasaña</t>
+          <t>ARMANDO Restaurante Madrid</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>4001</v>
+        <v>260</v>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
@@ -6023,134 +6019,130 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Española</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkbp8VEU4GVRT19DVy7rphHluzcXyM7blQAEsobdcdpggvupAmD5UOHyLSNV3x8RNxQ3EbJZz82tWu8lqULGRZKJfYTYtwv9asVOVp0u_llO_T3wojvqXBE3NXx6UANeR4hzXAwuXcbfJam=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcJpZ9wQwS6XfZ-1XPgkiol_C8x6wHC9zEjKxvbWSwdBB_82R8sctFpFZQDHQrOjWR09fonJc8obZ1LwpZlJubzdK9LNZCj3Qgoq1cCFCYh2MCN1P3lOh3SlZtGu7ku_JF3EU3D2E3sGVM=w80-h98-k-no</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>restaurante-el-perro-y-la-galleta-malasana.jpg</t>
+          <t>armando-restaurante-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Xihuramen</t>
+          <t>Ancho Madrid</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>1904</v>
+        <v>213</v>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Cocina asiática</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmV59HL7K3xWwnxQnRu1yMRwgw1Pp7guppkyZ0vM6uhCXMg1DK4v-QUf1Sqw74nHoki79qLZdPvAMnFY5cf1_i_jgpt8gq8bfLzS7lVZ7dRq9FTgo24B6CE7i6wj9HfvYi33dmUo_iVK07l=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdpAIWbmHplWMonQ3a26iYUNX-4ixguY2cj146QtGTDw43gIJVLUnSgM07wDVSyZDMpQgCEYI3LWsqPxzxbEdF01a5YM63aH3Zsk4TmnTbovc4OzJwGNG1O_cb6xoc1_2JOeFz6CjcOFSJl=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>xihuramen.jpg</t>
+          <t>ancho-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Giro Handroll</t>
+          <t>Casa a La Malicia Bar</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>167</v>
+        <v>220</v>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>1-10 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Restaurante de sushi para llevar</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmjJipUmK6ZvnZg1l9WfKEpLp3iXi08B0RKTsMHTp43wY3cuT_JKc9RXPBHprfJ1Maug-lLxeYB4k38KDPZTZ5c6gRRQfD9xuaKST11cJsmrO5HbChDEKlo4HVpZXCCu9EDo9yniJ4zd7nx=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdFgqWBebmnxfBSv27_3YvcSsUNWLd452ZNdM-VMgevDsCUnFYot8DKOU0uxC_-RIUeCtxp1bAnRkuxcAj_I0xegg2cZ140geMOrgnN_Xs8wuB7KQKk0C_5u1DtQzTzH29B2x8WyA=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>giro-handroll.jpg</t>
+          <t>casa-a-la-malicia-bar.jpg</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Restaurante Garrak</t>
+          <t>99 Cheesecake | Princesa</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>201</v>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>40-60 €</t>
-        </is>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="D169" s="2" t="inlineStr"/>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Repostería</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlFKvu-TpV97nj0N4cmKZMQk0EmTPJ1ZvHUGOXnxK3-11VPXjJeexT_7rD4HmS9lv-rIXX94_xrO48LMlvTm2N1mulasQNy7OE8s6X7q_IHQFt-2eQYO67IstFdivepy8nVwf7PQhbrwFEI=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdLdoSQTv7GGjvreEFYql9UqJei66r4BGvBK36hMKbH9XSe42ammLDn3ReW-aE8BomuinHw-XGIwmR0rXWJs-o-rqO1DaYq_Ib9Sy8ivOl_jFfQDraDQI_tjPRY1CpAiiXB8_kHQEsEInGk=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>restaurante-garrak.jpg</t>
+          <t>99-cheesecake-princesa.jpg</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Nolita - Coffee &amp; Brunch all day - Chamberí</t>
+          <t>Z&amp;Co.</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>688</v>
+        <v>1331</v>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
@@ -6159,32 +6151,32 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Brunch</t>
+          <t>Libanesa</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWntgGk1DOhDxFjJQ7vnsTiDfbkmROiCpDMKnOx-dd5d3QOQBgg1klZTTJhPYsQhl40HLPfWEPZAuyPh9RzOZZEnpyVjSRdxdqTXlRUlolBgojEy5YcX2vVNkqZCY7MjRvbSieQNBuHavFg1=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdx7bSrJjsyIVgjey-Z6hnmqAUr9yF8yX9weX9jkq4xNv7Pkv0ceSXaDa8Cy-QT1IXtL62ebDYn2EL_SAQwEBWxkWJeJaSFGG1DA7ntBQdaWcE8x8hwoh9TGSFwC4A_djceeXE=w115-h92-k-no</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>nolita-coffee-brunch-all-day-chamberi.jpg</t>
+          <t>z-co.jpg</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>NAP</t>
+          <t>Wall St Madrid</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>3854</v>
+        <v>423</v>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
@@ -6193,32 +6185,32 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Pizza</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmtJGLhoXbA6lnL9LruHQySC55yVSGDQCeqXD-l8zCJTrrtf3aERoaNoutAm7i1qUP_Rw9LT1gIiraeu-wgvG0cGk3W7k7SmuakGwiZ8nD8PIGstpflpsf5kn-qCvhAknnt5C3X=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcCe01SGHwxGGLFDcIy10iEIoW89zbOlDTPIOUDaPtDssZOX5EKOSEEdrhFMdWVhd2UcsUgUHjc7V9bnC0WLInjKxQax2QtxatNyU9QAE4a1uixII8yk16sb3n1zDCrXHz5RB2P=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>nap.jpg</t>
+          <t>wall-st-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Pizza Pronto</t>
+          <t>REVUELTO | Brioche sandwiches, Brunch &amp; Coffee</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>288</v>
+        <v>410</v>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
@@ -6227,236 +6219,236 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Pizza para llevar</t>
+          <t>Brunch</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlVsNj5QDkjzHNbsPXWe_seVczmAf1g527WAgQKj4ZL_4k069T_4sj207bPH6MFeS0JYsNB_8hhwo4IG7zGiVIGF-pBNjY7ApB5OgOl67caOGQZ1uUY_OQqCf7PFzqzAApJkjSAh-S1LRc=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc-M6sWzaaUOBjjZNswiG1o4T_rHpQZtvRTHv5lBbFZu04khuf0qmf0NemuJuHMQTanasy3mTeN5RdrXMgeO2t35eEO1xsOcqKp3S7v0wvpsRHVwUXxcaXHIYeN7vsPXY0-1EsVUACJ_L9A=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>pizza-pronto.jpg</t>
+          <t>revuelto-brioche-sandwiches-brunch-coffee.jpg</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>HUNDRED</t>
+          <t>Restaurante El Perro y la Galleta – Malasaña</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>10297</v>
+        <v>4124</v>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Española</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk8g9XPieZ0rpJ2AF3CSBhvvpNea6AAADzjKNxkPykMQHg0BRTJdMIrzW54LxLzcCPJc1jbuLOBbnTH2a77cfjPiTVo_wE4cA8G6D-MgG5dwbcGkmhft8vaaV6B7nwmrGnfAYj7ZpEJqdw=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf3HgVAhyM1TSOmCLxrulFW9sv7paZUDWp_4uIKPrFw5xvTw6rExGRJ8WPGbZpHT8896GAVsuFk4QmzTJ33r7pdhWn0Z_0tQj0WGEM--vez2wQP4QR8Ay0-hiSswTuFqd_k0ixkQmoCmC3r=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>hundred.jpg</t>
+          <t>restaurante-el-perro-y-la-galleta-malasana.jpg</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Olea</t>
+          <t>Xihuramen</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>576</v>
+        <v>1942</v>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Cocina asiática</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnrA-AHwWR1yB1KcXKcQbJbENPEVkEI1jDS3YcXa1Jk4Q8KQl0YeeFEojK57RPkK6KHBLZdYMNm9InHBxbzQ1N-FtYbPkgC-B82DQyf_AXZT7SKPHEUBlVwkbx3O7SX7S_vfkr07g=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcEtPBuZaqLsRDNMfoy6z7roZFY6qHV469X3VCGagjNcSMmGQpPXuH_yHr-a_nDH-5m2f2AxDwOaIl8DxWh4uwd_OzXbB54WiYkCbdBqExNNSTuDt_1kvPIxwgq89jEhUYXtm5YyDiFdedA=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>olea.jpg</t>
+          <t>xihuramen.jpg</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Casa Tabacos</t>
+          <t>Giro Handroll</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>402</v>
+        <v>177</v>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>1-10 €</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Española</t>
+          <t>Restaurante de sushi para llevar</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnrwfhPJiwQ71bHgktbGYa2D1xugjx-0vtQEgX1YByNiByvY5HRkI6XjWsBtstPmWKWS2NHBIE3hlwani4Vgz3lmNdd6pJZBeBis7MZI7zPe0rmzVshWGwuaKD0-A29ThQwZnUJ=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLci_USThO_UshebW8KD0o1jdJ0QnPUF7TtZVOYMfDm2kQ_w6S47nsEN9DXdUDihkH1eG41HhDQpzvVBNkyhkfOXAKH5ylrgyJreXz4Wpj7iW41ZedQhuSN2HC-FU3-GPp2-2e-vN0PBp00a=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>casa-tabacos.jpg</t>
+          <t>giro-handroll.jpg</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Persimmons | Restaurante Georgiano Madrid</t>
+          <t>Restaurante Garrak</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>1724</v>
+        <v>211</v>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>40-60 €</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Georgiana</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnz4wJoU_mmglk-ONZZhO7duc24Y09ZP9J7j-p4FWA9zQmmBtZZjdC2U-SrZchv61C6IB3dII_-s1Oezw6KH_wq6Gt4KejtZAXF2r69N0osmdAC3gKly0mquQivpc5Hz--pAWcjanKkPmU=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcMiR3yiQO3kUp9AjFvmQ3_8RehVeUTsOLzfI7vWHlLHyEVmXwkJeFfR6ZDJyXYg2JAmPAp53WnktjgDCsokfNGIfdSIDAWNSCFqlqsehK86RH6zIWOhAjSDLwfABF-HNQtTdgz6rJNChP3=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>persimmons-restaurante-georgiano-madrid.jpg</t>
+          <t>restaurante-garrak.jpg</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Bodega de los Secretos</t>
+          <t>Nolita - Coffee &amp; Brunch all day - Chamberí</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>6477</v>
+        <v>714</v>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>40-60 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Brunch</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkjxoZPrOdjXH3UAEEh4cgxpFP4qhsI6XgD9iAZJjI-WrOBNWm7RcSfDJ6cG4zyDFICdq3SkgVtXhr7cvqjUS4XTJbJYjBfrSvjurCRuUDo9IVcvxTqNYdQldgJlfbRYHR-mbPB=w150-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdFiE9hAYYzeEyj4Ik6u4i0vccMd4Nd8MP8UbCaIkn952VzBLcNwTvXRFfPWzzgxxxwkXzuIU56m3Q_QcvpvD_DIzCwRRtiLRlr1ocbkt42JQoEOrzexYIuZyqaO-3aLmFmcYV36RzWBawu=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>bodega-de-los-secretos.jpg</t>
+          <t>nolita-coffee-brunch-all-day-chamberi.jpg</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>La Gloria de Montera</t>
+          <t>NAP</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>9391</v>
+        <v>3883</v>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Española</t>
+          <t>Pizza</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkW8R9vY9vjKJa5XWqO7If7wmEZ6MJYpy9_2cU8cMag72hx5QyTRUsmZP-FK_P9WZPqIZzPbKjn8VItPLPRwFH8atId6Ocm8vrM_INK3EUbjeSBFE6Yg-vm1aEFFwPsgkymCto=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLepfQQUVflPXADbpi3ld95Bipb9tg_5q0ZY-0UtnWLj0i4SIOBveDrjbqQCi_0mvdIz8Fhe6WnsoR7tYRcQ7zeljH2FkMZif8VSzoNKXhQYgt0BDuiDOkEqsLgsTlwvkNv0rI0F=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>la-gloria-de-montera.jpg</t>
+          <t>nap.jpg</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Poyo Club</t>
+          <t>Pizza Pronto</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>817</v>
+        <v>300</v>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
@@ -6465,66 +6457,66 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Pizza para llevar</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnq-37-KgDL85yQ2uLvCejm80_jEvI2XwB0I7GIfuARfqVh_yLsD_qwtqtf9Ass9HuvXQFv_mbCP9ixfgXhqCMrXePaOC0Es3gozANSNSdo60vUzupLMxyMfaJMh0QSONVJcsKJ3WIXbNZ5=w92-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLclaiXZ5LM1rnZdAbyJeekNQAAgZltwLz4jVQjAl0USxBM78g-xsE1Bmhlk7I4lqXfMbxXEVG57O5XqPwP7eQdotO1JhxD7jP4-A7N0hHCbrIhLBXvn9AyFbAHx5LMgxr52wQisdGaLLMY=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>poyo-club.jpg</t>
+          <t>pizza-pronto.jpg</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Sushita Café</t>
+          <t>HUNDRED</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>4884</v>
+        <v>10620</v>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Sushi</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk5ENBFxDLsWLMKESI_HIoUTaKkSc05BTNvHEpB_3VkI6KVlIMrGmJWg_7fWRz_arxH14frJhnFCd-_O7_XMbcDtN58smUuPVq5607cmy6Xb4blUPBld7qWWcj4jGGiMPErZxM=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcSmE07mCgoS8M7hLKs2YqwlJEGOjCfy3CCOv9tSkXqEUjTgDrx5bdr9454umKYtNzbDat9VmBA--QJd6gz2t-Rfq6L-QtGpgDDxoWqXO97i4DhGIHROlgpO6JJcZtu9JbLjFf_469c6Gk=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>sushita-cafe.jpg</t>
+          <t>hundred.jpg</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Monsieur Sushita</t>
+          <t>Olea</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>3770</v>
+        <v>585</v>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
@@ -6533,32 +6525,32 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Sushi</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnwNvfM2DR0qgyLOetV_93L18yPO5xIgCk6jubKoAIculjWYvsjdPtEBRm5EKJsN6LqPHIzXGe2QN42o1mY0BOiCeWKGHM9U_GTsMgfFIP5M8mh5p3l-S8qbLYe5twK6NVtJ16G=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcdnTX1JSG29fZU9UpcgJGTMoesVdxebPtsdh4PGCwnTyHPKhTnEwD-nF5Y26fm08fh-j8Cxq2_ewrv4-BP2QJA-j71ijYfvIOKh586Hcnlmte0YEsj733Y-evOyvrweX5Kg-by0w=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>monsieur-sushita.jpg</t>
+          <t>olea.jpg</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Dolce Positano | Restaurante Italiano Madrid</t>
+          <t>Casa Tabacos</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>2629</v>
+        <v>417</v>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
@@ -6567,168 +6559,168 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Española</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn0qRcRlsyL7G5xhHwmVyC_Ad1UqTqO3tBN1DIOFRyQY4mEjaTAPURpQ7QQtKjm_vUDrs-lPx1eAZupEgxS5v565s9OjOZydnyc2Tu6CORsYi8cKum-9AClpx4mgcae9sHwPhp7fxnCTWs=w164-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcwu0K4RB0-9TC3wPYipuZ11Yr5SdZtO4Yvxjzyogi595ktCAwRA01tKa-pkAqdemrLmgD8aosHDO_rAMCrDxis6XhysRx2-4CBwjCZ7o5ngyCkRdMfoCEnNX4pfIILR_tME-mv=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>dolce-positano-restaurante-italiano-madrid.jpg</t>
+          <t>casa-tabacos.jpg</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Mawey Taco Bar - Majadahonda</t>
+          <t>Persimmons | Restaurante Georgiano Madrid</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>771</v>
+        <v>1770</v>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-50 €</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Mexicana</t>
+          <t>Georgiana</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmbSDqwcVZxzbKM-LMFn37HHrZeREVLAh9uM4D-koFz4oV5wT0963iBTsZNufEQ6s51CWbOPu8xDUzr2f7YMkxxkjkQPHBdk7e4ZFFieQ8OosaEvznzniG2oB5BFdI0E2Rl8OWjRg=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeRVA-ufmo8AUb2KPGO5dBkiVmeapM7VODkUcxQBV3QQuGVBjg_WztdJ75fym4riu3GVk1YiA9EjbmObsknUVZ5b6nPGw-Akp_eMPsnE8cFPYqhYAt-ESoSTHgquFECHPb_C8D6P9KqOL8=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>mawey-taco-bar-majadahonda.jpg</t>
+          <t>persimmons-restaurante-georgiano-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Bar Trafalgar</t>
+          <t>Bodega de los Secretos</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>1819</v>
+        <v>6565</v>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>20-40 €</t>
+          <t>30-70 €</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Parrilla</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlFcfuashghttHiMhwyh_U3NAdfCGjooYGrhcW2c1HgyurCXV4hFEMgL58I5ZFxeuk0KQt0jDYx-BP8mpHnX4Hvnq0wo9ypdrOAjiJ6pO_gJUHbAqV7negns120Zvk74148WWFD=w80-h142-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc5aOyKpRl3fetaayiaQxsQILYXBokcspqkUJVh3Uis7YTMESAQgNCYPNGHVP0kxmbZk2-ntgzue5BayzKRs0YTjlwvudWY5DAUFWomUs521v3FCMfLkrmgD8SAThAyPMTfFIyq=w150-h92-k-no</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>bar-trafalgar.jpg</t>
+          <t>bodega-de-los-secretos.jpg</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>La Alquimia vinos</t>
+          <t>La Gloria de Montera</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>345</v>
+        <v>9606</v>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>10-30 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Vinoteca</t>
+          <t>Española</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn4O9177RvgABSCVIwLj2g1V8XzwE-ijeSAuoMTBfDo2-i0HBhJOlS9yQOmSfrV9oXsPSYBn6qtlL6i5EdscaWaT4it_hsbmQLH_AK3yl7MvgmqaqQJrNLpZwO-xZNzHujsGlfs=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfPpWuZh9NKWyCeACG8x62HpfvOQpOP0U057BEx69sD1gjlucPAgwF4PGj9eYq_JDige-zucZms05K-8KgOzToaBEAet0xTmB-W5m07FOvHS0f01xusS1PEfzKnw3DgXDc20f5orJxnpfY=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>la-alquimia-vinos.jpg</t>
+          <t>la-gloria-de-montera.jpg</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Casa Botella</t>
+          <t>Poyo Club</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>182</v>
+        <v>841</v>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Vinoteca</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnddzT4JoveyUvfvdol8QFAKYHfGyE1m_hwFgdsSWt_B8jYiSDsRCUt8INx1qcMrg6sVHCg87EA-zf_CyKXU9xoebMJ0KUhmEaQRDGzLc7Xx9hPtWgIFNvyLADm1bL2dcwFd3dDjIGZ_YQw=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLekYY76s27b_tgYWXXE4X0ItsMCGyz1T5UPdcuz6IlbipqKB3sfeyEPo5pvMIkqHhXs2nojsS8O4fb285ybTp5Q8QKPbFYWHh6fcmCC7FyFbKADnTJsTF3bQ0fSHCkmaDNi-7Mb58vEcWGT=w80-h142-k-no</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>casa-botella.jpg</t>
+          <t>poyo-club.jpg</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Biri Biri</t>
+          <t>Sushita Café</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>307</v>
+        <v>4939</v>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
@@ -6737,168 +6729,168 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Sushi</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmq0f8OT2dUDgN0xbZ9GLda36tm4VGtygucuHxqAADAQwq1V2EqR02n9yrgfqyZQuGhRYTXAwmqmgzjmU_jqYPHmfzHNKdQgw-MCyAuctKIncFmotQOfjTVzth2WlW35_HKBZ4lcouiooX4=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeugoLpAkfx216YvuXLp3jr8meGvvQJNF1duQs_3EbMSWBcSrCsQgB5D_kOs5ta5wa43ISmOKpxAXb6wFGcuyFOVK1rW57GVl0_h0bXBybQO6o1U1cG-MuIxF51UFhH5YrVRjM=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>biri-biri.jpg</t>
+          <t>sushita-cafe.jpg</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Croffle Madrid</t>
+          <t>Monsieur Sushita</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>368</v>
+        <v>3865</v>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>1-10 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Cafetería</t>
+          <t>Sushi</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnPjDc5bh4LFSIEKpuv05Oh4WOJJZSkppR_6SbOMQyk4v75geNMLW01jXLGK2NkaHK9HCszashkO_E80ECXTQC1FnhQLxCmWc-YtkOFhmiu3B50RUUCyg81D1fmoiA-YSIzqPJU=w80-h142-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcAwX8NtzIAU3q70jObfPhjeP536GfsgdsyuviIR-Cs6SXghb4ldmUnWK9C7Uo8FeQhRFHU_EfIxHUkrrH4rQScAUHerSy2DgoLhJ7v3hym4uGXjwaFO1otIxUQvFoKVN1X__rz=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>croffle-madrid.jpg</t>
+          <t>monsieur-sushita.jpg</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>TACOS REAL</t>
+          <t>Dolce Positano | Restaurante Italiano Madrid</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>111</v>
+        <v>2947</v>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm6HgvQrzMvPYUdgdIV9YjCoKUPu7FHvOYLGvj3_sxhJplv2Y_jJcNurlf5nDpZT_qwuOY_yUp8H6MLZUOQZlyZyVVzqFOv3TgRoJinx-08h9g3vziZp4Ztqi-ZzZYatQ0HejzOxdNXoTY=w80-h94-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfsAq6pWNCLuEnD0RL_zZpyOMw8WEW51Tv-R_8kIf8b_OL4SHINW2KFE_tbGjiW88kNFmqWoTDNLvWAOBK9pSY0YbwljRGcbgkWjOfacGVJICih-2XDjbUfjbLO0SRzLc22r76H_dfXrpM=w164-h92-k-no</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>tacos-real.jpg</t>
+          <t>dolce-positano-restaurante-italiano-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Pistola</t>
+          <t>Mawey Taco Bar - Majadahonda</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>642</v>
+        <v>785</v>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Bocadillo</t>
+          <t>Mexicana</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlGaY0aM7AgZeYu0xagcYF8GesroW3sxZGXz1JXqTmXndps7FH0vSAXvBktPYtWzoFWOVeartR0DECK9dIC-TXLRQ_6yV0pVBoxLjMrWq8jROaJniiWVJ02_GZOJtuhbwLSFuL4pnOBQwqy=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdYDuBh4QBsdrAJKJwSGrUZOStgKydYd240vDo7t8PfemtgnQb8nYesdKgzMewuLEQyy5KDqV64EgaLUUFtOOGU-5UFZOVMpMEUt0dildaoT7RsfDvJhNAfmYdRwwbhGkSKo07RGw=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>pistola.jpg</t>
+          <t>mawey-taco-bar-majadahonda.jpg</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>DUM DUM | Chamberí</t>
+          <t>Bar Trafalgar</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>2025</v>
+        <v>1865</v>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>20-40 €</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Dumpling</t>
+          <t>Parrilla</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmqyiJa348exTrE5CDlfaOT1DN5dt2NKQFmnRs_grLR3Qrn5C5tKY2tnw8HQKJkQx3OSH_ICxUdbroSZSgxDHuBpmZ-MDhigorF9dtIy10A7TOv-CszWKfYcd18YhzeHoWJsIobewoJH5Ha=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeVneDgBupZ1zaZYOuUsaBIETb2KX8TxTMSw_xkhokwoUAcFwD_8_TGKW2FQWWAfJllNI2g2NGZV87KjTgUwxmLpmCPiXO5Ba0GyWTPMSgQx9W-VPWkFOKEieuNuPnb73fbTLR6=w80-h142-k-no</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>dum-dum-chamberi.jpg</t>
+          <t>bar-trafalgar.jpg</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Restaurante PAROLE - Pizzería Italiana</t>
+          <t>La Alquimia vinos</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>1948</v>
+        <v>350</v>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
@@ -6907,32 +6899,32 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Pizza</t>
+          <t>Vinoteca</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk5ufatZmRUeksQFfy8hfSZSAJclBPfVZll6DCmHt8scoOrmnpc-oOfpcKkb1E6S3nwukJWE6IdY-GhrI2rezkOwOqA01K2j6dUv9bhiOYocICkA1H8isXl3vu66Q2kmBWsvTLP=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdBk8sSmk3cZIKhHyvVHJiq7S1koF1tRDUkzbiyl-8nrFqBgHaIGtdrFWQmPnr4GljV6W0vhZRXwG8xkxXn7X5hLI7UUR6xkhMqPJ_Gw7XpOWBwhuBpwnv_gVR2icKqf3SIPVCQ=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>restaurante-parole-pizzeria-italiana.jpg</t>
+          <t>la-alquimia-vinos.jpg</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>La Casa del Pulpo - Bar Los Gallegos</t>
+          <t>Casa Botella</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>1826</v>
+        <v>206</v>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
@@ -6941,96 +6933,100 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Bar de tapas</t>
+          <t>Vinoteca</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkUwVPBYFVB6T-qaqtm9ewH1mqU4jc_ORURELD3-zdJWsyICMpYpArlhFk8kpWnMD1MSceo5fDPQzfxzafI9Cz-OCKKnzq80jQe7edOCeFGNVWehTXdRX3ZAmuZuuAtlYCpH3b9IDW4da4=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfm_xDbpcbHlvz6yiDONidO4JVFbPqDx7NcfNQyQNVT3dM8pevTwQ-MWPmNAQfjndN4jHj7z1medELO-hj57XqZIT-uKpuFxL74HCuwwUu8Y_3g9bMB7YPHGtrE9AEBZKaTS9iAJe0z3pN4=w80-h127-k-no</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>la-casa-del-pulpo-bar-los-gallegos.jpg</t>
+          <t>casa-botella.jpg</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Yakitoro Reina</t>
+          <t>Biri Biri</t>
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>11291</v>
+        <v>325</v>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-40 €</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWk-uaQDG9sGGGLqhOTjREIou27tPtIePPXFmYia08XmgYhjSvDIitx5exq4q_oHtwvKv_7Q3bnR4y37tChFm2MsaJ1y4B7O6uSrgnq1qp3XdJ0CSZ0je98C1VsMWqjqzlyQ1SAg=w149-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeGy0ZrWuqA-HkDry7ADFJDnej1XY8QLi_BHDbuKfursda4P87SmYZof7xCNVwOEiK-3YR1V0hW-4E9hxbXZSajK6DqLe1X_9yQV5TjSrHlDESBWlMIxCY9cvanAhB8MD6dOsDR2o96ZIvm=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>yakitoro-reina.jpg</t>
+          <t>biri-biri.jpg</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Pecados</t>
+          <t>Croffle Madrid</t>
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>4689</v>
-      </c>
-      <c r="D195" s="2" t="inlineStr"/>
-      <c r="E195" s="2" t="inlineStr"/>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>Cerrado temporalmente</t>
-        </is>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>1-10 €</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Cafetería</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmX0luTULxC6m_L6d0I6vDuCNdPMpikMLmNtGb5TX0OCzSRycAkXyz5QPdeCVTkSFO96LgG6nDUnDSaKC1hs43V40zPLsQxC3e9OEXH-sNmnaNScZYT5BLzoqB3p8kqi51K2-HAnG-acMas=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeMrP3xmtTiAugKPZTZ7tEUEed80mBm8OBjPGJMLxJzpcQL2h2RBUIiIGFf_NB7IWXkJPHpgfiXftvX1X0LVcvjyJoQVG7LZNI8OfQ9x4w82FtNkgRVAq-1y2odMC1WYvqEpVRT=w80-h142-k-no</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>pecados.jpg</t>
+          <t>croffle-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Neotaberna Miguelín</t>
+          <t>Pistola</t>
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>248</v>
+        <v>697</v>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
@@ -7039,66 +7035,66 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bocadillo</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWn1LvjVRJL4DMByI785R81wQTwxO8Jy6FTRYRtQRccJfS1dJg-Xp__SBoYAc5f23Q2Bj67SoNCsh7v-zJK8-9PItwccMz4DbzseTQoG3ly1_lKl636dJnO_NKFIcAb-cEBcn7qtQw=w105-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdQ5oRHY4K7Z0hr-Gjf8gO1DPsLOvTyXChC7IG4gbQG8Q7kc3wSFfFq7jXe2QxgTXSg4evcw1O10_0_G9XVHjCFzwa-PIwOkhVNFnvMmuxYOXLeLgENaBr1Ue8ld7S4qEc0QIh533V_V7U7=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>neotaberna-miguelin.jpg</t>
+          <t>pistola.jpg</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>AMÓS Restaurante</t>
+          <t>DUM DUM | Chamberí</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>291</v>
+        <v>2055</v>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Más de 100 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Dumpling</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkCNTPAsIFYNaoUbXO4qVdTUIJl6inFsN8kx3WddoQgAMQLnT0rXLuDH0SYsufUx4RTC-XUNdzxsHkGqSMaCyXl02Z_iblM_asrpFcYMqaei2fhWS6xbgUkR7k_ijfVL0xmdHUgNcXhsWc=w163-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLekU7g2Bwzj5VHi-G3bb4Om1QzNwNBYbGTjl8sJGL0uHikMVkb-3ssc2iYkFUqltycPLmqe4n82maC6TYIHzxmpFT3GCkDdOLB66_sV52oHiKZrlxlfTHhOz8l3istV-Txp88VVYYSoFp5j=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>amos-restaurante.jpg</t>
+          <t>dum-dum-chamberi.jpg</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Casa Macareno</t>
+          <t>Restaurante PAROLE - Pizzería Italiana</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>4763</v>
+        <v>2005</v>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
@@ -7107,66 +7103,66 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Pizza</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm-EVEk5BuAIf6AXhm3QeIyOeHvxnebpBg-1ruB5ejv13gTneDJ0mHUm3JIlUbN7aJNVKzyrl4bN_XYmF8M7MfBON5lUpOYru3LVUdVjDp3DiEznnpKuKOAWHKZYolFgMpBWN5nwD9tnwA=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdhG3zuYNzY87KE4TePVrip9CuV6lSSg1V2GEwXWOQfnd93pR_SSAif1Ggoy1Pc4YbTNfFeoqpWkXJsvdEwDNa2e5r6pQp7cXQPiF8ZmB2PpNeslhe7cnhb54u3cQ-UzcCLJdpr=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>casa-macareno.jpg</t>
+          <t>restaurante-parole-pizzeria-italiana.jpg</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Pizzería Piccola Napoli | Cuatro Caminos</t>
+          <t>La Casa del Pulpo - Bar Los Gallegos</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>4276</v>
+        <v>1843</v>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Pizza</t>
+          <t>Bar de tapas</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnzzwMFMDKcKtJoKJW1Ab-fyIVb2uUg2TWHIUmMBEeeaCXQ6EmUsU5afClFpCZGrFdX1onr9TJs2cP8HTjE69Zjw46WvDv1i2jfE9YCMks7xYRrq2JdoUXbnePBoJ9iqFQz90QrDA=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfs-P5OYTpEAgOzHxCFrob93xwHafQZzSNvQFvwGOsfGeUGK9ljcqxJNwOYpy3nQLav0BPFRCO-cPjZZunDQi2PiW0t65M80Bx_bQ7z_MVIoExMSRIO7Jn3Nc81qb8iTb3ONBx3CBj0oOY=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>pizzeria-piccola-napoli-cuatro-caminos.jpg</t>
+          <t>la-casa-del-pulpo-bar-los-gallegos.jpg</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Swiss Butter</t>
+          <t>Yakitoro Reina</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>5405</v>
+        <v>11318</v>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
@@ -7175,66 +7171,62 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Halal</t>
+          <t>Japonesa</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm_l8AosF2tDF6Rd8f2rIGT5txcveozBmoIg_WBcJP3U99vAdS-F8gVO3La4ZJq4TbQr-lWOM4x4UKIPoMmcef5zRkP4TlTk2Af3_d6lrobAn2hZTGV-gPgPjotsDjdUTXCv0m7=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdofu7cE66i-TKD_Z2GbY5IideHSwPzek6xVdtl3JPja5IgiLfVEkToegE3nLgeLdQl64QyjzC_WscdYyuzMVCyzWkw-ES-dbbawertGZh4mz3X0UAlubhBuI9wFQ2BmZg4T51H=w149-h92-k-no</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>swiss-butter.jpg</t>
+          <t>yakitoro-reina.jpg</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>La Maruca - Velázquez</t>
+          <t>Pecados</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>9162</v>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t>20-50 €</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>Restaurante</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr"/>
+        <v>4684</v>
+      </c>
+      <c r="D201" s="2" t="inlineStr"/>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Cerrado temporalmente</t>
+        </is>
+      </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkURIoTEUuVbhHpnGkhJ4EsTSFF_C6VpoiBwU4XeqwpkIz6wz-FQXUBu82mlj5dqfCd_Ui6jvKR4wM7M6tJmrfFkuO_xjpwEsle9slyvTlI6Jqk3izsze-bide09i3pClHarXVBqXl6Qpdq=w165-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcASKO2SL2chrePGA1BW-RTcM0djvqTLPZDLI6egJMSWLLpMp2TlJD7EvpkPYrjvY2plnN8yLpqVr3F80YA2sijRKBjeCSbNXIs-i905M-JnMsjjQHIPZ3aA1H76f0-DGpt5PEB1CwTCkic=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>la-maruca-velazquez.jpg</t>
+          <t>pecados.jpg</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Ristorante Reginella</t>
+          <t>Neotaberna Miguelín | Chamberí</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>3411</v>
+        <v>266</v>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
@@ -7243,270 +7235,270 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Italiana</t>
+          <t>Taberna</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWl9guvz3LePoJ4MX3MZbHlFP55To2KvStk8vIisEXH8a5SbdmkHKkH1mVsmNfTGtO2DjPhnNw3LYxFzmG7XpWW3Ioc2k1aEEfcxd4OOG129BK2fZpSegf1nPKMbtZnAMGYHNFU=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfogvGdZTX89-lsgGvC1339Vz4h3AHeEukIMnVJTC7neFqemiWiNqwravZnBC3_98FGZpNieSTwPEQCrwNO3H1Bg_AxEWE1acnyLNeLQV8dZDDRNhHXDyksAVTgMKKbLIbO5MIq7w=w105-h92-k-no</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>ristorante-reginella.jpg</t>
+          <t>neotaberna-miguelin-chamberi.jpg</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Brickell Majadahonda - Hamburguesas Burger Smash o Clásicas.</t>
+          <t>AMÓS Restaurante</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="C203" s="2" t="n">
-        <v>1008</v>
+        <v>294</v>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>Más de 100 €</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnQVFs7la_iFfYM96wyzWG-p6vqUkskS2voT2pSZR2yEvjZ9vgtlpyGdZMfSpmr9C4av1-sOMJcalAtB3KGXw7iBOgxQHMxLmj811W2bbvHqhCCsWx9Z99dYGBuVENhnbMN2gn5sQ=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLccvw_DmEGrgb-9IA9XZwuVT6ZPjDmFLI3Ojh3nVio-11jm-ewrNesGij2mlR3L4cxk0I9zPqcozmh6kB49rB4-VQGXr6s8QxDlQcYSX-WzP4glk5cTrXr5KZlwJh8hHSuEFtfE5RoDPK8=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>brickell-majadahonda-hamburguesas-burger-smash-o-clasicas.jpg</t>
+          <t>amos-restaurante.jpg</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Macas Goya</t>
+          <t>Casa Macareno</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="C204" s="2" t="n">
-        <v>561</v>
+        <v>4838</v>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm7qtPRk8xp7Lx-x9yohOl3kRquZWunfshm8SAyAQO9pLvaxQSr_oU97nmH2Oyvo1rU7q3RX_G1FzuPMiEHvORInSXK4iKtTdskA39j-yZuvpCmKy8xocZNeR4cenr2TJoUZvH3HMiYHbkO=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf4EqXu_E2sjCycUmuBx4LLXll_74kWj8QlgqwQxxngED0rfDi-eJt_Z8X7uBbA4_qlbFEAtgfD9y5cfJKBxJP7UThe-Z6s1BYVUX3QuLTKOgY9ueyzpQPuDMBsocJ3LFWrqs1XAcGeozi1=w163-h92-k-no</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>macas-goya.jpg</t>
+          <t>casa-macareno.jpg</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Pizza Wallet | Pizzería Madrid</t>
+          <t>Pizzería Piccola Napoli | Cuatro Caminos</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="C205" s="2" t="n">
-        <v>864</v>
+        <v>4302</v>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>1-10 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Pizza</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWma_sS1qvWDv80ytQwp5uf_fWl8iQwoBGJvNC4Hrx4XYAkA1bYb3I5-g6hLIiY5etQQnihXdAajiSkiWC4k8XJJLkHIgGr2EpkPmUyNj-NT3sGnPnDDMF2cKLlGPXkmjpumnG5OKzYt52Pg=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcQDwymF13uN21FwYHbLW1eQHYkpX7siAbOuspVsZJbqs_2oa3vO5XAju9Y9q1KJbiCPmNzife0dPTPW8-dh8fY7r8zwODWydNzN8PghfujnLwNOnQo-bJtvPaoXoWREuXCm4jXmQ=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>pizza-wallet-pizzeria-madrid.jpg</t>
+          <t>pizzeria-piccola-napoli-cuatro-caminos.jpg</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Watts Cantina</t>
+          <t>Swiss Butter</t>
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="C206" s="2" t="n">
-        <v>1401</v>
+        <v>5560</v>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Carne</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWku-kWAWPypnALdXRyOOOkAaInj4aqB_6cIEi81JZKeXltPTalWsC0GsQDy8XpYOyDUyJzXFxODnj6OREKV7ZaxUF-062gt7xhPU5jyoApacFuE5Q0oCxw0_26bfroI0efwcJKDSuqwOdOS=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc67jmVCVrWrBM_frXYIDrqK0Ystq7NfyjlTtXJzf2p5ag9pxWIenuhBk8jQLebs7OWVf-2H8b4qk_qtRBa5gXRsoxAJvh0tgu7PATj-vCl8vVhGtQFDJNnWOAA0U-9HoxSLwb0=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>watts-cantina.jpg</t>
+          <t>swiss-butter.jpg</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Bô Specialty Coffee</t>
+          <t>La Maruca - Velázquez</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="C207" s="2" t="n">
-        <v>2129</v>
+        <v>9245</v>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-50 €</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Cafetería</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmOFTKFMr8iyqEsQ3Lmptld7UFNi4jV64ev4cfA4Ugb_dtd51Ux_0kTy0YZe7LGp8d9mii2BYgAn7zl-3FWqjH1fP9tn0nangXmMd-mLUUHeADKIDXXtjJZdX8ZnuLQHUssQm2x1w=w80-h107-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLd9uLFgRn2oq--2mBTrlaY6FeS6dHpt7EYc2b46ivYgrA0o5bRXZrMk2JPP73XG2bVt4CkD34mr-3qxcuIns0y1pHGNC0DuLfn84YfkL-cWE918tmiXvI3ry-q-9Pl65XhG2uwvJ6PM2F8V=w165-h92-k-no</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>bo-specialty-coffee.jpg</t>
+          <t>la-maruca-velazquez.jpg</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Kricky Pelton Chamberí l Hamburguesería Madrid</t>
+          <t>Ristorante Reginella</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
         <v>4.3</v>
       </c>
       <c r="C208" s="2" t="n">
-        <v>1217</v>
+        <v>3429</v>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Hamburguesa</t>
+          <t>Italiana</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnQ1NANrSZJxcFWL-uPUHiWchCc8cPoGlYTAB8VirVuldpkAqpO6I7z63xXX0HSgH6k1xJJFlKgk_1HJTt7nfFJd-2iHc5KdSMjBWrVDBrsHrAltUCjHLQWDT4eupUbJmNny_Kbgw=w80-h106-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeASDVuhzez1vizTEtvB8b-9kHK74uIrgulA1IN_IuQG_XuCPV0DGFI8aqMrpfIJrPwGG2p-QD4pW8pmox1itcimdg-zs_6e298t9Q0VIsfQ-uK9Uv9Ho93fhutYOrqXdpQWHcxcA7BGGuQ=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>kricky-pelton-chamberi-l-hamburgueseria-madrid.jpg</t>
+          <t>ristorante-reginella.jpg</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>PinsaPizza</t>
+          <t>Brickell Majadahonda - Hamburguesas Burger Smash o Clásicas.</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
         <v>4.5</v>
       </c>
       <c r="C209" s="2" t="n">
-        <v>1147</v>
+        <v>1020</v>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Pizza</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWncEEJiMkwPNe176qLfrBwzoxQAai0gm7anSEVKOKjk0L8XgzCdFa17gTRswuu_T-lEXLzLuWO_4exJ5soNTG666KCQ_ivydO6-KWpuRe8P-tLFNBFhSZEm1OD7P7frJQCeq4jQ0A=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLevDeWBsuZbCh8glVN1-cZ4VoneqQnjqfrEI7ralWREJdBuwdV4hvB_EwT0R_CFtzILeoMR8IDriqysdlLYBTM5ZENDLW45LqwZZ_bnZzPCnpRB9AjMlDUcJP_MeKZN9DnMUtU-JQ=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>pinsapizza.jpg</t>
+          <t>brickell-majadahonda-hamburguesas-burger-smash-o-clasicas.jpg</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Frankie Burgers Lagasca - Hamburguesería Madrid</t>
+          <t>Macas Goya</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="C210" s="2" t="n">
-        <v>1473</v>
+        <v>582</v>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
@@ -7521,132 +7513,132 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmhKVCQ96vsGRXz4ZTca0kqEJUUM4e5O-XlAoa08fvobVqiMARLGkNGq2v2CxRYmiOHHZwEYwYZpLmZJuVlS4Mdr6YFn1fklLd0mP064w9tmisxbEfEidkxNtcOnjRogA-4RLOs=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfvENawel0f5zCVKLcSMwL_SMEVfQtzaf3dj8aNTpsSTavSmkMzySYPCR6f3ARzpZ-7JU3b8CJC2f2LozKdSTo6diqXMGTvTWaJtQ0W8kjWrxIDLc_CuswHzi5_4oDks9TYQSD-kszCeWT-=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>frankie-burgers-lagasca-hamburgueseria-madrid.jpg</t>
+          <t>macas-goya.jpg</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Amets Gastroteka</t>
+          <t>Pizza Wallet | Pizzería Madrid</t>
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="C211" s="2" t="n">
-        <v>247</v>
+        <v>888</v>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>40-50 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Cocina vasca</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWmje8PF2hqtOUeGQ580JpB_rrkTcx14yLuPtBnPg7QUJccwt7AFuodw-KnPovuUlkrTOpekt4nKw0Me1xF3XJpe6YpLzNIfz6a31Fmp336Zvly2zboNX-hc3doCWYv-Rrppz5tbag=w80-h142-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLfrGTVVCn5iEkley0gSATtMSAp588317iivG5F-bMlrFH9iicCKVDU9Eopaa5zkWbHUPh70jYaNbu2_ZoD8qDTwPdhLcNzE8FbajiMameKOLvjGFRBdX5R58b1fCcFj6JuR60j2hoRcHOc=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>amets-gastroteka.jpg</t>
+          <t>pizza-wallet-pizzeria-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Santoku La Barra</t>
+          <t>Watts Cantina</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="C212" s="2" t="n">
-        <v>696</v>
+        <v>1461</v>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Cocina asiática</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm6jdemr111CVr9aIMgVR0oMRY9EY75JvO9AP7O8R5PnE8E1FOlWM471fJeoIzQjAJPdwCXZgrvYLkMwrLbNC9awuKTyfbFLAc8iDkTOuE6hcb2kQUhpPoqBiFqmB7oSqiSLOIZ7j3GOqQ0=w122-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc23f8JxECDaUOIbuLbIKsugMVKNubVPmwxoGoEvBEu8MAwlomiRo990wOa0O1GKsmmGs0jckS3rshTyKIjknvLiVlVWdc_fFo8hSaOG_uFQQ1NHnTbMi-t2FTAso6DfyhhAvBYHe-SR0lg=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>santoku-la-barra.jpg</t>
+          <t>watts-cantina.jpg</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Raza Madrid Barquillo</t>
+          <t>Bô Specialty Coffee</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="C213" s="2" t="n">
-        <v>4339</v>
+        <v>2151</v>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>40-70 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Cafetería</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlcAmVkL6_A26sL9OklMJkfyrQgZRJmNXXgN2OYe8vtfQfAlgUKrpxi6uHbwZE9TxMgR1YK1JdZ73Q-LJcRI44d0mBnXjWTOoU12_xOYa5rOUg3Oh7vkpSGqiorv7eXqEc26l8ajA=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcNmJpS1J7o4ivTPkDKhPBk5EyRnkghbXY_ZRIQn4F_G8O6gewIT4_48J9J1WZSzQlCq2cdMoS-LzQFHqj7fMW43KpGGjPqrH0DCzIE6fdk-MWM40FiB5fs_ceUbq5ddo_2VwC0xA=w80-h107-k-no</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>raza-madrid-barquillo.jpg</t>
+          <t>bo-specialty-coffee.jpg</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Dispatch</t>
+          <t>Kricky Pelton Chamberí l Hamburguesería Madrid</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="C214" s="2" t="n">
-        <v>402</v>
+        <v>1229</v>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -7657,268 +7649,268 @@
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlvHpMEz1IRConmp0VxcyaH0t2C163h63peWWWETTZF2zIESdQ_oUqznKyttqKHJFJ28s_hMIK_LLDOXGnx9nL8gxPZbbqDpye7PsYJNQHoKMeVF8ISLcirGHRMo_d27k3OeF0QN-BWZQE=w80-h120-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdWjcuarNRrv2KRU68klwHgS6Z73fHr38BXj_EXAuSJdvov_dXWPdqyCTxzOITkb8lSO8k5qwYfT1Mt3R9RcmR3ctUNvdtcCRBufvhtbmWkqgD0eqUBiBhlZYjwasoc3XGTyvp2bw=w80-h106-k-no</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>dispatch.jpg</t>
+          <t>kricky-pelton-chamberi-l-hamburgueseria-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>HIRO</t>
+          <t>PinsaPizza</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="C215" s="2" t="n">
-        <v>532</v>
+        <v>1154</v>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>30-60 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Taberna</t>
+          <t>Pizza</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnmwEdQKcsT54Kf2c7IQu6tWN-Tdbm9VR4O84crwlPCJBTEYchkQfoBVPzKnCBrr_ccz8YxfJBfPwZ7xyd9zzXOS-Lq-JpnbyAqIwFwaAYF2wBUAshJ1eVRURdM8saYisdQGkmh5qaoVI_s=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcGyqeTXQF8D3cfmQ-5O3L9YKJdCh_n6uocV49Z1XAvpU4-iebPFNla99Y3CsEJZ-lcHuhA6itRrZUxXtZyOGLUBVB0s_CkeOviHDvABtuHZco6Yn_piUrX8PtN_ZArM3kb68K1gw=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>hiro.jpg</t>
+          <t>pinsapizza.jpg</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>MYO Hand Roll Bar | García Paredes</t>
+          <t>Frankie Burgers Lagasca - Hamburguesería Madrid</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="C216" s="2" t="n">
-        <v>244</v>
+        <v>1602</v>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>30-50 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm_mZL0uZd1Lp7JTY9K2gui-k_e7BMkA6Wf-zxYqLJsX81OHbkxneGASFCaoy6G0kpl-vOpxENdhM4yPCA77F3tcsdkCN99F7ZlMIdba-6uCAu_D2Pu6ZhjuJt2XS_ddEAMUM7_Rt7bS3EM=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLezA5_VdeaBEEmWGrsgu4DO6-Z6b1zT13WHFMntXlrnP_klBUKDsiKG-lRnOKNgxFIWbczZFHf7aZVjEAvvfm_cxsUR1AMQxasz5dFlplVeD_4vxngfLTna6E_neSFG9f8OS0oz=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>myo-hand-roll-bar-garcia-paredes.jpg</t>
+          <t>frankie-burgers-lagasca-hamburgueseria-madrid.jpg</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Biang Biang Bar Chueca</t>
+          <t>Amets Gastroteka</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="C217" s="2" t="n">
-        <v>1909</v>
+        <v>256</v>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>40-70 €</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Fideos chinos</t>
+          <t>Cocina vasca</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnWEgZ6yjzASlMSzIbZP633oC-zJYZzlB8f3bbz6qNY4jDB5YGqYtUPt1XzpvV7OLx-QS7me6-ZtTV_YirCvKEnztMWBwhGOPhruT012nYueKE-W3CDsOFgPQkoqkehD92_17MThw8axdNg=w80-h100-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcMnD4jlP8VhO2FOegz94Uyrw6Ut11nYrc7yte3NI-9BsQlq17GyWZbd2wvwPuyyXX0M50KPbvW5b8BLHcDhz3XOCk7lpWFJggzEoxD1GfjiaCW_Tv6SHEUSvrWJOxkjnAyC7mQKA=w80-h142-k-no</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>biang-biang-bar-chueca.jpg</t>
+          <t>amets-gastroteka.jpg</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>CASA PEI+</t>
+          <t>Santoku La Barra</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="C218" s="2" t="n">
-        <v>800</v>
+        <v>720</v>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>10-20 €</t>
+          <t>40-50 €</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Cocina asiática</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWm0z6_e2ir2rY95KB6aXmXZ2t80FUv0xophiD_jMduKeTtUu4cANv7PiPAuqiDssEm3QaITqj1oPiwvU-PBQTV5v1UswbCIgbsupecCEEoxUsttU45kbgnROPghW2TIt74XYDl0=w130-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc3_snviP5hM610ig9Ad0pVVJ4NIZbIZREubld2NsszvZDuchNHcweuGwDPm72AYNu77j22nzDkkI9NF1MVws6SF2wflHLUM76HbulyeDEiONPMeStCYSgZUm_zvUOSFRHL8u9hzaSGpC3H=w122-h92-k-no</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>casa-pei.jpg</t>
+          <t>santoku-la-barra.jpg</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Sushi Bar Tottori (Lagasca)</t>
+          <t>Raza Madrid Barquillo</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="C219" s="2" t="n">
-        <v>1234</v>
+        <v>4358</v>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>50-100 €</t>
+          <t>40-80 €</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Japonesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr"/>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlIlCtKmXRf7qTlDHlT8-hc1qD7qVF9RB-hiJq4yyqzsnVm_MG63J4hxe3UPLSEWJ5PGrt2ZmujrTCGzT6hDAl7kmp3SzGhowvYn4dzY8v04gHIruVvlnoVeySGzpCpZop06BoqveDrftTP=w80-h100-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcUIyEjmjuZrt4esUW6rE0Q9GbPGwsyi8MS2C5AIbvFMTAS0GXzRF0pMN3sYLwfaR96DN7uJzb3JC_49iXUTchOha31MvkP8UxY4QXTGfsARrkYixtf1kDaFjtphLIwa0Rfabl7rQ=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>sushi-bar-tottori-lagasca.jpg</t>
+          <t>raza-madrid-barquillo.jpg</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GAMAN by Luis Arévalo</t>
+          <t>Dispatch</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="C220" s="2" t="n">
-        <v>1868</v>
+        <v>414</v>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>50-100 €</t>
+          <t>20-30 €</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Peruana</t>
+          <t>Hamburguesa</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkCxiUFxRw3nm4JGLZXN5Ss6qdlBDdpNX-H85Bb-cFNh27AUGEjv-Q_TnmnHFCNQNpRZ2b3JuI4hToXvCv_ajNivlqcfqFxB05NpQBcZnKL0QYQnjSfZVXSe7goHjmcgwW54q4mjAmEJVk=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcQgxBf452YpcvRWtr72SItSNFaTCmfqiHQhM7lWMKZ-BDBxTlvkahVRd1w8fWwNdWdHeTHimG_ztghvm5Yj1ruVcWF58-l32gaenPZnI57zwWw0mXxAAIbqlf6VsioWvHNYmX2IqWGFrY=w80-h120-k-no</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>gaman-by-luis-arevalo.jpg</t>
+          <t>dispatch.jpg</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Fismuler | Madrid</t>
+          <t>HIRO Bistro</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="C221" s="2" t="n">
-        <v>3933</v>
+        <v>548</v>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>30-70 €</t>
+          <t>30-60 €</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Taberna</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlP3rIVHQnWMRBK0I5bZEcTEa4FrsgQcAThLNOrhF2LxcEoVKfU6i3uImhSvHCWPnGSFoQK5pM1RwaAepgIwfXLxOalmmpeUZM87sIPk-kvGrM9mI_isSs3NTlyCLGau9ODKb4jWNIH-lud=w80-h142-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeFPuS5QHkbRaSays5ke0zqhtL8RP8ruPD9sGKpzCz2t7cvVe3xXaIriflQeIKVi5kdIeo4urPYTHHnMtu4bC0feyg9g2kK_FZvoK-R57uh3V6P2DPwSmR4k-P9ZMayFdpV4xO4kWylnXLN=w138-h92-k-no</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>fismuler-madrid.jpg</t>
+          <t>hiro-bistro.jpg</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Bākkō | Omakase Madrid</t>
+          <t>MYO Hand Roll Bar | García Paredes</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="C222" s="2" t="n">
-        <v>474</v>
+        <v>263</v>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Más de 100 €</t>
+          <t>30-50 €</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -7929,64 +7921,64 @@
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWnitVyBt9hS3r9P1DxseAE0E9xyXBET8xnviTXG1hDByPW94Bexf1MMKfBvADoDWTK8RyzXveOackQj3XoQbtFjyYYI0bGLwZiOKt8MfW3hsTpmEXw9IH0PdiBse7OCl8OCeCSgU0OFtfA=w123-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcub4kyRIen5NqKNSEV9NZFVILX3gkgNh0Hc1Dyo-o8DI_wVmurfwlGYD9YgLpLgT8m25p0oT7O-eCeRWxrZ69QBDn_E8l8_-9NJPMgYBDLTqxI4va9RrEb3081V1m6CLG-VQkJnpMSzhCx=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>bakko-omakase-madrid.jpg</t>
+          <t>myo-hand-roll-bar-garcia-paredes.jpg</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Restaurante Farah</t>
+          <t>Biang Biang Bar Chueca</t>
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="C223" s="2" t="n">
-        <v>904</v>
+        <v>1929</v>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Fideos chinos</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlj65SS3CeymI9IK1WoDv0ldmp35xkmC1xT2dkCcUvupdqqW7metr3vCw0nsMQq4mCAO954XYsIAPHSM_L6muNDex9HJ6SRHtOZje7Q89T88E-mZM7HfWNGx7TsP5f9lCZyYBAucyCFp1S8=w80-h142-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdBTJvmRKjlkLFOJ9NAO96S9zm_H_PMF6_6YsWKdpSQA_nrpkAxlNSFi2ynwBN4O-ywEY0Cu48geVIZgNwIKQRxaypAxofpqKSkYS3laytUC4LWigf0Ya4Ga5UNfgjE73g9ysDAueTsh2i2=w80-h100-k-no</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>restaurante-farah.jpg</t>
+          <t>biang-biang-bar-chueca.jpg</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Casa Mùi</t>
+          <t>CASA PEI+</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="C224" s="2" t="n">
-        <v>453</v>
+        <v>815</v>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>30-40 €</t>
+          <t>10-20 €</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -7997,119 +7989,323 @@
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkb0scJIp9D9tjVRCRzEkr1qN1aOD_hmk3g0SZhgbmk1gWtdO9wLPn100PcejbK8xZmB_YTvSAM9QNvGYpIkc8aQYdKdKxpEzKWtpK5gZl_ndWD_okp9m8Wn-_LxCQt4lBt91iY=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdAz4Hsi-t2qitZjbvCAJS4_MxOs4IK0rNXaIcNIEWfTwf3ji8OKizDxzcmQYGyPBn7kNTAUZa12F2EsDiwuYfTmKfsUU_lSei4wSl3PSxLMAYLAPfC-9Ofw3zs6O1yq26XqOYb=w130-h92-k-no</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>casa-mui.jpg</t>
+          <t>casa-pei.jpg</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Smoked Room Madrid. Fire Omakase by Dani García</t>
+          <t>Sushi Bar Tottori (Lagasca)</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="C225" s="2" t="n">
-        <v>354</v>
+        <v>1255</v>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Más de 100 €</t>
+          <t>50-100 €</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Alta cocina</t>
+          <t>Japonesa</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWliggOLQTHpQ9w4rvdF6jCVdWVo6FvdxIjdEHyBKvrqyERLMeIWT_QiZefZH3Q1qQwJhqIIHl5hGVS3QFoxKriWNhV3pHYO_s4nUHnxq1ujPushtKRYpXsRdvf5_UVWAtt-FZ_X-A=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc6tmtmUPOpUhifgPh1DY3wvTrD68Ghh-BsVq8uX5F51TAgO5D-ovbEGhSzkKj-9SCWn-pm4N6HSgfUJT80FUDSrziyGapbiRko1po9RSoNzFm6QfjEkvNby7H71KOQ2RCzm-nYfOUcwLks=w80-h100-k-no</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>smoked-room-madrid-fire-omakase-by-dani-garcia.jpg</t>
+          <t>sushi-bar-tottori-lagasca.jpg</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Kuoco</t>
+          <t>GAMAN by Luis Arévalo</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="C226" s="2" t="n">
-        <v>2024</v>
+        <v>1926</v>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Más de 100 €</t>
+          <t>50-60 €</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Peruana</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWlbyYjn7hBQBddUxxyin0rERnLvrGYuC6glmE37DKbq81vCYRSdKdu4Xp6990Gru6xpw7Ge5a55kVyC79XYpl3crKB-Tf4LVfU5mWyAVRq_1d4fQN46Fhs6oux41bU0jrxASQlpD_m7AT0Z=w137-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLdwb7-CI5Y8u7GA5eMFDDTyp_RgcqKIpRCTZYtP_hp2OQmuvsGEt8AqCttA9FfhQloYOBFQGCltdzllRsFc0uwnq4RM5NmAG_dZKML1XrA64JVJFqIeFHLU9fdAe8mH3Nur6CQF=w137-h92-k-no</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>kuoco.jpg</t>
+          <t>gaman-by-luis-arevalo.jpg</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Pui's Thai Tapas</t>
+          <t>Fismuler | Madrid</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
         <v>4.4</v>
       </c>
       <c r="C227" s="2" t="n">
-        <v>2171</v>
+        <v>3980</v>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>20-30 €</t>
+          <t>30-70 €</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Tailandesa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>https://lh3.googleusercontent.com/gps-cs-s/AHRPTWkihOJUBSty1FjBbYUhyplG2HMKWQ3GHet4XDHPduR-aBQWS-q8eo5kmBVEPLpm4V9ZHZ3EG7ySeJnhCo5U7i3nFji0XaWwNpY7UHzE6UDAlChwRVeeH5CbreOyAbxAeY2XDiSb8g=w138-h92-k-no</t>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLcULDAxXuFLxxv02HZfcqwzkUm91qsXPKSde4nHRDPrCGwPrpdMuFkqAnE0jEPWyGYMzCG2haQv7l5Xa-gf9ZWxCi5kbUS7IzjfyBO0frSxk33f4IbudC0GxnfEm5bn_Z7iBg5_EWAdPUY=w92-h92-k-no</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
+          <t>fismuler-madrid.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Bākkō | Omakase Madrid</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C228" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Más de 100 €</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Japonesa</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLe3uPZ3oYG3zOJw7TpUUCf9id5-EL72gdsFW67RZAu-hOYKIfauX_WxByYhxATHqdoPzhMEeiyR9WBzDjnb5K_RbDs5QnqB9r9APWx8ndVB_Q7_fH4pkHsc3aZ3mnO-r31MeuAk6oJtJys=w123-h92-k-no</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>bakko-omakase-madrid.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Restaurante Farah</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C229" s="2" t="n">
+        <v>934</v>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>30-50 €</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLck4P4FqeP0gzNlIjed90PpzFs7e1XjQyrXHxKXuMmc3yHi7z5MKoTCnoKKYiDmassc50EkGUckmG1ELBm-78LdyNyGbJgNVqGSRUSaQJMX1-syaw-FMcGoUv2llB_d8coT87DZSUZydThI=w80-h142-k-no</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>restaurante-farah.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Casa Mùi</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C230" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>30-40 €</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLf7E1FwnK0sQzao8op8IgKRsZIicjkLKDlJ2iJTxEpxKZSgd4ay5fDKbiX_GMEwl_Tvl6ySV4xgyIfY4Uv-hNgnV-6LXdEY07tp_s1196lJDWaKpSPhaqcQ3fTTidYhv0g8Ciy-=w138-h92-k-no</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>casa-mui.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Smoked Room Madrid. Fire Omakase by Dani García</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C231" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Más de 100 €</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Alta cocina</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeN9ncG4S107ReYSju2g9WCYX5CHp0HdTKD12QSgPFdeHut3XuJ2SKPgSWInnhecivK4U47MZatelw7FMGraVey8HSStldKYZ5oVLQzgqxqXqX686vlUwolp0v2TD9uofYnX83c7g=w137-h92-k-no</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>smoked-room-madrid-fire-omakase-by-dani-garcia.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Kuoco</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C232" s="2" t="n">
+        <v>2043</v>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Más de 100 €</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLc4Q_xPRPjyWyqoN4qgYx-KGqc0YgzAv0Ie_fR7lzhmSdxsNUpY8J6WFQWYWVnGH06cEathIIjeqTDT3aiG8BmR92uwjmRC53iLwZg_i9WBWKoljOcWJ5GvosNQ74yPqOcIciPMzEZRcObd=w137-h92-k-no</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>kuoco.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Pui's Thai Tapas</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C233" s="2" t="n">
+        <v>2187</v>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>20-30 €</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>Tailandesa</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/grass-cs/AABkmLeTg8KnEjLcf3GSHwH7lqy2m8obFAeJvsqJqBw7YyeapNvCErm9w1Q_LiOC7eBDv8ey84W9B0L7A5fb4Dfgiwanv3TN22ivpARM8qPjSCuZJX_an5FIwlmfw4tBxL96CTCyEJP_yA=w138-h92-k-no</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
           <t>puis-thai-tapas.jpg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H227"/>
+  <autoFilter ref="A1:H233"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>